--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$94</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$104</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$92</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -4645,7 +4645,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-09-30</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 3.5, "op_wape_pct": 85.0, "n": 1, "note": "실측 1분기만 비교(나머지는 실적 없음 — 추정 vs 추정은 세지 않음) · 단일 회사 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 12543.01, "rev_act": 13003.49, "op_pred": 301.93, "op_act": 2008.07}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 3.5, "op_wape_pct": 85.0, "n": 1, "note": "실측 1분기만 비교(나머지는 실적 없음 — 추정 vs 추정은 세지 않음) · 단일 회사 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 12543.01, "rev_act": 13003.49, "op_pred": 301.93, "op_act": 2008.07}]}</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO94"/>
+  <dimension ref="A1:AO104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16444,66 +16444,35 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>-277126.05</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="31" t="n">
-        <v>170813.3</v>
-      </c>
-      <c r="H79" s="31" t="n">
-        <v>104465.44</v>
-      </c>
-      <c r="I79" s="31" t="n">
-        <v>-125000.98</v>
-      </c>
-      <c r="J79" s="31" t="n">
-        <v>58129.01</v>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>208406.77</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>-188211.1</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>-53555.39</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>11244.77</v>
-      </c>
-      <c r="O79" s="31" t="n">
-        <v>-302762.84</v>
-      </c>
-      <c r="P79" s="32" t="n">
-        <v>-533284.5600000001</v>
-      </c>
+      <c r="K79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
       <c r="Q79" s="31" t="n">
-        <v>273016.62</v>
+        <v>4357</v>
       </c>
       <c r="R79" s="31" t="n">
-        <v>173229.52</v>
+        <v>3987</v>
       </c>
       <c r="S79" s="31" t="n">
-        <v>177754.72</v>
+        <v>4372</v>
       </c>
       <c r="T79" s="31" t="n">
-        <v>-263100.88</v>
+        <v>3542</v>
       </c>
       <c r="U79" s="32" t="n">
-        <v>360899.98</v>
+        <v>16258</v>
       </c>
       <c r="V79" s="31" t="n">
-        <v>373397.19</v>
+        <v>2662</v>
       </c>
       <c r="W79" s="31" t="n">
-        <v>185990.07</v>
+        <v>3356</v>
       </c>
       <c r="X79" s="33" t="n">
-        <v>33364.41</v>
+        <v>4295</v>
       </c>
       <c r="Y79" s="10" t="n"/>
       <c r="Z79" s="11" t="n"/>
@@ -16529,66 +16498,35 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="n">
-        <v>4282.45</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="31" t="n">
-        <v>1706.76</v>
-      </c>
-      <c r="H80" s="31" t="n">
-        <v>2481.35</v>
-      </c>
-      <c r="I80" s="31" t="n">
-        <v>3695.38</v>
-      </c>
-      <c r="J80" s="31" t="n">
-        <v>5564.86</v>
-      </c>
-      <c r="K80" s="32" t="n">
-        <v>13448.35</v>
-      </c>
-      <c r="L80" s="31" t="n">
-        <v>4357.71</v>
-      </c>
-      <c r="M80" s="31" t="n">
-        <v>3827.73</v>
-      </c>
-      <c r="N80" s="31" t="n">
-        <v>3783.54</v>
-      </c>
-      <c r="O80" s="31" t="n">
-        <v>4127.83</v>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>16096.81</v>
-      </c>
+      <c r="K80" s="9" t="n"/>
+      <c r="P80" s="9" t="n"/>
       <c r="Q80" s="31" t="n">
-        <v>4101.74</v>
+        <v>62</v>
       </c>
       <c r="R80" s="31" t="n">
-        <v>4261.59</v>
+        <v>0</v>
       </c>
       <c r="S80" s="31" t="n">
-        <v>4566.95</v>
+        <v>0</v>
       </c>
       <c r="T80" s="31" t="n">
-        <v>3566.37</v>
+        <v>0</v>
       </c>
       <c r="U80" s="32" t="n">
-        <v>16496.65</v>
+        <v>62</v>
       </c>
       <c r="V80" s="31" t="n">
-        <v>2607.4</v>
+        <v>62</v>
       </c>
       <c r="W80" s="31" t="n">
-        <v>3185.5</v>
+        <v>0</v>
       </c>
       <c r="X80" s="33" t="n">
-        <v>4529.74</v>
+        <v>0</v>
       </c>
       <c r="Y80" s="10" t="n"/>
       <c r="Z80" s="11" t="n"/>
@@ -16614,66 +16552,35 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="n">
-        <v>-794.54</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="31" t="n">
-        <v>-893.52</v>
-      </c>
-      <c r="H81" s="31" t="n">
-        <v>-1319.03</v>
-      </c>
-      <c r="I81" s="31" t="n">
-        <v>-1626.76</v>
-      </c>
-      <c r="J81" s="31" t="n">
-        <v>-1579.31</v>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>-5418.62</v>
-      </c>
-      <c r="L81" s="31" t="n">
-        <v>-1516.71</v>
-      </c>
-      <c r="M81" s="31" t="n">
-        <v>-2761.78</v>
-      </c>
-      <c r="N81" s="31" t="n">
-        <v>-3720.91</v>
-      </c>
-      <c r="O81" s="31" t="n">
-        <v>-4621.86</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>-12621.26</v>
-      </c>
+      <c r="K81" s="9" t="n"/>
+      <c r="P81" s="9" t="n"/>
       <c r="Q81" s="31" t="n">
-        <v>-7512.68</v>
+        <v>6913</v>
       </c>
       <c r="R81" s="31" t="n">
-        <v>-4709.32</v>
+        <v>5247</v>
       </c>
       <c r="S81" s="31" t="n">
-        <v>-5689.37</v>
+        <v>4547</v>
       </c>
       <c r="T81" s="31" t="n">
-        <v>-2725.01</v>
+        <v>2756</v>
       </c>
       <c r="U81" s="32" t="n">
-        <v>-20636.38</v>
+        <v>19463</v>
       </c>
       <c r="V81" s="31" t="n">
-        <v>-3253.48</v>
+        <v>3218</v>
       </c>
       <c r="W81" s="31" t="n">
-        <v>-980.22</v>
+        <v>945</v>
       </c>
       <c r="X81" s="33" t="n">
-        <v>-1138.26</v>
+        <v>1136</v>
       </c>
       <c r="Y81" s="10" t="n"/>
       <c r="Z81" s="11" t="n"/>
@@ -16699,36 +16606,35 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="n">
-        <v>0</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="I82" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="31" t="n">
-        <v>0</v>
-      </c>
       <c r="K82" s="9" t="n"/>
-      <c r="N82" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>0</v>
-      </c>
       <c r="P82" s="9" t="n"/>
+      <c r="Q82" s="31" t="n">
+        <v>55680</v>
+      </c>
+      <c r="R82" s="31" t="n">
+        <v>70776</v>
+      </c>
       <c r="S82" s="31" t="n">
-        <v>0</v>
+        <v>38658</v>
       </c>
       <c r="T82" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" s="9" t="n"/>
+        <v>49739</v>
+      </c>
+      <c r="U82" s="32" t="n">
+        <v>214853</v>
+      </c>
+      <c r="V82" s="31" t="n">
+        <v>25945</v>
+      </c>
+      <c r="W82" s="31" t="n">
+        <v>42459</v>
+      </c>
       <c r="X82" s="33" t="n">
-        <v>0</v>
+        <v>52535</v>
       </c>
       <c r="Y82" s="10" t="n"/>
       <c r="Z82" s="11" t="n"/>
@@ -16754,66 +16660,35 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>998.0599999999999</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="G83" s="31" t="n">
-        <v>-708.73</v>
-      </c>
-      <c r="H83" s="31" t="n">
-        <v>134.1</v>
-      </c>
-      <c r="I83" s="31" t="n">
-        <v>-855.9</v>
-      </c>
-      <c r="J83" s="31" t="n">
-        <v>-754.63</v>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>-2185.16</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>-1603.51</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>436.18</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>-908.67</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>-891.87</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>-2967.87</v>
-      </c>
+      <c r="K83" s="9" t="n"/>
+      <c r="P83" s="9" t="n"/>
       <c r="Q83" s="31" t="n">
-        <v>-769.0599999999999</v>
+        <v>23076</v>
       </c>
       <c r="R83" s="31" t="n">
-        <v>2243.11</v>
+        <v>25167</v>
       </c>
       <c r="S83" s="31" t="n">
-        <v>-1015.08</v>
+        <v>48578</v>
       </c>
       <c r="T83" s="31" t="n">
-        <v>-1671.63</v>
+        <v>20919</v>
       </c>
       <c r="U83" s="32" t="n">
-        <v>-1212.66</v>
+        <v>117740</v>
       </c>
       <c r="V83" s="31" t="n">
-        <v>-2780.83</v>
+        <v>32246</v>
       </c>
       <c r="W83" s="31" t="n">
-        <v>93.31999999999999</v>
+        <v>82351</v>
       </c>
       <c r="X83" s="33" t="n">
-        <v>-4789.56</v>
+        <v>59961</v>
       </c>
       <c r="Y83" s="10" t="n"/>
       <c r="Z83" s="11" t="n"/>
@@ -16839,66 +16714,35 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E84" s="31" t="n">
-        <v>59163.3</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="G84" s="31" t="n">
-        <v>14323.61</v>
-      </c>
-      <c r="H84" s="31" t="n">
-        <v>-122026.47</v>
-      </c>
-      <c r="I84" s="31" t="n">
-        <v>11195.65</v>
-      </c>
-      <c r="J84" s="31" t="n">
-        <v>49239.81</v>
-      </c>
-      <c r="K84" s="32" t="n">
-        <v>-47267.4</v>
-      </c>
-      <c r="L84" s="31" t="n">
-        <v>-164.79</v>
-      </c>
-      <c r="M84" s="31" t="n">
-        <v>-41967.79</v>
-      </c>
-      <c r="N84" s="31" t="n">
-        <v>-41352.56</v>
-      </c>
-      <c r="O84" s="31" t="n">
-        <v>-28139.68</v>
-      </c>
-      <c r="P84" s="32" t="n">
-        <v>-111624.82</v>
-      </c>
+      <c r="K84" s="9" t="n"/>
+      <c r="P84" s="9" t="n"/>
       <c r="Q84" s="31" t="n">
-        <v>-20168.17</v>
+        <v>35797</v>
       </c>
       <c r="R84" s="31" t="n">
-        <v>-46989.31</v>
+        <v>0</v>
       </c>
       <c r="S84" s="31" t="n">
-        <v>-57535.23</v>
+        <v>0</v>
       </c>
       <c r="T84" s="31" t="n">
-        <v>-24467.08</v>
+        <v>77825</v>
       </c>
       <c r="U84" s="32" t="n">
-        <v>-149159.79</v>
+        <v>113622</v>
       </c>
       <c r="V84" s="31" t="n">
-        <v>-24053.75</v>
+        <v>9870</v>
       </c>
       <c r="W84" s="31" t="n">
-        <v>-43203.86</v>
+        <v>11049</v>
       </c>
       <c r="X84" s="33" t="n">
-        <v>-47602.35</v>
+        <v>56424</v>
       </c>
       <c r="Y84" s="10" t="n"/>
       <c r="Z84" s="11" t="n"/>
@@ -16924,66 +16768,35 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E85" s="31" t="n">
-        <v>81.06999999999999</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="31" t="n">
-        <v>152.44</v>
-      </c>
-      <c r="H85" s="31" t="n">
-        <v>144.29</v>
-      </c>
-      <c r="I85" s="31" t="n">
-        <v>379.52</v>
-      </c>
-      <c r="J85" s="31" t="n">
-        <v>143.01</v>
-      </c>
-      <c r="K85" s="32" t="n">
-        <v>819.26</v>
-      </c>
-      <c r="L85" s="31" t="n">
-        <v>96.27</v>
-      </c>
-      <c r="M85" s="31" t="n">
-        <v>156.54</v>
-      </c>
-      <c r="N85" s="31" t="n">
-        <v>1122.85</v>
-      </c>
-      <c r="O85" s="31" t="n">
-        <v>59.91</v>
-      </c>
-      <c r="P85" s="32" t="n">
-        <v>1435.57</v>
-      </c>
+      <c r="K85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
       <c r="Q85" s="31" t="n">
-        <v>21.15</v>
+        <v>10002</v>
       </c>
       <c r="R85" s="31" t="n">
-        <v>56.87</v>
+        <v>11048</v>
       </c>
       <c r="S85" s="31" t="n">
-        <v>57.98</v>
+        <v>38628</v>
       </c>
       <c r="T85" s="31" t="n">
-        <v>100.04</v>
+        <v>4848</v>
       </c>
       <c r="U85" s="32" t="n">
-        <v>236.04</v>
+        <v>64526</v>
       </c>
       <c r="V85" s="31" t="n">
-        <v>75.95</v>
+        <v>6229</v>
       </c>
       <c r="W85" s="31" t="n">
-        <v>32.1</v>
+        <v>64400</v>
       </c>
       <c r="X85" s="33" t="n">
-        <v>155.04</v>
+        <v>0</v>
       </c>
       <c r="Y85" s="10" t="n"/>
       <c r="Z85" s="11" t="n"/>
@@ -17009,17 +16822,36 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
-      </c>
-      <c r="E86" s="31" t="n">
-        <v>300</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="K86" s="9" t="n"/>
       <c r="P86" s="9" t="n"/>
-      <c r="U86" s="9" t="n"/>
-      <c r="X86" s="5" t="n"/>
+      <c r="Q86" s="31" t="n">
+        <v>836</v>
+      </c>
+      <c r="R86" s="31" t="n">
+        <v>998</v>
+      </c>
+      <c r="S86" s="31" t="n">
+        <v>154816</v>
+      </c>
+      <c r="T86" s="31" t="n">
+        <v>-19934</v>
+      </c>
+      <c r="U86" s="32" t="n">
+        <v>136716</v>
+      </c>
+      <c r="V86" s="31" t="n">
+        <v>6844</v>
+      </c>
+      <c r="W86" s="31" t="n">
+        <v>279207</v>
+      </c>
+      <c r="X86" s="33" t="n">
+        <v>13620</v>
+      </c>
       <c r="Y86" s="10" t="n"/>
       <c r="Z86" s="11" t="n"/>
       <c r="AA86" s="10" t="n"/>
@@ -17044,66 +16876,35 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E87" s="31" t="n">
-        <v>24549.79</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="31" t="n">
-        <v>25778.59</v>
-      </c>
-      <c r="H87" s="31" t="n">
-        <v>27979.13</v>
-      </c>
-      <c r="I87" s="31" t="n">
-        <v>35363.12</v>
-      </c>
-      <c r="J87" s="31" t="n">
-        <v>24697.17</v>
-      </c>
-      <c r="K87" s="32" t="n">
-        <v>113818.01</v>
-      </c>
-      <c r="L87" s="31" t="n">
-        <v>12709.68</v>
-      </c>
-      <c r="M87" s="31" t="n">
-        <v>36541.6</v>
-      </c>
-      <c r="N87" s="31" t="n">
-        <v>37058.97</v>
-      </c>
-      <c r="O87" s="31" t="n">
-        <v>31051.26</v>
-      </c>
-      <c r="P87" s="32" t="n">
-        <v>117361.51</v>
-      </c>
+      <c r="K87" s="9" t="n"/>
+      <c r="P87" s="9" t="n"/>
       <c r="Q87" s="31" t="n">
-        <v>25245.76</v>
+        <v>136360</v>
       </c>
       <c r="R87" s="31" t="n">
-        <v>40674.65</v>
+        <v>114421</v>
       </c>
       <c r="S87" s="31" t="n">
-        <v>52329.86</v>
+        <v>22967</v>
       </c>
       <c r="T87" s="31" t="n">
-        <v>26366.14</v>
+        <v>359609</v>
       </c>
       <c r="U87" s="32" t="n">
-        <v>144616.41</v>
+        <v>633357</v>
       </c>
       <c r="V87" s="31" t="n">
-        <v>27973.91</v>
+        <v>31244</v>
       </c>
       <c r="W87" s="31" t="n">
-        <v>34297.34</v>
+        <v>1374</v>
       </c>
       <c r="X87" s="33" t="n">
-        <v>42028.58</v>
+        <v>165333</v>
       </c>
       <c r="Y87" s="10" t="n"/>
       <c r="Z87" s="11" t="n"/>
@@ -17129,66 +16930,35 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E88" s="31" t="n">
-        <v>24756.66</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F88" s="9" t="n"/>
-      <c r="G88" s="31" t="n">
-        <v>26483.58</v>
-      </c>
-      <c r="H88" s="31" t="n">
-        <v>29160.3</v>
-      </c>
-      <c r="I88" s="31" t="n">
-        <v>37179.8</v>
-      </c>
-      <c r="J88" s="31" t="n">
-        <v>25944.91</v>
-      </c>
-      <c r="K88" s="32" t="n">
-        <v>118768.59</v>
-      </c>
-      <c r="L88" s="31" t="n">
-        <v>14294.11</v>
-      </c>
-      <c r="M88" s="31" t="n">
-        <v>38862.7</v>
-      </c>
-      <c r="N88" s="31" t="n">
-        <v>39913.4</v>
-      </c>
-      <c r="O88" s="31" t="n">
-        <v>34557.88</v>
-      </c>
-      <c r="P88" s="32" t="n">
-        <v>127628.09</v>
-      </c>
+      <c r="K88" s="9" t="n"/>
+      <c r="P88" s="9" t="n"/>
       <c r="Q88" s="31" t="n">
-        <v>25987.84</v>
+        <v>-2556</v>
       </c>
       <c r="R88" s="31" t="n">
-        <v>42005.73</v>
+        <v>-1260</v>
       </c>
       <c r="S88" s="31" t="n">
-        <v>53479.73</v>
+        <v>-175</v>
       </c>
       <c r="T88" s="31" t="n">
-        <v>29797.7</v>
+        <v>786</v>
       </c>
       <c r="U88" s="32" t="n">
-        <v>151271</v>
+        <v>-3205</v>
       </c>
       <c r="V88" s="31" t="n">
-        <v>28478.81</v>
+        <v>-556</v>
       </c>
       <c r="W88" s="31" t="n">
-        <v>35116.14</v>
+        <v>2411</v>
       </c>
       <c r="X88" s="33" t="n">
-        <v>42880.66</v>
+        <v>3159</v>
       </c>
       <c r="Y88" s="10" t="n"/>
       <c r="Z88" s="11" t="n"/>
@@ -17214,66 +16984,66 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E89" s="31" t="n">
-        <v>206.87</v>
+        <v>-277126.05</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="31" t="n">
-        <v>704.99</v>
+        <v>170813.3</v>
       </c>
       <c r="H89" s="31" t="n">
-        <v>1181.17</v>
+        <v>104465.44</v>
       </c>
       <c r="I89" s="31" t="n">
-        <v>1816.68</v>
+        <v>-125000.98</v>
       </c>
       <c r="J89" s="31" t="n">
-        <v>1247.74</v>
+        <v>58129.01</v>
       </c>
       <c r="K89" s="32" t="n">
-        <v>4950.58</v>
+        <v>208406.77</v>
       </c>
       <c r="L89" s="31" t="n">
-        <v>1584.43</v>
+        <v>-188211.1</v>
       </c>
       <c r="M89" s="31" t="n">
-        <v>2321.1</v>
+        <v>-53555.39</v>
       </c>
       <c r="N89" s="31" t="n">
-        <v>2854.43</v>
+        <v>11244.77</v>
       </c>
       <c r="O89" s="31" t="n">
-        <v>3506.62</v>
+        <v>-302762.84</v>
       </c>
       <c r="P89" s="32" t="n">
-        <v>10266.58</v>
+        <v>-533284.5600000001</v>
       </c>
       <c r="Q89" s="31" t="n">
-        <v>742.08</v>
+        <v>273016.62</v>
       </c>
       <c r="R89" s="31" t="n">
-        <v>1331.08</v>
+        <v>173229.52</v>
       </c>
       <c r="S89" s="31" t="n">
-        <v>1149.87</v>
+        <v>177754.72</v>
       </c>
       <c r="T89" s="31" t="n">
-        <v>3431.56</v>
+        <v>-263100.88</v>
       </c>
       <c r="U89" s="32" t="n">
-        <v>6654.59</v>
+        <v>360899.98</v>
       </c>
       <c r="V89" s="31" t="n">
-        <v>504.9</v>
+        <v>373397.19</v>
       </c>
       <c r="W89" s="31" t="n">
-        <v>818.8</v>
+        <v>185990.07</v>
       </c>
       <c r="X89" s="33" t="n">
-        <v>852.08</v>
+        <v>33364.41</v>
       </c>
       <c r="Y89" s="10" t="n"/>
       <c r="Z89" s="11" t="n"/>
@@ -17299,66 +17069,66 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E90" s="31" t="n">
-        <v>-19803.01</v>
+        <v>4282.45</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="31" t="n">
-        <v>29459.88</v>
+        <v>1706.76</v>
       </c>
       <c r="H90" s="31" t="n">
-        <v>-22849.06</v>
+        <v>2481.35</v>
       </c>
       <c r="I90" s="31" t="n">
-        <v>-41952.08</v>
+        <v>3695.38</v>
       </c>
       <c r="J90" s="31" t="n">
-        <v>-36271.62</v>
+        <v>5564.86</v>
       </c>
       <c r="K90" s="32" t="n">
-        <v>-71612.88</v>
+        <v>13448.35</v>
       </c>
       <c r="L90" s="31" t="n">
-        <v>61195.62</v>
+        <v>4357.71</v>
       </c>
       <c r="M90" s="31" t="n">
-        <v>112168.78</v>
+        <v>3827.73</v>
       </c>
       <c r="N90" s="31" t="n">
-        <v>72702.5</v>
+        <v>3783.54</v>
       </c>
       <c r="O90" s="31" t="n">
-        <v>217579.95</v>
+        <v>4127.83</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>463646.85</v>
+        <v>16096.81</v>
       </c>
       <c r="Q90" s="31" t="n">
-        <v>-145772.01</v>
+        <v>4101.74</v>
       </c>
       <c r="R90" s="31" t="n">
-        <v>-124965.07</v>
+        <v>4261.59</v>
       </c>
       <c r="S90" s="31" t="n">
-        <v>-140452.34</v>
+        <v>4566.95</v>
       </c>
       <c r="T90" s="31" t="n">
-        <v>48048.03</v>
+        <v>3566.37</v>
       </c>
       <c r="U90" s="32" t="n">
-        <v>-363141.39</v>
+        <v>16496.65</v>
       </c>
       <c r="V90" s="31" t="n">
-        <v>-80956.35000000001</v>
+        <v>2607.4</v>
       </c>
       <c r="W90" s="31" t="n">
-        <v>-58905.22</v>
+        <v>3185.5</v>
       </c>
       <c r="X90" s="33" t="n">
-        <v>-26092.23</v>
+        <v>4529.74</v>
       </c>
       <c r="Y90" s="10" t="n"/>
       <c r="Z90" s="11" t="n"/>
@@ -17384,66 +17154,66 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E91" s="31" t="n">
-        <v>488.69</v>
+        <v>-794.54</v>
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="31" t="n">
-        <v>277.53</v>
+        <v>-893.52</v>
       </c>
       <c r="H91" s="31" t="n">
-        <v>292.48</v>
+        <v>-1319.03</v>
       </c>
       <c r="I91" s="31" t="n">
-        <v>478.95</v>
+        <v>-1626.76</v>
       </c>
       <c r="J91" s="31" t="n">
-        <v>460.06</v>
+        <v>-1579.31</v>
       </c>
       <c r="K91" s="32" t="n">
-        <v>1509.02</v>
+        <v>-5418.62</v>
       </c>
       <c r="L91" s="31" t="n">
-        <v>298.33</v>
+        <v>-1516.71</v>
       </c>
       <c r="M91" s="31" t="n">
-        <v>369.84</v>
+        <v>-2761.78</v>
       </c>
       <c r="N91" s="31" t="n">
-        <v>591.8200000000001</v>
+        <v>-3720.91</v>
       </c>
       <c r="O91" s="31" t="n">
-        <v>404.48</v>
+        <v>-4621.86</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>1664.47</v>
+        <v>-12621.26</v>
       </c>
       <c r="Q91" s="31" t="n">
-        <v>1671.26</v>
+        <v>-7512.68</v>
       </c>
       <c r="R91" s="31" t="n">
-        <v>1472.54</v>
+        <v>-4709.32</v>
       </c>
       <c r="S91" s="31" t="n">
-        <v>1346.52</v>
+        <v>-5689.37</v>
       </c>
       <c r="T91" s="31" t="n">
-        <v>1299.29</v>
+        <v>-2725.01</v>
       </c>
       <c r="U91" s="32" t="n">
-        <v>5789.61</v>
+        <v>-20636.38</v>
       </c>
       <c r="V91" s="31" t="n">
-        <v>956.35</v>
+        <v>-3253.48</v>
       </c>
       <c r="W91" s="31" t="n">
-        <v>1012.32</v>
+        <v>-980.22</v>
       </c>
       <c r="X91" s="33" t="n">
-        <v>1412.31</v>
+        <v>-1138.26</v>
       </c>
       <c r="Y91" s="10" t="n"/>
       <c r="Z91" s="11" t="n"/>
@@ -17469,66 +17239,36 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E92" s="31" t="n">
-        <v>-237877.95</v>
+        <v>0</v>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="31" t="n">
-        <v>215217.07</v>
-      </c>
-      <c r="H92" s="31" t="n">
-        <v>-37791.11</v>
-      </c>
       <c r="I92" s="31" t="n">
-        <v>-151538.89</v>
+        <v>0</v>
       </c>
       <c r="J92" s="31" t="n">
-        <v>63885.83</v>
-      </c>
-      <c r="K92" s="32" t="n">
-        <v>89772.89999999999</v>
-      </c>
-      <c r="L92" s="31" t="n">
-        <v>-125351.78</v>
-      </c>
-      <c r="M92" s="31" t="n">
-        <v>16293.35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K92" s="9" t="n"/>
       <c r="N92" s="31" t="n">
-        <v>43112.89</v>
+        <v>0</v>
       </c>
       <c r="O92" s="31" t="n">
-        <v>-114157.42</v>
-      </c>
-      <c r="P92" s="32" t="n">
-        <v>-180102.96</v>
-      </c>
-      <c r="Q92" s="31" t="n">
-        <v>108171.53</v>
-      </c>
-      <c r="R92" s="31" t="n">
-        <v>2781.94</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P92" s="9" t="n"/>
       <c r="S92" s="31" t="n">
-        <v>-24390.76</v>
+        <v>0</v>
       </c>
       <c r="T92" s="31" t="n">
-        <v>-231507.39</v>
-      </c>
-      <c r="U92" s="32" t="n">
-        <v>-144944.68</v>
-      </c>
-      <c r="V92" s="31" t="n">
-        <v>268913.28</v>
-      </c>
-      <c r="W92" s="31" t="n">
-        <v>78806.78999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U92" s="9" t="n"/>
       <c r="X92" s="33" t="n">
-        <v>-39252.17</v>
+        <v>0</v>
       </c>
       <c r="Y92" s="10" t="n"/>
       <c r="Z92" s="11" t="n"/>
@@ -17554,66 +17294,66 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E93" s="31" t="n">
-        <v>-237877.95</v>
+        <v>998.0599999999999</v>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="G93" s="31" t="n">
-        <v>615588.03</v>
+        <v>-708.73</v>
       </c>
       <c r="H93" s="31" t="n">
-        <v>-37791.11</v>
+        <v>134.1</v>
       </c>
       <c r="I93" s="31" t="n">
-        <v>-151538.89</v>
+        <v>-855.9</v>
       </c>
       <c r="J93" s="31" t="n">
-        <v>63885.82</v>
+        <v>-754.63</v>
       </c>
       <c r="K93" s="32" t="n">
-        <v>490143.85</v>
+        <v>-2185.16</v>
       </c>
       <c r="L93" s="31" t="n">
-        <v>364792.08</v>
+        <v>-1603.51</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>16293.35</v>
+        <v>436.18</v>
       </c>
       <c r="N93" s="31" t="n">
-        <v>43112.89</v>
+        <v>-908.67</v>
       </c>
       <c r="O93" s="31" t="n">
-        <v>-114157.43</v>
+        <v>-891.87</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>310040.89</v>
+        <v>-2967.87</v>
       </c>
       <c r="Q93" s="31" t="n">
-        <v>418212.43</v>
+        <v>-769.0599999999999</v>
       </c>
       <c r="R93" s="31" t="n">
-        <v>2781.93</v>
+        <v>2243.11</v>
       </c>
       <c r="S93" s="31" t="n">
-        <v>-24390.76</v>
+        <v>-1015.08</v>
       </c>
       <c r="T93" s="31" t="n">
-        <v>-231507.39</v>
+        <v>-1671.63</v>
       </c>
       <c r="U93" s="32" t="n">
-        <v>165096.21</v>
+        <v>-1212.66</v>
       </c>
       <c r="V93" s="31" t="n">
-        <v>434009.49</v>
+        <v>-2780.83</v>
       </c>
       <c r="W93" s="31" t="n">
-        <v>78806.78999999999</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="X93" s="33" t="n">
-        <v>-39252.17</v>
+        <v>-4789.56</v>
       </c>
       <c r="Y93" s="10" t="n"/>
       <c r="Z93" s="11" t="n"/>
@@ -17639,15 +17379,66 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>배당금지급</t>
-        </is>
+          <t>투자활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E94" s="31" t="n">
+        <v>59163.3</v>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="K94" s="9" t="n"/>
-      <c r="P94" s="9" t="n"/>
-      <c r="U94" s="9" t="n"/>
+      <c r="G94" s="31" t="n">
+        <v>14323.61</v>
+      </c>
+      <c r="H94" s="31" t="n">
+        <v>-122026.47</v>
+      </c>
+      <c r="I94" s="31" t="n">
+        <v>11195.65</v>
+      </c>
+      <c r="J94" s="31" t="n">
+        <v>49239.81</v>
+      </c>
+      <c r="K94" s="32" t="n">
+        <v>-47267.4</v>
+      </c>
+      <c r="L94" s="31" t="n">
+        <v>-164.79</v>
+      </c>
+      <c r="M94" s="31" t="n">
+        <v>-41967.79</v>
+      </c>
+      <c r="N94" s="31" t="n">
+        <v>-41352.56</v>
+      </c>
+      <c r="O94" s="31" t="n">
+        <v>-28139.68</v>
+      </c>
+      <c r="P94" s="32" t="n">
+        <v>-111624.82</v>
+      </c>
+      <c r="Q94" s="31" t="n">
+        <v>-20168.17</v>
+      </c>
+      <c r="R94" s="31" t="n">
+        <v>-46989.31</v>
+      </c>
+      <c r="S94" s="31" t="n">
+        <v>-57535.23</v>
+      </c>
+      <c r="T94" s="31" t="n">
+        <v>-24467.08</v>
+      </c>
+      <c r="U94" s="32" t="n">
+        <v>-149159.79</v>
+      </c>
+      <c r="V94" s="31" t="n">
+        <v>-24053.75</v>
+      </c>
+      <c r="W94" s="31" t="n">
+        <v>-43203.86</v>
+      </c>
       <c r="X94" s="33" t="n">
-        <v>19144.46</v>
+        <v>-47602.35</v>
       </c>
       <c r="Y94" s="10" t="n"/>
       <c r="Z94" s="11" t="n"/>
@@ -17666,6 +17457,755 @@
       <c r="AM94" s="10" t="n"/>
       <c r="AN94" s="10" t="n"/>
       <c r="AO94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="E95" s="31" t="n">
+        <v>81.06999999999999</v>
+      </c>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="31" t="n">
+        <v>152.44</v>
+      </c>
+      <c r="H95" s="31" t="n">
+        <v>144.29</v>
+      </c>
+      <c r="I95" s="31" t="n">
+        <v>379.52</v>
+      </c>
+      <c r="J95" s="31" t="n">
+        <v>143.01</v>
+      </c>
+      <c r="K95" s="32" t="n">
+        <v>819.26</v>
+      </c>
+      <c r="L95" s="31" t="n">
+        <v>96.27</v>
+      </c>
+      <c r="M95" s="31" t="n">
+        <v>156.54</v>
+      </c>
+      <c r="N95" s="31" t="n">
+        <v>1122.85</v>
+      </c>
+      <c r="O95" s="31" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="P95" s="32" t="n">
+        <v>1435.57</v>
+      </c>
+      <c r="Q95" s="31" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="R95" s="31" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="S95" s="31" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="T95" s="31" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="U95" s="32" t="n">
+        <v>236.04</v>
+      </c>
+      <c r="V95" s="31" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="W95" s="31" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="X95" s="33" t="n">
+        <v>155.04</v>
+      </c>
+      <c r="Y95" s="10" t="n"/>
+      <c r="Z95" s="11" t="n"/>
+      <c r="AA95" s="10" t="n"/>
+      <c r="AB95" s="10" t="n"/>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="11" t="n"/>
+      <c r="AK95" s="10" t="n"/>
+      <c r="AL95" s="10" t="n"/>
+      <c r="AM95" s="10" t="n"/>
+      <c r="AN95" s="10" t="n"/>
+      <c r="AO95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>무형자산의감소</t>
+        </is>
+      </c>
+      <c r="E96" s="31" t="n">
+        <v>300</v>
+      </c>
+      <c r="F96" s="9" t="n"/>
+      <c r="K96" s="9" t="n"/>
+      <c r="P96" s="9" t="n"/>
+      <c r="U96" s="9" t="n"/>
+      <c r="X96" s="5" t="n"/>
+      <c r="Y96" s="10" t="n"/>
+      <c r="Z96" s="11" t="n"/>
+      <c r="AA96" s="10" t="n"/>
+      <c r="AB96" s="10" t="n"/>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="10" t="n"/>
+      <c r="AL96" s="10" t="n"/>
+      <c r="AM96" s="10" t="n"/>
+      <c r="AN96" s="10" t="n"/>
+      <c r="AO96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="E97" s="31" t="n">
+        <v>24549.79</v>
+      </c>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="31" t="n">
+        <v>25778.59</v>
+      </c>
+      <c r="H97" s="31" t="n">
+        <v>27979.13</v>
+      </c>
+      <c r="I97" s="31" t="n">
+        <v>35363.12</v>
+      </c>
+      <c r="J97" s="31" t="n">
+        <v>24697.17</v>
+      </c>
+      <c r="K97" s="32" t="n">
+        <v>113818.01</v>
+      </c>
+      <c r="L97" s="31" t="n">
+        <v>12709.68</v>
+      </c>
+      <c r="M97" s="31" t="n">
+        <v>36541.6</v>
+      </c>
+      <c r="N97" s="31" t="n">
+        <v>37058.97</v>
+      </c>
+      <c r="O97" s="31" t="n">
+        <v>31051.26</v>
+      </c>
+      <c r="P97" s="32" t="n">
+        <v>117361.51</v>
+      </c>
+      <c r="Q97" s="31" t="n">
+        <v>25245.76</v>
+      </c>
+      <c r="R97" s="31" t="n">
+        <v>40674.65</v>
+      </c>
+      <c r="S97" s="31" t="n">
+        <v>52329.86</v>
+      </c>
+      <c r="T97" s="31" t="n">
+        <v>26366.14</v>
+      </c>
+      <c r="U97" s="32" t="n">
+        <v>144616.41</v>
+      </c>
+      <c r="V97" s="31" t="n">
+        <v>27973.91</v>
+      </c>
+      <c r="W97" s="31" t="n">
+        <v>34297.34</v>
+      </c>
+      <c r="X97" s="33" t="n">
+        <v>42028.58</v>
+      </c>
+      <c r="Y97" s="10" t="n"/>
+      <c r="Z97" s="11" t="n"/>
+      <c r="AA97" s="10" t="n"/>
+      <c r="AB97" s="10" t="n"/>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="11" t="n"/>
+      <c r="AK97" s="10" t="n"/>
+      <c r="AL97" s="10" t="n"/>
+      <c r="AM97" s="10" t="n"/>
+      <c r="AN97" s="10" t="n"/>
+      <c r="AO97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E98" s="31" t="n">
+        <v>24756.66</v>
+      </c>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="31" t="n">
+        <v>26483.58</v>
+      </c>
+      <c r="H98" s="31" t="n">
+        <v>29160.3</v>
+      </c>
+      <c r="I98" s="31" t="n">
+        <v>37179.8</v>
+      </c>
+      <c r="J98" s="31" t="n">
+        <v>25944.91</v>
+      </c>
+      <c r="K98" s="32" t="n">
+        <v>118768.59</v>
+      </c>
+      <c r="L98" s="31" t="n">
+        <v>14294.11</v>
+      </c>
+      <c r="M98" s="31" t="n">
+        <v>38862.7</v>
+      </c>
+      <c r="N98" s="31" t="n">
+        <v>39913.4</v>
+      </c>
+      <c r="O98" s="31" t="n">
+        <v>34557.88</v>
+      </c>
+      <c r="P98" s="32" t="n">
+        <v>127628.09</v>
+      </c>
+      <c r="Q98" s="31" t="n">
+        <v>25987.84</v>
+      </c>
+      <c r="R98" s="31" t="n">
+        <v>42005.73</v>
+      </c>
+      <c r="S98" s="31" t="n">
+        <v>53479.73</v>
+      </c>
+      <c r="T98" s="31" t="n">
+        <v>29797.7</v>
+      </c>
+      <c r="U98" s="32" t="n">
+        <v>151271</v>
+      </c>
+      <c r="V98" s="31" t="n">
+        <v>28478.81</v>
+      </c>
+      <c r="W98" s="31" t="n">
+        <v>35116.14</v>
+      </c>
+      <c r="X98" s="33" t="n">
+        <v>42880.66</v>
+      </c>
+      <c r="Y98" s="10" t="n"/>
+      <c r="Z98" s="11" t="n"/>
+      <c r="AA98" s="10" t="n"/>
+      <c r="AB98" s="10" t="n"/>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="10" t="n"/>
+      <c r="AL98" s="10" t="n"/>
+      <c r="AM98" s="10" t="n"/>
+      <c r="AN98" s="10" t="n"/>
+      <c r="AO98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E99" s="31" t="n">
+        <v>206.87</v>
+      </c>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="31" t="n">
+        <v>704.99</v>
+      </c>
+      <c r="H99" s="31" t="n">
+        <v>1181.17</v>
+      </c>
+      <c r="I99" s="31" t="n">
+        <v>1816.68</v>
+      </c>
+      <c r="J99" s="31" t="n">
+        <v>1247.74</v>
+      </c>
+      <c r="K99" s="32" t="n">
+        <v>4950.58</v>
+      </c>
+      <c r="L99" s="31" t="n">
+        <v>1584.43</v>
+      </c>
+      <c r="M99" s="31" t="n">
+        <v>2321.1</v>
+      </c>
+      <c r="N99" s="31" t="n">
+        <v>2854.43</v>
+      </c>
+      <c r="O99" s="31" t="n">
+        <v>3506.62</v>
+      </c>
+      <c r="P99" s="32" t="n">
+        <v>10266.58</v>
+      </c>
+      <c r="Q99" s="31" t="n">
+        <v>742.08</v>
+      </c>
+      <c r="R99" s="31" t="n">
+        <v>1331.08</v>
+      </c>
+      <c r="S99" s="31" t="n">
+        <v>1149.87</v>
+      </c>
+      <c r="T99" s="31" t="n">
+        <v>3431.56</v>
+      </c>
+      <c r="U99" s="32" t="n">
+        <v>6654.59</v>
+      </c>
+      <c r="V99" s="31" t="n">
+        <v>504.9</v>
+      </c>
+      <c r="W99" s="31" t="n">
+        <v>818.8</v>
+      </c>
+      <c r="X99" s="33" t="n">
+        <v>852.08</v>
+      </c>
+      <c r="Y99" s="10" t="n"/>
+      <c r="Z99" s="11" t="n"/>
+      <c r="AA99" s="10" t="n"/>
+      <c r="AB99" s="10" t="n"/>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="10" t="n"/>
+      <c r="AL99" s="10" t="n"/>
+      <c r="AM99" s="10" t="n"/>
+      <c r="AN99" s="10" t="n"/>
+      <c r="AO99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E100" s="31" t="n">
+        <v>-19803.01</v>
+      </c>
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="31" t="n">
+        <v>29459.88</v>
+      </c>
+      <c r="H100" s="31" t="n">
+        <v>-22849.06</v>
+      </c>
+      <c r="I100" s="31" t="n">
+        <v>-41952.08</v>
+      </c>
+      <c r="J100" s="31" t="n">
+        <v>-36271.62</v>
+      </c>
+      <c r="K100" s="32" t="n">
+        <v>-71612.88</v>
+      </c>
+      <c r="L100" s="31" t="n">
+        <v>61195.62</v>
+      </c>
+      <c r="M100" s="31" t="n">
+        <v>112168.78</v>
+      </c>
+      <c r="N100" s="31" t="n">
+        <v>72702.5</v>
+      </c>
+      <c r="O100" s="31" t="n">
+        <v>217579.95</v>
+      </c>
+      <c r="P100" s="32" t="n">
+        <v>463646.85</v>
+      </c>
+      <c r="Q100" s="31" t="n">
+        <v>-145772.01</v>
+      </c>
+      <c r="R100" s="31" t="n">
+        <v>-124965.07</v>
+      </c>
+      <c r="S100" s="31" t="n">
+        <v>-140452.34</v>
+      </c>
+      <c r="T100" s="31" t="n">
+        <v>48048.03</v>
+      </c>
+      <c r="U100" s="32" t="n">
+        <v>-363141.39</v>
+      </c>
+      <c r="V100" s="31" t="n">
+        <v>-80956.35000000001</v>
+      </c>
+      <c r="W100" s="31" t="n">
+        <v>-58905.22</v>
+      </c>
+      <c r="X100" s="33" t="n">
+        <v>-26092.23</v>
+      </c>
+      <c r="Y100" s="10" t="n"/>
+      <c r="Z100" s="11" t="n"/>
+      <c r="AA100" s="10" t="n"/>
+      <c r="AB100" s="10" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="10" t="n"/>
+      <c r="AL100" s="10" t="n"/>
+      <c r="AM100" s="10" t="n"/>
+      <c r="AN100" s="10" t="n"/>
+      <c r="AO100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E101" s="31" t="n">
+        <v>488.69</v>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="31" t="n">
+        <v>277.53</v>
+      </c>
+      <c r="H101" s="31" t="n">
+        <v>292.48</v>
+      </c>
+      <c r="I101" s="31" t="n">
+        <v>478.95</v>
+      </c>
+      <c r="J101" s="31" t="n">
+        <v>460.06</v>
+      </c>
+      <c r="K101" s="32" t="n">
+        <v>1509.02</v>
+      </c>
+      <c r="L101" s="31" t="n">
+        <v>298.33</v>
+      </c>
+      <c r="M101" s="31" t="n">
+        <v>369.84</v>
+      </c>
+      <c r="N101" s="31" t="n">
+        <v>591.8200000000001</v>
+      </c>
+      <c r="O101" s="31" t="n">
+        <v>404.48</v>
+      </c>
+      <c r="P101" s="32" t="n">
+        <v>1664.47</v>
+      </c>
+      <c r="Q101" s="31" t="n">
+        <v>1671.26</v>
+      </c>
+      <c r="R101" s="31" t="n">
+        <v>1472.54</v>
+      </c>
+      <c r="S101" s="31" t="n">
+        <v>1346.52</v>
+      </c>
+      <c r="T101" s="31" t="n">
+        <v>1299.29</v>
+      </c>
+      <c r="U101" s="32" t="n">
+        <v>5789.61</v>
+      </c>
+      <c r="V101" s="31" t="n">
+        <v>956.35</v>
+      </c>
+      <c r="W101" s="31" t="n">
+        <v>1012.32</v>
+      </c>
+      <c r="X101" s="33" t="n">
+        <v>1412.31</v>
+      </c>
+      <c r="Y101" s="10" t="n"/>
+      <c r="Z101" s="11" t="n"/>
+      <c r="AA101" s="10" t="n"/>
+      <c r="AB101" s="10" t="n"/>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E102" s="31" t="n">
+        <v>-237877.95</v>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="31" t="n">
+        <v>215217.07</v>
+      </c>
+      <c r="H102" s="31" t="n">
+        <v>-37791.11</v>
+      </c>
+      <c r="I102" s="31" t="n">
+        <v>-151538.89</v>
+      </c>
+      <c r="J102" s="31" t="n">
+        <v>63885.83</v>
+      </c>
+      <c r="K102" s="32" t="n">
+        <v>89772.89999999999</v>
+      </c>
+      <c r="L102" s="31" t="n">
+        <v>-125351.78</v>
+      </c>
+      <c r="M102" s="31" t="n">
+        <v>16293.35</v>
+      </c>
+      <c r="N102" s="31" t="n">
+        <v>43112.89</v>
+      </c>
+      <c r="O102" s="31" t="n">
+        <v>-114157.42</v>
+      </c>
+      <c r="P102" s="32" t="n">
+        <v>-180102.96</v>
+      </c>
+      <c r="Q102" s="31" t="n">
+        <v>108171.53</v>
+      </c>
+      <c r="R102" s="31" t="n">
+        <v>2781.94</v>
+      </c>
+      <c r="S102" s="31" t="n">
+        <v>-24390.76</v>
+      </c>
+      <c r="T102" s="31" t="n">
+        <v>-231507.39</v>
+      </c>
+      <c r="U102" s="32" t="n">
+        <v>-144944.68</v>
+      </c>
+      <c r="V102" s="31" t="n">
+        <v>268913.28</v>
+      </c>
+      <c r="W102" s="31" t="n">
+        <v>78806.78999999999</v>
+      </c>
+      <c r="X102" s="33" t="n">
+        <v>-39252.17</v>
+      </c>
+      <c r="Y102" s="10" t="n"/>
+      <c r="Z102" s="11" t="n"/>
+      <c r="AA102" s="10" t="n"/>
+      <c r="AB102" s="10" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E103" s="31" t="n">
+        <v>-237877.95</v>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="31" t="n">
+        <v>615588.03</v>
+      </c>
+      <c r="H103" s="31" t="n">
+        <v>-37791.11</v>
+      </c>
+      <c r="I103" s="31" t="n">
+        <v>-151538.89</v>
+      </c>
+      <c r="J103" s="31" t="n">
+        <v>63885.82</v>
+      </c>
+      <c r="K103" s="32" t="n">
+        <v>490143.85</v>
+      </c>
+      <c r="L103" s="31" t="n">
+        <v>364792.08</v>
+      </c>
+      <c r="M103" s="31" t="n">
+        <v>16293.35</v>
+      </c>
+      <c r="N103" s="31" t="n">
+        <v>43112.89</v>
+      </c>
+      <c r="O103" s="31" t="n">
+        <v>-114157.43</v>
+      </c>
+      <c r="P103" s="32" t="n">
+        <v>310040.89</v>
+      </c>
+      <c r="Q103" s="31" t="n">
+        <v>418212.43</v>
+      </c>
+      <c r="R103" s="31" t="n">
+        <v>2781.93</v>
+      </c>
+      <c r="S103" s="31" t="n">
+        <v>-24390.76</v>
+      </c>
+      <c r="T103" s="31" t="n">
+        <v>-231507.39</v>
+      </c>
+      <c r="U103" s="32" t="n">
+        <v>165096.21</v>
+      </c>
+      <c r="V103" s="31" t="n">
+        <v>434009.49</v>
+      </c>
+      <c r="W103" s="31" t="n">
+        <v>78806.78999999999</v>
+      </c>
+      <c r="X103" s="33" t="n">
+        <v>-39252.17</v>
+      </c>
+      <c r="Y103" s="10" t="n"/>
+      <c r="Z103" s="11" t="n"/>
+      <c r="AA103" s="10" t="n"/>
+      <c r="AB103" s="10" t="n"/>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
+      <c r="P104" s="9" t="n"/>
+      <c r="U104" s="9" t="n"/>
+      <c r="X104" s="33" t="n">
+        <v>19144.46</v>
+      </c>
+      <c r="Y104" s="10" t="n"/>
+      <c r="Z104" s="11" t="n"/>
+      <c r="AA104" s="10" t="n"/>
+      <c r="AB104" s="10" t="n"/>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="10" t="n"/>
+      <c r="AL104" s="10" t="n"/>
+      <c r="AM104" s="10" t="n"/>
+      <c r="AN104" s="10" t="n"/>
+      <c r="AO104" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17926,7 +18466,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5032,7 +5032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-05</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5906,35 +5906,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -6025,35 +6025,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6144,35 +6144,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6263,35 +6263,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6382,35 +6382,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6501,35 +6501,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6620,35 +6620,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6739,35 +6739,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="D47" s="33" t="n">
-        <v>0.9354648903175657</v>
+        <v>0.9354648903175656</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19409,7 +19409,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -5032,7 +5032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-06</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5906,35 +5906,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -6025,35 +6025,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6144,35 +6144,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6263,35 +6263,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6382,35 +6382,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6501,35 +6501,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6620,35 +6620,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6739,35 +6739,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19409,7 +19409,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -5032,7 +5032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-07</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19409,7 +19409,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -5906,35 +5906,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -6025,35 +6025,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6144,35 +6144,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6263,35 +6263,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6382,35 +6382,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6501,35 +6501,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6620,35 +6620,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6739,35 +6739,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$104</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$105</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$92</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -5032,7 +5032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-08</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="D47" s="33" t="n">
-        <v>0.9354648903175656</v>
+        <v>0.9354648903175657</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO104"/>
+  <dimension ref="A1:AO105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12847,7 +12847,7 @@
         <v>276982.09</v>
       </c>
       <c r="R28" s="34" t="n">
-        <v>180481.47</v>
+        <v>160481</v>
       </c>
       <c r="S28" s="34" t="n">
         <v>94568.63</v>
@@ -12933,9 +12933,6 @@
       <c r="Q29" s="34" t="n">
         <v>276982.09</v>
       </c>
-      <c r="R29" s="34" t="n">
-        <v>180481.47</v>
-      </c>
       <c r="S29" s="34" t="n">
         <v>94568.63</v>
       </c>
@@ -13336,25 +13333,25 @@
         <v>10008.11</v>
       </c>
       <c r="G34" s="34" t="n">
-        <v>1507.08</v>
+        <v>10081.63</v>
       </c>
       <c r="H34" s="34" t="n">
-        <v>1231.99</v>
+        <v>9788.940000000001</v>
       </c>
       <c r="I34" s="34" t="n">
-        <v>1151.79</v>
+        <v>9357.15</v>
       </c>
       <c r="J34" s="34" t="n">
-        <v>1716.81</v>
+        <v>11558.32</v>
       </c>
       <c r="K34" s="35" t="n">
-        <v>1716.81</v>
+        <v>11558.32</v>
       </c>
       <c r="L34" s="34" t="n">
-        <v>1932.27</v>
+        <v>11921.09</v>
       </c>
       <c r="M34" s="34" t="n">
-        <v>2000.36</v>
+        <v>12152.18</v>
       </c>
       <c r="N34" s="34" t="n">
         <v>18224.38</v>
@@ -14031,7 +14028,27 @@
       <c r="F42" s="35" t="n">
         <v>8553.76</v>
       </c>
-      <c r="K42" s="9" t="n"/>
+      <c r="G42" s="34" t="n">
+        <v>8574.549999999999</v>
+      </c>
+      <c r="H42" s="34" t="n">
+        <v>8556.950000000001</v>
+      </c>
+      <c r="I42" s="34" t="n">
+        <v>8205.360000000001</v>
+      </c>
+      <c r="J42" s="34" t="n">
+        <v>9841.51</v>
+      </c>
+      <c r="K42" s="35" t="n">
+        <v>9841.51</v>
+      </c>
+      <c r="L42" s="34" t="n">
+        <v>9988.82</v>
+      </c>
+      <c r="M42" s="34" t="n">
+        <v>10151.82</v>
+      </c>
       <c r="N42" s="34" t="n">
         <v>14407.87</v>
       </c>
@@ -14099,25 +14116,25 @@
         <v>41493.39</v>
       </c>
       <c r="G43" s="34" t="n">
-        <v>30456.02</v>
+        <v>39030.57</v>
       </c>
       <c r="H43" s="34" t="n">
-        <v>81004.24000000001</v>
+        <v>89561.19</v>
       </c>
       <c r="I43" s="34" t="n">
-        <v>174527.51</v>
+        <v>182732.87</v>
       </c>
       <c r="J43" s="34" t="n">
-        <v>44078.8</v>
+        <v>53920.31</v>
       </c>
       <c r="K43" s="35" t="n">
-        <v>44078.8</v>
+        <v>53920.31</v>
       </c>
       <c r="L43" s="34" t="n">
-        <v>46542.5</v>
+        <v>56531.32</v>
       </c>
       <c r="M43" s="34" t="n">
-        <v>44884.85</v>
+        <v>55036.67</v>
       </c>
       <c r="N43" s="34" t="n">
         <v>74613.71000000001</v>
@@ -15176,7 +15193,7 @@
         <v>436982.09</v>
       </c>
       <c r="R55" s="34" t="n">
-        <v>320481.47</v>
+        <v>320481</v>
       </c>
       <c r="S55" s="34" t="n">
         <v>174568.63</v>
@@ -15263,7 +15280,7 @@
         <v>-74037.61</v>
       </c>
       <c r="R56" s="34" t="n">
-        <v>-225830.34</v>
+        <v>-225830.81</v>
       </c>
       <c r="S56" s="34" t="n">
         <v>-304288.68</v>
@@ -15577,67 +15594,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
-        </is>
-      </c>
-      <c r="E61" s="34" t="n">
-        <v>860545.88</v>
+          <t>유동성장기부채</t>
+        </is>
       </c>
       <c r="F61" s="9" t="n"/>
-      <c r="G61" s="34" t="n">
-        <v>875958.75</v>
-      </c>
-      <c r="H61" s="34" t="n">
-        <v>935436.14</v>
-      </c>
-      <c r="I61" s="34" t="n">
-        <v>882268.5699999999</v>
-      </c>
-      <c r="J61" s="34" t="n">
-        <v>1023197.48</v>
-      </c>
-      <c r="K61" s="35" t="n">
-        <v>3716860.94</v>
-      </c>
-      <c r="L61" s="34" t="n">
-        <v>909161.3</v>
-      </c>
-      <c r="M61" s="34" t="n">
-        <v>1033370.76</v>
-      </c>
-      <c r="N61" s="34" t="n">
-        <v>993800.53</v>
-      </c>
-      <c r="O61" s="34" t="n">
-        <v>1102733.12</v>
-      </c>
-      <c r="P61" s="35" t="n">
-        <v>4039065.71</v>
-      </c>
-      <c r="Q61" s="34" t="n">
-        <v>1000493.63</v>
-      </c>
+      <c r="K61" s="9" t="n"/>
+      <c r="P61" s="9" t="n"/>
       <c r="R61" s="34" t="n">
-        <v>1129062.86</v>
-      </c>
-      <c r="S61" s="34" t="n">
-        <v>1077667.04</v>
-      </c>
-      <c r="T61" s="34" t="n">
-        <v>1422825.22</v>
-      </c>
-      <c r="U61" s="35" t="n">
-        <v>4630048.75</v>
-      </c>
-      <c r="V61" s="34" t="n">
-        <v>1183823.02</v>
-      </c>
-      <c r="W61" s="34" t="n">
-        <v>1234448.39</v>
-      </c>
-      <c r="X61" s="36" t="n">
-        <v>1300349.18</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="U61" s="9" t="n"/>
+      <c r="X61" s="5" t="n"/>
       <c r="Y61" s="10" t="n"/>
       <c r="Z61" s="11" t="n"/>
       <c r="AA61" s="10" t="n"/>
@@ -15662,66 +15629,66 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>매출액(수익)</t>
         </is>
       </c>
       <c r="E62" s="34" t="n">
-        <v>904118.38</v>
+        <v>860545.88</v>
       </c>
       <c r="F62" s="9" t="n"/>
       <c r="G62" s="34" t="n">
-        <v>910119.27</v>
+        <v>875958.75</v>
       </c>
       <c r="H62" s="34" t="n">
-        <v>912937.13</v>
+        <v>935436.14</v>
       </c>
       <c r="I62" s="34" t="n">
-        <v>837566.97</v>
+        <v>882268.5699999999</v>
       </c>
       <c r="J62" s="34" t="n">
-        <v>1043382.9</v>
+        <v>1023197.48</v>
       </c>
       <c r="K62" s="35" t="n">
-        <v>3704006.27</v>
+        <v>3716860.94</v>
       </c>
       <c r="L62" s="34" t="n">
-        <v>916503.53</v>
+        <v>909161.3</v>
       </c>
       <c r="M62" s="34" t="n">
-        <v>1055211.06</v>
+        <v>1033370.76</v>
       </c>
       <c r="N62" s="34" t="n">
-        <v>968931.1800000001</v>
+        <v>993800.53</v>
       </c>
       <c r="O62" s="34" t="n">
-        <v>1129092.3</v>
+        <v>1102733.12</v>
       </c>
       <c r="P62" s="35" t="n">
-        <v>4069738.07</v>
+        <v>4039065.71</v>
       </c>
       <c r="Q62" s="34" t="n">
-        <v>973253.53</v>
+        <v>1000493.63</v>
       </c>
       <c r="R62" s="34" t="n">
-        <v>1073429.94</v>
+        <v>1129062.86</v>
       </c>
       <c r="S62" s="34" t="n">
-        <v>1003389.35</v>
+        <v>1077667.04</v>
       </c>
       <c r="T62" s="34" t="n">
-        <v>1332063.89</v>
+        <v>1422825.22</v>
       </c>
       <c r="U62" s="35" t="n">
-        <v>4382136.71</v>
+        <v>4630048.75</v>
       </c>
       <c r="V62" s="34" t="n">
-        <v>1076844.94</v>
+        <v>1183823.02</v>
       </c>
       <c r="W62" s="34" t="n">
-        <v>1101947.64</v>
+        <v>1234448.39</v>
       </c>
       <c r="X62" s="36" t="n">
-        <v>1050007.01</v>
+        <v>1300349.18</v>
       </c>
       <c r="Y62" s="10" t="n"/>
       <c r="Z62" s="11" t="n"/>
@@ -15747,66 +15714,66 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="E63" s="34" t="n">
-        <v>-43572.51</v>
+        <v>904118.38</v>
       </c>
       <c r="F63" s="9" t="n"/>
       <c r="G63" s="34" t="n">
-        <v>-34160.52</v>
+        <v>910119.27</v>
       </c>
       <c r="H63" s="34" t="n">
-        <v>22499.01</v>
+        <v>912937.13</v>
       </c>
       <c r="I63" s="34" t="n">
-        <v>44701.59</v>
+        <v>837566.97</v>
       </c>
       <c r="J63" s="34" t="n">
-        <v>-20185.4</v>
+        <v>1043382.9</v>
       </c>
       <c r="K63" s="35" t="n">
-        <v>12854.68</v>
+        <v>3704006.27</v>
       </c>
       <c r="L63" s="34" t="n">
-        <v>-7342.24</v>
+        <v>916503.53</v>
       </c>
       <c r="M63" s="34" t="n">
-        <v>-21840.3</v>
+        <v>1055211.06</v>
       </c>
       <c r="N63" s="34" t="n">
-        <v>24869.35</v>
+        <v>968931.1800000001</v>
       </c>
       <c r="O63" s="34" t="n">
-        <v>-26359.17</v>
+        <v>1129092.3</v>
       </c>
       <c r="P63" s="35" t="n">
-        <v>-30672.36</v>
+        <v>4069738.07</v>
       </c>
       <c r="Q63" s="34" t="n">
-        <v>27240.1</v>
+        <v>973253.53</v>
       </c>
       <c r="R63" s="34" t="n">
-        <v>55632.92</v>
+        <v>1073429.94</v>
       </c>
       <c r="S63" s="34" t="n">
-        <v>74277.7</v>
+        <v>1003389.35</v>
       </c>
       <c r="T63" s="34" t="n">
-        <v>90761.35000000001</v>
+        <v>1332063.89</v>
       </c>
       <c r="U63" s="35" t="n">
-        <v>247912.07</v>
+        <v>4382136.71</v>
       </c>
       <c r="V63" s="34" t="n">
-        <v>106978.08</v>
+        <v>1076844.94</v>
       </c>
       <c r="W63" s="34" t="n">
-        <v>132500.75</v>
+        <v>1101947.64</v>
       </c>
       <c r="X63" s="36" t="n">
-        <v>250342.17</v>
+        <v>1050007.01</v>
       </c>
       <c r="Y63" s="10" t="n"/>
       <c r="Z63" s="11" t="n"/>
@@ -15832,66 +15799,66 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="E64" s="34" t="n">
-        <v>33434.36</v>
+        <v>-43572.51</v>
       </c>
       <c r="F64" s="9" t="n"/>
       <c r="G64" s="34" t="n">
-        <v>27674.49</v>
+        <v>-34160.52</v>
       </c>
       <c r="H64" s="34" t="n">
-        <v>29099.78</v>
+        <v>22499.01</v>
       </c>
       <c r="I64" s="34" t="n">
-        <v>30633.25</v>
+        <v>44701.59</v>
       </c>
       <c r="J64" s="34" t="n">
-        <v>34513.27</v>
+        <v>-20185.4</v>
       </c>
       <c r="K64" s="35" t="n">
-        <v>121920.79</v>
+        <v>12854.68</v>
       </c>
       <c r="L64" s="34" t="n">
-        <v>20070.5</v>
+        <v>-7342.24</v>
       </c>
       <c r="M64" s="34" t="n">
-        <v>30627.65</v>
+        <v>-21840.3</v>
       </c>
       <c r="N64" s="34" t="n">
-        <v>32725.63</v>
+        <v>24869.35</v>
       </c>
       <c r="O64" s="34" t="n">
-        <v>38820.2</v>
+        <v>-26359.17</v>
       </c>
       <c r="P64" s="35" t="n">
-        <v>122243.98</v>
+        <v>-30672.36</v>
       </c>
       <c r="Q64" s="34" t="n">
-        <v>38284.07</v>
+        <v>27240.1</v>
       </c>
       <c r="R64" s="34" t="n">
-        <v>38208.52</v>
+        <v>55632.92</v>
       </c>
       <c r="S64" s="34" t="n">
-        <v>39027.39</v>
+        <v>74277.7</v>
       </c>
       <c r="T64" s="34" t="n">
-        <v>43864.18</v>
+        <v>90761.35000000001</v>
       </c>
       <c r="U64" s="35" t="n">
-        <v>159384.16</v>
+        <v>247912.07</v>
       </c>
       <c r="V64" s="34" t="n">
-        <v>38493.99</v>
+        <v>106978.08</v>
       </c>
       <c r="W64" s="34" t="n">
-        <v>43081.52</v>
+        <v>132500.75</v>
       </c>
       <c r="X64" s="36" t="n">
-        <v>49534.75</v>
+        <v>250342.17</v>
       </c>
       <c r="Y64" s="10" t="n"/>
       <c r="Z64" s="11" t="n"/>
@@ -15917,66 +15884,66 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="E65" s="34" t="n">
-        <v>-77006.86</v>
+        <v>33434.36</v>
       </c>
       <c r="F65" s="9" t="n"/>
       <c r="G65" s="34" t="n">
-        <v>-61835.01</v>
+        <v>27674.49</v>
       </c>
       <c r="H65" s="34" t="n">
-        <v>-6600.78</v>
+        <v>29099.78</v>
       </c>
       <c r="I65" s="34" t="n">
-        <v>14068.34</v>
+        <v>30633.25</v>
       </c>
       <c r="J65" s="34" t="n">
-        <v>-54698.67</v>
+        <v>34513.27</v>
       </c>
       <c r="K65" s="35" t="n">
-        <v>-109066.12</v>
+        <v>121920.79</v>
       </c>
       <c r="L65" s="34" t="n">
-        <v>-27412.73</v>
+        <v>20070.5</v>
       </c>
       <c r="M65" s="34" t="n">
-        <v>-52467.95</v>
+        <v>30627.65</v>
       </c>
       <c r="N65" s="34" t="n">
-        <v>-7856.29</v>
+        <v>32725.63</v>
       </c>
       <c r="O65" s="34" t="n">
-        <v>-65179.38</v>
+        <v>38820.2</v>
       </c>
       <c r="P65" s="35" t="n">
-        <v>-152916.35</v>
+        <v>122243.98</v>
       </c>
       <c r="Q65" s="34" t="n">
-        <v>-11043.97</v>
+        <v>38284.07</v>
       </c>
       <c r="R65" s="34" t="n">
-        <v>17424.4</v>
+        <v>38208.52</v>
       </c>
       <c r="S65" s="34" t="n">
-        <v>35250.31</v>
+        <v>39027.39</v>
       </c>
       <c r="T65" s="34" t="n">
-        <v>46897.16</v>
+        <v>43864.18</v>
       </c>
       <c r="U65" s="35" t="n">
-        <v>88527.89999999999</v>
+        <v>159384.16</v>
       </c>
       <c r="V65" s="34" t="n">
-        <v>68484.09</v>
+        <v>38493.99</v>
       </c>
       <c r="W65" s="34" t="n">
-        <v>89419.23</v>
+        <v>43081.52</v>
       </c>
       <c r="X65" s="36" t="n">
-        <v>200807.42</v>
+        <v>49534.75</v>
       </c>
       <c r="Y65" s="10" t="n"/>
       <c r="Z65" s="11" t="n"/>
@@ -16002,66 +15969,66 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="E66" s="34" t="n">
-        <v>1195.07</v>
+        <v>-77006.86</v>
       </c>
       <c r="F66" s="9" t="n"/>
       <c r="G66" s="34" t="n">
-        <v>53668.16</v>
+        <v>-61835.01</v>
       </c>
       <c r="H66" s="34" t="n">
-        <v>104555.76</v>
+        <v>-6600.78</v>
       </c>
       <c r="I66" s="34" t="n">
-        <v>189143.77</v>
+        <v>14068.34</v>
       </c>
       <c r="J66" s="34" t="n">
-        <v>15041.13</v>
+        <v>-54698.67</v>
       </c>
       <c r="K66" s="35" t="n">
-        <v>362408.82</v>
+        <v>-109066.12</v>
       </c>
       <c r="L66" s="34" t="n">
-        <v>96006.47</v>
+        <v>-27412.73</v>
       </c>
       <c r="M66" s="34" t="n">
-        <v>58463.62</v>
+        <v>-52467.95</v>
       </c>
       <c r="N66" s="34" t="n">
-        <v>66725.12</v>
+        <v>-7856.29</v>
       </c>
       <c r="O66" s="34" t="n">
-        <v>25449.53</v>
+        <v>-65179.38</v>
       </c>
       <c r="P66" s="35" t="n">
-        <v>246644.74</v>
+        <v>-152916.35</v>
       </c>
       <c r="Q66" s="34" t="n">
-        <v>96732.17999999999</v>
+        <v>-11043.97</v>
       </c>
       <c r="R66" s="34" t="n">
-        <v>75761.3</v>
+        <v>17424.4</v>
       </c>
       <c r="S66" s="34" t="n">
-        <v>197846.34</v>
+        <v>35250.31</v>
       </c>
       <c r="T66" s="34" t="n">
-        <v>111172.08</v>
+        <v>46897.16</v>
       </c>
       <c r="U66" s="35" t="n">
-        <v>481511.9</v>
+        <v>88527.89999999999</v>
       </c>
       <c r="V66" s="34" t="n">
-        <v>45383.44</v>
+        <v>68484.09</v>
       </c>
       <c r="W66" s="34" t="n">
-        <v>336070.62</v>
+        <v>89419.23</v>
       </c>
       <c r="X66" s="36" t="n">
-        <v>126873.65</v>
+        <v>200807.42</v>
       </c>
       <c r="Y66" s="10" t="n"/>
       <c r="Z66" s="11" t="n"/>
@@ -16087,66 +16054,66 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="E67" s="34" t="n">
-        <v>4460.13</v>
+        <v>1195.07</v>
       </c>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="34" t="n">
-        <v>66730.03999999999</v>
+        <v>53668.16</v>
       </c>
       <c r="H67" s="34" t="n">
-        <v>195716.47</v>
+        <v>104555.76</v>
       </c>
       <c r="I67" s="34" t="n">
-        <v>317517.92</v>
+        <v>189143.77</v>
       </c>
       <c r="J67" s="34" t="n">
-        <v>-140005</v>
+        <v>15041.13</v>
       </c>
       <c r="K67" s="35" t="n">
-        <v>439959.43</v>
+        <v>362408.82</v>
       </c>
       <c r="L67" s="34" t="n">
-        <v>132242.95</v>
+        <v>96006.47</v>
       </c>
       <c r="M67" s="34" t="n">
-        <v>64766.54</v>
+        <v>58463.62</v>
       </c>
       <c r="N67" s="34" t="n">
-        <v>130225.19</v>
+        <v>66725.12</v>
       </c>
       <c r="O67" s="34" t="n">
-        <v>-16833.39</v>
+        <v>25449.53</v>
       </c>
       <c r="P67" s="35" t="n">
-        <v>310401.29</v>
+        <v>246644.74</v>
       </c>
       <c r="Q67" s="34" t="n">
-        <v>176351.15</v>
+        <v>96732.17999999999</v>
       </c>
       <c r="R67" s="34" t="n">
-        <v>155883.22</v>
+        <v>75761.3</v>
       </c>
       <c r="S67" s="34" t="n">
-        <v>114720.45</v>
+        <v>197846.34</v>
       </c>
       <c r="T67" s="34" t="n">
-        <v>388132.17</v>
+        <v>111172.08</v>
       </c>
       <c r="U67" s="35" t="n">
-        <v>835086.99</v>
+        <v>481511.9</v>
       </c>
       <c r="V67" s="34" t="n">
-        <v>72937.35000000001</v>
+        <v>45383.44</v>
       </c>
       <c r="W67" s="34" t="n">
-        <v>149070.35</v>
+        <v>336070.62</v>
       </c>
       <c r="X67" s="36" t="n">
-        <v>226429.97</v>
+        <v>126873.65</v>
       </c>
       <c r="Y67" s="10" t="n"/>
       <c r="Z67" s="11" t="n"/>
@@ -16172,66 +16139,66 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="E68" s="34" t="n">
-        <v>285.48</v>
+        <v>4460.13</v>
       </c>
       <c r="F68" s="9" t="n"/>
       <c r="G68" s="34" t="n">
-        <v>30870.54</v>
+        <v>66730.03999999999</v>
       </c>
       <c r="H68" s="34" t="n">
-        <v>151072.65</v>
+        <v>195716.47</v>
       </c>
       <c r="I68" s="34" t="n">
-        <v>284603.73</v>
+        <v>317517.92</v>
       </c>
       <c r="J68" s="34" t="n">
-        <v>-249360.06</v>
+        <v>-140005</v>
       </c>
       <c r="K68" s="35" t="n">
-        <v>217186.86</v>
+        <v>439959.43</v>
       </c>
       <c r="L68" s="34" t="n">
-        <v>67092.05</v>
+        <v>132242.95</v>
       </c>
       <c r="M68" s="34" t="n">
-        <v>22391.99</v>
+        <v>64766.54</v>
       </c>
       <c r="N68" s="34" t="n">
-        <v>90055.83</v>
+        <v>130225.19</v>
       </c>
       <c r="O68" s="34" t="n">
-        <v>-66761.22</v>
+        <v>-16833.39</v>
       </c>
       <c r="P68" s="35" t="n">
-        <v>112778.65</v>
+        <v>310401.29</v>
       </c>
       <c r="Q68" s="34" t="n">
-        <v>107249.15</v>
+        <v>176351.15</v>
       </c>
       <c r="R68" s="34" t="n">
-        <v>103563.63</v>
+        <v>155883.22</v>
       </c>
       <c r="S68" s="34" t="n">
-        <v>847.11</v>
+        <v>114720.45</v>
       </c>
       <c r="T68" s="34" t="n">
-        <v>333631.87</v>
+        <v>388132.17</v>
       </c>
       <c r="U68" s="35" t="n">
-        <v>545291.76</v>
+        <v>835086.99</v>
       </c>
       <c r="V68" s="34" t="n">
-        <v>28986.59</v>
+        <v>72937.35000000001</v>
       </c>
       <c r="W68" s="34" t="n">
-        <v>500.66</v>
+        <v>149070.35</v>
       </c>
       <c r="X68" s="36" t="n">
-        <v>136763.59</v>
+        <v>226429.97</v>
       </c>
       <c r="Y68" s="10" t="n"/>
       <c r="Z68" s="11" t="n"/>
@@ -16257,66 +16224,66 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="E69" s="34" t="n">
-        <v>23192.57</v>
+        <v>285.48</v>
       </c>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="34" t="n">
-        <v>5630.29</v>
+        <v>30870.54</v>
       </c>
       <c r="H69" s="34" t="n">
-        <v>2474.16</v>
+        <v>151072.65</v>
       </c>
       <c r="I69" s="34" t="n">
-        <v>28300.93</v>
+        <v>284603.73</v>
       </c>
       <c r="J69" s="34" t="n">
-        <v>57412.41</v>
+        <v>-249360.06</v>
       </c>
       <c r="K69" s="35" t="n">
-        <v>93817.78999999999</v>
+        <v>217186.86</v>
       </c>
       <c r="L69" s="34" t="n">
-        <v>8258.299999999999</v>
+        <v>67092.05</v>
       </c>
       <c r="M69" s="34" t="n">
-        <v>9968.09</v>
+        <v>22391.99</v>
       </c>
       <c r="N69" s="34" t="n">
-        <v>5080.01</v>
+        <v>90055.83</v>
       </c>
       <c r="O69" s="34" t="n">
-        <v>29685.92</v>
+        <v>-66761.22</v>
       </c>
       <c r="P69" s="35" t="n">
-        <v>52992.32</v>
+        <v>112778.65</v>
       </c>
       <c r="Q69" s="34" t="n">
-        <v>13284.14</v>
+        <v>107249.15</v>
       </c>
       <c r="R69" s="34" t="n">
-        <v>5274.82</v>
+        <v>103563.63</v>
       </c>
       <c r="S69" s="34" t="n">
-        <v>116381.47</v>
+        <v>847.11</v>
       </c>
       <c r="T69" s="34" t="n">
-        <v>-903.7</v>
+        <v>333631.87</v>
       </c>
       <c r="U69" s="35" t="n">
-        <v>134036.73</v>
+        <v>545291.76</v>
       </c>
       <c r="V69" s="34" t="n">
-        <v>10106.06</v>
+        <v>28986.59</v>
       </c>
       <c r="W69" s="34" t="n">
-        <v>249025.31</v>
+        <v>500.66</v>
       </c>
       <c r="X69" s="36" t="n">
-        <v>7236.62</v>
+        <v>136763.59</v>
       </c>
       <c r="Y69" s="10" t="n"/>
       <c r="Z69" s="11" t="n"/>
@@ -16342,66 +16309,66 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="E70" s="34" t="n">
-        <v>-103179.03</v>
+        <v>23192.57</v>
       </c>
       <c r="F70" s="9" t="n"/>
       <c r="G70" s="34" t="n">
-        <v>-49656.65</v>
+        <v>5630.29</v>
       </c>
       <c r="H70" s="34" t="n">
-        <v>50837.01</v>
+        <v>2474.16</v>
       </c>
       <c r="I70" s="34" t="n">
-        <v>141996.99</v>
+        <v>28300.93</v>
       </c>
       <c r="J70" s="34" t="n">
-        <v>-206425.01</v>
+        <v>57412.41</v>
       </c>
       <c r="K70" s="35" t="n">
-        <v>-63247.66</v>
+        <v>93817.78999999999</v>
       </c>
       <c r="L70" s="34" t="n">
-        <v>-4815.46</v>
+        <v>8258.299999999999</v>
       </c>
       <c r="M70" s="34" t="n">
-        <v>-46346.97</v>
+        <v>9968.09</v>
       </c>
       <c r="N70" s="34" t="n">
-        <v>13619.47</v>
+        <v>5080.01</v>
       </c>
       <c r="O70" s="34" t="n">
-        <v>-119343.61</v>
+        <v>29685.92</v>
       </c>
       <c r="P70" s="35" t="n">
-        <v>-156886.57</v>
+        <v>52992.32</v>
       </c>
       <c r="Q70" s="34" t="n">
-        <v>3302.06</v>
+        <v>13284.14</v>
       </c>
       <c r="R70" s="34" t="n">
-        <v>35591.29</v>
+        <v>5274.82</v>
       </c>
       <c r="S70" s="34" t="n">
-        <v>2841.83</v>
+        <v>116381.47</v>
       </c>
       <c r="T70" s="34" t="n">
-        <v>104472.65</v>
+        <v>-903.7</v>
       </c>
       <c r="U70" s="35" t="n">
-        <v>146207.83</v>
+        <v>134036.73</v>
       </c>
       <c r="V70" s="34" t="n">
-        <v>59810.7</v>
+        <v>10106.06</v>
       </c>
       <c r="W70" s="34" t="n">
-        <v>27894.84</v>
+        <v>249025.31</v>
       </c>
       <c r="X70" s="36" t="n">
-        <v>230778.08</v>
+        <v>7236.62</v>
       </c>
       <c r="Y70" s="10" t="n"/>
       <c r="Z70" s="11" t="n"/>
@@ -16427,66 +16394,66 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="E71" s="34" t="n">
-        <v>-24812.81</v>
+        <v>-103179.03</v>
       </c>
       <c r="F71" s="9" t="n"/>
       <c r="G71" s="34" t="n">
-        <v>-10198.24</v>
+        <v>-49656.65</v>
       </c>
       <c r="H71" s="34" t="n">
-        <v>13368.58</v>
+        <v>50837.01</v>
       </c>
       <c r="I71" s="34" t="n">
-        <v>34717.31</v>
+        <v>141996.99</v>
       </c>
       <c r="J71" s="34" t="n">
-        <v>-57368.52</v>
+        <v>-206425.01</v>
       </c>
       <c r="K71" s="35" t="n">
-        <v>-19480.87</v>
+        <v>-63247.66</v>
       </c>
       <c r="L71" s="34" t="n">
-        <v>-445.95</v>
+        <v>-4815.46</v>
       </c>
       <c r="M71" s="34" t="n">
-        <v>-11399.12</v>
+        <v>-46346.97</v>
       </c>
       <c r="N71" s="34" t="n">
-        <v>3886.5</v>
+        <v>13619.47</v>
       </c>
       <c r="O71" s="34" t="n">
-        <v>-9975.280000000001</v>
+        <v>-119343.61</v>
       </c>
       <c r="P71" s="35" t="n">
-        <v>-17933.85</v>
+        <v>-156886.57</v>
       </c>
       <c r="Q71" s="34" t="n">
-        <v>1165.49</v>
+        <v>3302.06</v>
       </c>
       <c r="R71" s="34" t="n">
-        <v>6662.5</v>
+        <v>35591.29</v>
       </c>
       <c r="S71" s="34" t="n">
-        <v>237.49</v>
+        <v>2841.83</v>
       </c>
       <c r="T71" s="34" t="n">
-        <v>24894</v>
+        <v>104472.65</v>
       </c>
       <c r="U71" s="35" t="n">
-        <v>32959.48</v>
+        <v>146207.83</v>
       </c>
       <c r="V71" s="34" t="n">
-        <v>8113.35</v>
+        <v>59810.7</v>
       </c>
       <c r="W71" s="34" t="n">
-        <v>2685.97</v>
+        <v>27894.84</v>
       </c>
       <c r="X71" s="36" t="n">
-        <v>47936.06</v>
+        <v>230778.08</v>
       </c>
       <c r="Y71" s="10" t="n"/>
       <c r="Z71" s="11" t="n"/>
@@ -16512,66 +16479,66 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E72" s="34" t="n">
-        <v>-78366.22</v>
+        <v>-24812.81</v>
       </c>
       <c r="F72" s="9" t="n"/>
       <c r="G72" s="34" t="n">
-        <v>-39458.41</v>
+        <v>-10198.24</v>
       </c>
       <c r="H72" s="34" t="n">
-        <v>37468.43</v>
+        <v>13368.58</v>
       </c>
       <c r="I72" s="34" t="n">
-        <v>107279.69</v>
+        <v>34717.31</v>
       </c>
       <c r="J72" s="34" t="n">
-        <v>-149056.49</v>
+        <v>-57368.52</v>
       </c>
       <c r="K72" s="35" t="n">
-        <v>-43766.78</v>
+        <v>-19480.87</v>
       </c>
       <c r="L72" s="34" t="n">
-        <v>-4369.51</v>
+        <v>-445.95</v>
       </c>
       <c r="M72" s="34" t="n">
-        <v>-34947.84</v>
+        <v>-11399.12</v>
       </c>
       <c r="N72" s="34" t="n">
-        <v>9732.969999999999</v>
+        <v>3886.5</v>
       </c>
       <c r="O72" s="34" t="n">
-        <v>-109368.33</v>
+        <v>-9975.280000000001</v>
       </c>
       <c r="P72" s="35" t="n">
-        <v>-138952.71</v>
+        <v>-17933.85</v>
       </c>
       <c r="Q72" s="34" t="n">
-        <v>2136.57</v>
+        <v>1165.49</v>
       </c>
       <c r="R72" s="34" t="n">
-        <v>28928.79</v>
+        <v>6662.5</v>
       </c>
       <c r="S72" s="34" t="n">
-        <v>2604.35</v>
+        <v>237.49</v>
       </c>
       <c r="T72" s="34" t="n">
-        <v>79578.64</v>
+        <v>24894</v>
       </c>
       <c r="U72" s="35" t="n">
-        <v>113248.35</v>
+        <v>32959.48</v>
       </c>
       <c r="V72" s="34" t="n">
-        <v>51697.35</v>
+        <v>8113.35</v>
       </c>
       <c r="W72" s="34" t="n">
-        <v>25208.87</v>
+        <v>2685.97</v>
       </c>
       <c r="X72" s="36" t="n">
-        <v>182842.03</v>
+        <v>47936.06</v>
       </c>
       <c r="Y72" s="10" t="n"/>
       <c r="Z72" s="11" t="n"/>
@@ -16597,66 +16564,66 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E73" s="34" t="n">
-        <v>-85841.95</v>
+        <v>-78366.22</v>
       </c>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="34" t="n">
-        <v>-33607.76</v>
+        <v>-39458.41</v>
       </c>
       <c r="H73" s="34" t="n">
-        <v>43063.65</v>
+        <v>37468.43</v>
       </c>
       <c r="I73" s="34" t="n">
-        <v>116987.24</v>
+        <v>107279.69</v>
       </c>
       <c r="J73" s="34" t="n">
-        <v>-151845.84</v>
+        <v>-149056.49</v>
       </c>
       <c r="K73" s="35" t="n">
-        <v>-25402.71</v>
+        <v>-43766.78</v>
       </c>
       <c r="L73" s="34" t="n">
-        <v>-1773.34</v>
+        <v>-4369.51</v>
       </c>
       <c r="M73" s="34" t="n">
-        <v>-34249.21</v>
+        <v>-34947.84</v>
       </c>
       <c r="N73" s="34" t="n">
-        <v>12135.61</v>
+        <v>9732.969999999999</v>
       </c>
       <c r="O73" s="34" t="n">
-        <v>-136163.58</v>
+        <v>-109368.33</v>
       </c>
       <c r="P73" s="35" t="n">
-        <v>-160050.52</v>
+        <v>-138952.71</v>
       </c>
       <c r="Q73" s="34" t="n">
-        <v>6592.48</v>
+        <v>2136.57</v>
       </c>
       <c r="R73" s="34" t="n">
-        <v>31914.81</v>
+        <v>28928.79</v>
       </c>
       <c r="S73" s="34" t="n">
-        <v>-2695.38</v>
+        <v>2604.35</v>
       </c>
       <c r="T73" s="34" t="n">
-        <v>56741.83</v>
+        <v>79578.64</v>
       </c>
       <c r="U73" s="35" t="n">
-        <v>92553.74000000001</v>
+        <v>113248.35</v>
       </c>
       <c r="V73" s="34" t="n">
-        <v>51457.82</v>
+        <v>51697.35</v>
       </c>
       <c r="W73" s="34" t="n">
-        <v>69514.88</v>
+        <v>25208.87</v>
       </c>
       <c r="X73" s="36" t="n">
-        <v>187199.9</v>
+        <v>182842.03</v>
       </c>
       <c r="Y73" s="10" t="n"/>
       <c r="Z73" s="11" t="n"/>
@@ -16682,66 +16649,66 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="E74" s="34" t="n">
-        <v>-79240.08</v>
+        <v>-85841.95</v>
       </c>
       <c r="F74" s="9" t="n"/>
       <c r="G74" s="34" t="n">
-        <v>-41229.95</v>
+        <v>-33607.76</v>
       </c>
       <c r="H74" s="34" t="n">
-        <v>40110.16</v>
+        <v>43063.65</v>
       </c>
       <c r="I74" s="34" t="n">
-        <v>107279.35</v>
+        <v>116987.24</v>
       </c>
       <c r="J74" s="34" t="n">
-        <v>-150740.68</v>
+        <v>-151845.84</v>
       </c>
       <c r="K74" s="35" t="n">
-        <v>-44581.12</v>
+        <v>-25402.71</v>
       </c>
       <c r="L74" s="34" t="n">
-        <v>-4516.24</v>
+        <v>-1773.34</v>
       </c>
       <c r="M74" s="34" t="n">
-        <v>-37006.41</v>
+        <v>-34249.21</v>
       </c>
       <c r="N74" s="34" t="n">
-        <v>9302.52</v>
+        <v>12135.61</v>
       </c>
       <c r="O74" s="34" t="n">
-        <v>-110719</v>
+        <v>-136163.58</v>
       </c>
       <c r="P74" s="35" t="n">
-        <v>-142939.13</v>
+        <v>-160050.52</v>
       </c>
       <c r="Q74" s="34" t="n">
-        <v>1859.49</v>
+        <v>6592.48</v>
       </c>
       <c r="R74" s="34" t="n">
-        <v>27372.69</v>
+        <v>31914.81</v>
       </c>
       <c r="S74" s="34" t="n">
-        <v>-168.22</v>
+        <v>-2695.38</v>
       </c>
       <c r="T74" s="34" t="n">
-        <v>76465.67999999999</v>
+        <v>56741.83</v>
       </c>
       <c r="U74" s="35" t="n">
-        <v>105529.64</v>
+        <v>92553.74000000001</v>
       </c>
       <c r="V74" s="34" t="n">
-        <v>49003.03</v>
+        <v>51457.82</v>
       </c>
       <c r="W74" s="34" t="n">
-        <v>22253.22</v>
+        <v>69514.88</v>
       </c>
       <c r="X74" s="36" t="n">
-        <v>180549.41</v>
+        <v>187199.9</v>
       </c>
       <c r="Y74" s="10" t="n"/>
       <c r="Z74" s="11" t="n"/>
@@ -16767,66 +16734,66 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>(비지배주주지분)당기순이익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E75" s="34" t="n">
-        <v>873.87</v>
+        <v>-79240.08</v>
       </c>
       <c r="F75" s="9" t="n"/>
       <c r="G75" s="34" t="n">
-        <v>1771.54</v>
+        <v>-41229.95</v>
       </c>
       <c r="H75" s="34" t="n">
-        <v>-2641.73</v>
+        <v>40110.16</v>
       </c>
       <c r="I75" s="34" t="n">
-        <v>0.34</v>
+        <v>107279.35</v>
       </c>
       <c r="J75" s="34" t="n">
-        <v>1684.2</v>
+        <v>-150740.68</v>
       </c>
       <c r="K75" s="35" t="n">
-        <v>814.35</v>
+        <v>-44581.12</v>
       </c>
       <c r="L75" s="34" t="n">
-        <v>146.73</v>
+        <v>-4516.24</v>
       </c>
       <c r="M75" s="34" t="n">
-        <v>2058.57</v>
+        <v>-37006.41</v>
       </c>
       <c r="N75" s="34" t="n">
-        <v>430.45</v>
+        <v>9302.52</v>
       </c>
       <c r="O75" s="34" t="n">
-        <v>1350.67</v>
+        <v>-110719</v>
       </c>
       <c r="P75" s="35" t="n">
-        <v>3986.42</v>
+        <v>-142939.13</v>
       </c>
       <c r="Q75" s="34" t="n">
-        <v>277.08</v>
+        <v>1859.49</v>
       </c>
       <c r="R75" s="34" t="n">
-        <v>1556.1</v>
+        <v>27372.69</v>
       </c>
       <c r="S75" s="34" t="n">
-        <v>2772.57</v>
+        <v>-168.22</v>
       </c>
       <c r="T75" s="34" t="n">
-        <v>3112.97</v>
+        <v>76465.67999999999</v>
       </c>
       <c r="U75" s="35" t="n">
-        <v>7718.72</v>
+        <v>105529.64</v>
       </c>
       <c r="V75" s="34" t="n">
-        <v>2694.33</v>
+        <v>49003.03</v>
       </c>
       <c r="W75" s="34" t="n">
-        <v>2955.64</v>
+        <v>22253.22</v>
       </c>
       <c r="X75" s="36" t="n">
-        <v>2292.62</v>
+        <v>180549.41</v>
       </c>
       <c r="Y75" s="10" t="n"/>
       <c r="Z75" s="11" t="n"/>
@@ -16852,66 +16819,66 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>(비지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E76" s="34" t="n">
-        <v>-3265.06</v>
+        <v>873.87</v>
       </c>
       <c r="F76" s="9" t="n"/>
       <c r="G76" s="34" t="n">
-        <v>-13061.88</v>
+        <v>1771.54</v>
       </c>
       <c r="H76" s="34" t="n">
-        <v>-91160.71000000001</v>
+        <v>-2641.73</v>
       </c>
       <c r="I76" s="34" t="n">
-        <v>-128374.15</v>
+        <v>0.34</v>
       </c>
       <c r="J76" s="34" t="n">
-        <v>155046.13</v>
+        <v>1684.2</v>
       </c>
       <c r="K76" s="35" t="n">
-        <v>-77550.61</v>
+        <v>814.35</v>
       </c>
       <c r="L76" s="34" t="n">
-        <v>-36236.48</v>
+        <v>146.73</v>
       </c>
       <c r="M76" s="34" t="n">
-        <v>-6302.92</v>
+        <v>2058.57</v>
       </c>
       <c r="N76" s="34" t="n">
-        <v>-63500.07</v>
+        <v>430.45</v>
       </c>
       <c r="O76" s="34" t="n">
-        <v>42282.92</v>
+        <v>1350.67</v>
       </c>
       <c r="P76" s="35" t="n">
-        <v>-63756.55</v>
+        <v>3986.42</v>
       </c>
       <c r="Q76" s="34" t="n">
-        <v>-79618.97</v>
+        <v>277.08</v>
       </c>
       <c r="R76" s="34" t="n">
-        <v>-80121.92</v>
+        <v>1556.1</v>
       </c>
       <c r="S76" s="34" t="n">
-        <v>83125.89</v>
+        <v>2772.57</v>
       </c>
       <c r="T76" s="34" t="n">
-        <v>-276960.09</v>
+        <v>3112.97</v>
       </c>
       <c r="U76" s="35" t="n">
-        <v>-353575.09</v>
+        <v>7718.72</v>
       </c>
       <c r="V76" s="34" t="n">
-        <v>-27553.91</v>
+        <v>2694.33</v>
       </c>
       <c r="W76" s="34" t="n">
-        <v>187000.27</v>
+        <v>2955.64</v>
       </c>
       <c r="X76" s="36" t="n">
-        <v>-99556.32000000001</v>
+        <v>2292.62</v>
       </c>
       <c r="Y76" s="10" t="n"/>
       <c r="Z76" s="11" t="n"/>
@@ -16937,66 +16904,66 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="E77" s="34" t="n">
-        <v>-22907.09</v>
+        <v>-3265.06</v>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="34" t="n">
-        <v>25240.25</v>
+        <v>-13061.88</v>
       </c>
       <c r="H77" s="34" t="n">
-        <v>148598.49</v>
+        <v>-91160.71000000001</v>
       </c>
       <c r="I77" s="34" t="n">
-        <v>256302.8</v>
+        <v>-128374.15</v>
       </c>
       <c r="J77" s="34" t="n">
-        <v>-306772.47</v>
+        <v>155046.13</v>
       </c>
       <c r="K77" s="35" t="n">
-        <v>123369.07</v>
+        <v>-77550.61</v>
       </c>
       <c r="L77" s="34" t="n">
-        <v>58833.75</v>
+        <v>-36236.48</v>
       </c>
       <c r="M77" s="34" t="n">
-        <v>12423.9</v>
+        <v>-6302.92</v>
       </c>
       <c r="N77" s="34" t="n">
-        <v>84975.82000000001</v>
+        <v>-63500.07</v>
       </c>
       <c r="O77" s="34" t="n">
-        <v>-96447.14</v>
+        <v>42282.92</v>
       </c>
       <c r="P77" s="35" t="n">
-        <v>59786.33</v>
+        <v>-63756.55</v>
       </c>
       <c r="Q77" s="34" t="n">
-        <v>93965.00999999999</v>
+        <v>-79618.97</v>
       </c>
       <c r="R77" s="34" t="n">
-        <v>98288.81</v>
+        <v>-80121.92</v>
       </c>
       <c r="S77" s="34" t="n">
-        <v>-115534.36</v>
+        <v>83125.89</v>
       </c>
       <c r="T77" s="34" t="n">
-        <v>334535.57</v>
+        <v>-276960.09</v>
       </c>
       <c r="U77" s="35" t="n">
-        <v>411255.03</v>
+        <v>-353575.09</v>
       </c>
       <c r="V77" s="34" t="n">
-        <v>18880.53</v>
+        <v>-27553.91</v>
       </c>
       <c r="W77" s="34" t="n">
-        <v>-248524.65</v>
+        <v>187000.27</v>
       </c>
       <c r="X77" s="36" t="n">
-        <v>129526.97</v>
+        <v>-99556.32000000001</v>
       </c>
       <c r="Y77" s="10" t="n"/>
       <c r="Z77" s="11" t="n"/>
@@ -17022,66 +16989,66 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E78" s="34" t="n">
-        <v>-78366.22</v>
+        <v>-22907.09</v>
       </c>
       <c r="F78" s="9" t="n"/>
       <c r="G78" s="34" t="n">
-        <v>-39458.41</v>
+        <v>25240.25</v>
       </c>
       <c r="H78" s="34" t="n">
-        <v>37468.43</v>
+        <v>148598.49</v>
       </c>
       <c r="I78" s="34" t="n">
-        <v>107279.69</v>
+        <v>256302.8</v>
       </c>
       <c r="J78" s="34" t="n">
-        <v>-149056.49</v>
+        <v>-306772.47</v>
       </c>
       <c r="K78" s="35" t="n">
-        <v>-43766.78</v>
+        <v>123369.07</v>
       </c>
       <c r="L78" s="34" t="n">
-        <v>-4369.51</v>
+        <v>58833.75</v>
       </c>
       <c r="M78" s="34" t="n">
-        <v>-34947.84</v>
+        <v>12423.9</v>
       </c>
       <c r="N78" s="34" t="n">
-        <v>9732.969999999999</v>
+        <v>84975.82000000001</v>
       </c>
       <c r="O78" s="34" t="n">
-        <v>-109368.33</v>
+        <v>-96447.14</v>
       </c>
       <c r="P78" s="35" t="n">
-        <v>-138952.71</v>
+        <v>59786.33</v>
       </c>
       <c r="Q78" s="34" t="n">
-        <v>2136.57</v>
+        <v>93965.00999999999</v>
       </c>
       <c r="R78" s="34" t="n">
-        <v>28928.79</v>
+        <v>98288.81</v>
       </c>
       <c r="S78" s="34" t="n">
-        <v>2604.35</v>
+        <v>-115534.36</v>
       </c>
       <c r="T78" s="34" t="n">
-        <v>79578.64</v>
+        <v>334535.57</v>
       </c>
       <c r="U78" s="35" t="n">
-        <v>113248.35</v>
+        <v>411255.03</v>
       </c>
       <c r="V78" s="34" t="n">
-        <v>51697.35</v>
+        <v>18880.53</v>
       </c>
       <c r="W78" s="34" t="n">
-        <v>25208.87</v>
+        <v>-248524.65</v>
       </c>
       <c r="X78" s="36" t="n">
-        <v>182842.03</v>
+        <v>129526.97</v>
       </c>
       <c r="Y78" s="10" t="n"/>
       <c r="Z78" s="11" t="n"/>
@@ -17107,63 +17074,66 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>이자수익</t>
-        </is>
+          <t>계속사업이익</t>
+        </is>
+      </c>
+      <c r="E79" s="34" t="n">
+        <v>-78366.22</v>
       </c>
       <c r="F79" s="9" t="n"/>
       <c r="G79" s="34" t="n">
-        <v>1721</v>
+        <v>-39458.41</v>
       </c>
       <c r="H79" s="34" t="n">
-        <v>2717</v>
+        <v>37468.43</v>
       </c>
       <c r="I79" s="34" t="n">
-        <v>4028</v>
+        <v>107279.69</v>
       </c>
       <c r="J79" s="34" t="n">
-        <v>5073</v>
+        <v>-149056.49</v>
       </c>
       <c r="K79" s="35" t="n">
-        <v>13539</v>
+        <v>-43766.78</v>
       </c>
       <c r="L79" s="34" t="n">
-        <v>4039</v>
+        <v>-4369.51</v>
       </c>
       <c r="M79" s="34" t="n">
-        <v>3835</v>
+        <v>-34947.84</v>
       </c>
       <c r="N79" s="34" t="n">
-        <v>3965</v>
+        <v>9732.969999999999</v>
       </c>
       <c r="O79" s="34" t="n">
-        <v>4081</v>
+        <v>-109368.33</v>
       </c>
       <c r="P79" s="35" t="n">
-        <v>15920</v>
+        <v>-138952.71</v>
       </c>
       <c r="Q79" s="34" t="n">
-        <v>4357</v>
+        <v>2136.57</v>
       </c>
       <c r="R79" s="34" t="n">
-        <v>3987</v>
+        <v>28928.79</v>
       </c>
       <c r="S79" s="34" t="n">
-        <v>4372</v>
+        <v>2604.35</v>
       </c>
       <c r="T79" s="34" t="n">
-        <v>3542</v>
+        <v>79578.64</v>
       </c>
       <c r="U79" s="35" t="n">
-        <v>16258</v>
+        <v>113248.35</v>
       </c>
       <c r="V79" s="34" t="n">
-        <v>2662</v>
+        <v>51697.35</v>
       </c>
       <c r="W79" s="34" t="n">
-        <v>3356</v>
+        <v>25208.87</v>
       </c>
       <c r="X79" s="36" t="n">
-        <v>4295</v>
+        <v>182842.03</v>
       </c>
       <c r="Y79" s="10" t="n"/>
       <c r="Z79" s="11" t="n"/>
@@ -17189,63 +17159,63 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>배당금수익</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="F80" s="9" t="n"/>
       <c r="G80" s="34" t="n">
-        <v>37</v>
+        <v>1721</v>
       </c>
       <c r="H80" s="34" t="n">
-        <v>0</v>
+        <v>2717</v>
       </c>
       <c r="I80" s="34" t="n">
-        <v>0</v>
+        <v>4028</v>
       </c>
       <c r="J80" s="34" t="n">
-        <v>0</v>
+        <v>5073</v>
       </c>
       <c r="K80" s="35" t="n">
-        <v>37</v>
+        <v>13539</v>
       </c>
       <c r="L80" s="34" t="n">
-        <v>42</v>
+        <v>4039</v>
       </c>
       <c r="M80" s="34" t="n">
-        <v>0</v>
+        <v>3835</v>
       </c>
       <c r="N80" s="34" t="n">
-        <v>0</v>
+        <v>3965</v>
       </c>
       <c r="O80" s="34" t="n">
-        <v>0</v>
+        <v>4081</v>
       </c>
       <c r="P80" s="35" t="n">
-        <v>42</v>
+        <v>15920</v>
       </c>
       <c r="Q80" s="34" t="n">
-        <v>62</v>
+        <v>4357</v>
       </c>
       <c r="R80" s="34" t="n">
-        <v>0</v>
+        <v>3987</v>
       </c>
       <c r="S80" s="34" t="n">
-        <v>0</v>
+        <v>4372</v>
       </c>
       <c r="T80" s="34" t="n">
-        <v>0</v>
+        <v>3542</v>
       </c>
       <c r="U80" s="35" t="n">
-        <v>62</v>
+        <v>16258</v>
       </c>
       <c r="V80" s="34" t="n">
-        <v>62</v>
+        <v>2662</v>
       </c>
       <c r="W80" s="34" t="n">
-        <v>0</v>
+        <v>3356</v>
       </c>
       <c r="X80" s="36" t="n">
-        <v>0</v>
+        <v>4295</v>
       </c>
       <c r="Y80" s="10" t="n"/>
       <c r="Z80" s="11" t="n"/>
@@ -17271,63 +17241,63 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="F81" s="9" t="n"/>
       <c r="G81" s="34" t="n">
-        <v>821</v>
+        <v>37</v>
       </c>
       <c r="H81" s="34" t="n">
-        <v>1213</v>
+        <v>0</v>
       </c>
       <c r="I81" s="34" t="n">
-        <v>1509</v>
+        <v>0</v>
       </c>
       <c r="J81" s="34" t="n">
-        <v>1518</v>
+        <v>0</v>
       </c>
       <c r="K81" s="35" t="n">
-        <v>5061</v>
+        <v>37</v>
       </c>
       <c r="L81" s="34" t="n">
-        <v>1517</v>
+        <v>42</v>
       </c>
       <c r="M81" s="34" t="n">
-        <v>3171</v>
+        <v>0</v>
       </c>
       <c r="N81" s="34" t="n">
-        <v>3949</v>
+        <v>0</v>
       </c>
       <c r="O81" s="34" t="n">
-        <v>5196</v>
+        <v>0</v>
       </c>
       <c r="P81" s="35" t="n">
-        <v>13833</v>
+        <v>42</v>
       </c>
       <c r="Q81" s="34" t="n">
-        <v>6913</v>
+        <v>62</v>
       </c>
       <c r="R81" s="34" t="n">
-        <v>5247</v>
+        <v>0</v>
       </c>
       <c r="S81" s="34" t="n">
-        <v>4547</v>
+        <v>0</v>
       </c>
       <c r="T81" s="34" t="n">
-        <v>2756</v>
+        <v>0</v>
       </c>
       <c r="U81" s="35" t="n">
-        <v>19463</v>
+        <v>62</v>
       </c>
       <c r="V81" s="34" t="n">
-        <v>3218</v>
+        <v>62</v>
       </c>
       <c r="W81" s="34" t="n">
-        <v>945</v>
+        <v>0</v>
       </c>
       <c r="X81" s="36" t="n">
-        <v>1136</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="10" t="n"/>
       <c r="Z81" s="11" t="n"/>
@@ -17353,63 +17323,63 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>외환차익</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="F82" s="9" t="n"/>
       <c r="G82" s="34" t="n">
-        <v>38996</v>
+        <v>821</v>
       </c>
       <c r="H82" s="34" t="n">
-        <v>58814</v>
+        <v>1213</v>
       </c>
       <c r="I82" s="34" t="n">
-        <v>86354</v>
+        <v>1509</v>
       </c>
       <c r="J82" s="34" t="n">
-        <v>87300</v>
+        <v>1518</v>
       </c>
       <c r="K82" s="35" t="n">
-        <v>271464</v>
+        <v>5061</v>
       </c>
       <c r="L82" s="34" t="n">
-        <v>52556</v>
+        <v>1517</v>
       </c>
       <c r="M82" s="34" t="n">
-        <v>46704</v>
+        <v>3171</v>
       </c>
       <c r="N82" s="34" t="n">
-        <v>41098</v>
+        <v>3949</v>
       </c>
       <c r="O82" s="34" t="n">
-        <v>28852</v>
+        <v>5196</v>
       </c>
       <c r="P82" s="35" t="n">
-        <v>169210</v>
+        <v>13833</v>
       </c>
       <c r="Q82" s="34" t="n">
-        <v>55680</v>
+        <v>6913</v>
       </c>
       <c r="R82" s="34" t="n">
-        <v>70776</v>
+        <v>5247</v>
       </c>
       <c r="S82" s="34" t="n">
-        <v>38658</v>
+        <v>4547</v>
       </c>
       <c r="T82" s="34" t="n">
-        <v>49739</v>
+        <v>2756</v>
       </c>
       <c r="U82" s="35" t="n">
-        <v>214853</v>
+        <v>19463</v>
       </c>
       <c r="V82" s="34" t="n">
-        <v>25945</v>
+        <v>3218</v>
       </c>
       <c r="W82" s="34" t="n">
-        <v>42459</v>
+        <v>945</v>
       </c>
       <c r="X82" s="36" t="n">
-        <v>52535</v>
+        <v>1136</v>
       </c>
       <c r="Y82" s="10" t="n"/>
       <c r="Z82" s="11" t="n"/>
@@ -17435,63 +17405,63 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="34" t="n">
-        <v>23277</v>
+        <v>38996</v>
       </c>
       <c r="H83" s="34" t="n">
-        <v>20508</v>
+        <v>58814</v>
       </c>
       <c r="I83" s="34" t="n">
-        <v>18165</v>
+        <v>86354</v>
       </c>
       <c r="J83" s="34" t="n">
-        <v>70742</v>
+        <v>87300</v>
       </c>
       <c r="K83" s="35" t="n">
-        <v>132692</v>
+        <v>271464</v>
       </c>
       <c r="L83" s="34" t="n">
-        <v>38078</v>
+        <v>52556</v>
       </c>
       <c r="M83" s="34" t="n">
-        <v>23420</v>
+        <v>46704</v>
       </c>
       <c r="N83" s="34" t="n">
-        <v>22862</v>
+        <v>41098</v>
       </c>
       <c r="O83" s="34" t="n">
-        <v>34179</v>
+        <v>28852</v>
       </c>
       <c r="P83" s="35" t="n">
-        <v>118539</v>
+        <v>169210</v>
       </c>
       <c r="Q83" s="34" t="n">
-        <v>23076</v>
+        <v>55680</v>
       </c>
       <c r="R83" s="34" t="n">
-        <v>25167</v>
+        <v>70776</v>
       </c>
       <c r="S83" s="34" t="n">
-        <v>48578</v>
+        <v>38658</v>
       </c>
       <c r="T83" s="34" t="n">
-        <v>20919</v>
+        <v>49739</v>
       </c>
       <c r="U83" s="35" t="n">
-        <v>117740</v>
+        <v>214853</v>
       </c>
       <c r="V83" s="34" t="n">
-        <v>32246</v>
+        <v>25945</v>
       </c>
       <c r="W83" s="34" t="n">
-        <v>82351</v>
+        <v>42459</v>
       </c>
       <c r="X83" s="36" t="n">
-        <v>59961</v>
+        <v>52535</v>
       </c>
       <c r="Y83" s="10" t="n"/>
       <c r="Z83" s="11" t="n"/>
@@ -17517,63 +17487,63 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>외화환산이익</t>
+          <t>외환차손</t>
         </is>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="34" t="n">
-        <v>9518</v>
+        <v>23277</v>
       </c>
       <c r="H84" s="34" t="n">
-        <v>42793</v>
+        <v>20508</v>
       </c>
       <c r="I84" s="34" t="n">
-        <v>98762</v>
+        <v>18165</v>
       </c>
       <c r="J84" s="34" t="n">
-        <v>-132785</v>
+        <v>70742</v>
       </c>
       <c r="K84" s="35" t="n">
-        <v>18288</v>
+        <v>132692</v>
       </c>
       <c r="L84" s="34" t="n">
-        <v>34361</v>
+        <v>38078</v>
       </c>
       <c r="M84" s="34" t="n">
-        <v>-12185</v>
+        <v>23420</v>
       </c>
       <c r="N84" s="34" t="n">
-        <v>16611</v>
+        <v>22862</v>
       </c>
       <c r="O84" s="34" t="n">
-        <v>-31125</v>
+        <v>34179</v>
       </c>
       <c r="P84" s="35" t="n">
-        <v>7662</v>
+        <v>118539</v>
       </c>
       <c r="Q84" s="34" t="n">
-        <v>35797</v>
+        <v>23076</v>
       </c>
       <c r="R84" s="34" t="n">
-        <v>0</v>
+        <v>25167</v>
       </c>
       <c r="S84" s="34" t="n">
-        <v>0</v>
+        <v>48578</v>
       </c>
       <c r="T84" s="34" t="n">
-        <v>77825</v>
+        <v>20919</v>
       </c>
       <c r="U84" s="35" t="n">
-        <v>113622</v>
+        <v>117740</v>
       </c>
       <c r="V84" s="34" t="n">
-        <v>9870</v>
+        <v>32246</v>
       </c>
       <c r="W84" s="34" t="n">
-        <v>11049</v>
+        <v>82351</v>
       </c>
       <c r="X84" s="36" t="n">
-        <v>56424</v>
+        <v>59961</v>
       </c>
       <c r="Y84" s="10" t="n"/>
       <c r="Z84" s="11" t="n"/>
@@ -17599,63 +17569,63 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>외화환산손실</t>
+          <t>외화환산이익</t>
         </is>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="34" t="n">
-        <v>6962</v>
+        <v>9518</v>
       </c>
       <c r="H85" s="34" t="n">
-        <v>11922</v>
+        <v>42793</v>
       </c>
       <c r="I85" s="34" t="n">
-        <v>21824</v>
+        <v>98762</v>
       </c>
       <c r="J85" s="34" t="n">
-        <v>56309</v>
+        <v>-132785</v>
       </c>
       <c r="K85" s="35" t="n">
-        <v>97017</v>
+        <v>18288</v>
       </c>
       <c r="L85" s="34" t="n">
-        <v>9266</v>
+        <v>34361</v>
       </c>
       <c r="M85" s="34" t="n">
-        <v>9146</v>
+        <v>-12185</v>
       </c>
       <c r="N85" s="34" t="n">
-        <v>6293</v>
+        <v>16611</v>
       </c>
       <c r="O85" s="34" t="n">
-        <v>17985</v>
+        <v>-31125</v>
       </c>
       <c r="P85" s="35" t="n">
-        <v>42690</v>
+        <v>7662</v>
       </c>
       <c r="Q85" s="34" t="n">
-        <v>10002</v>
+        <v>35797</v>
       </c>
       <c r="R85" s="34" t="n">
-        <v>11048</v>
+        <v>0</v>
       </c>
       <c r="S85" s="34" t="n">
-        <v>38628</v>
+        <v>0</v>
       </c>
       <c r="T85" s="34" t="n">
-        <v>4848</v>
+        <v>77825</v>
       </c>
       <c r="U85" s="35" t="n">
-        <v>64526</v>
+        <v>113622</v>
       </c>
       <c r="V85" s="34" t="n">
-        <v>6229</v>
+        <v>9870</v>
       </c>
       <c r="W85" s="34" t="n">
-        <v>64400</v>
+        <v>11049</v>
       </c>
       <c r="X85" s="36" t="n">
-        <v>0</v>
+        <v>56424</v>
       </c>
       <c r="Y85" s="10" t="n"/>
       <c r="Z85" s="11" t="n"/>
@@ -17681,63 +17651,63 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>파생상품이익</t>
+          <t>외화환산손실</t>
         </is>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="34" t="n">
-        <v>3259</v>
+        <v>6962</v>
       </c>
       <c r="H86" s="34" t="n">
-        <v>232</v>
+        <v>11922</v>
       </c>
       <c r="I86" s="34" t="n">
-        <v>-151</v>
+        <v>21824</v>
       </c>
       <c r="J86" s="34" t="n">
-        <v>55453</v>
+        <v>56309</v>
       </c>
       <c r="K86" s="35" t="n">
-        <v>58793</v>
+        <v>97017</v>
       </c>
       <c r="L86" s="34" t="n">
-        <v>5008</v>
+        <v>9266</v>
       </c>
       <c r="M86" s="34" t="n">
-        <v>7925</v>
+        <v>9146</v>
       </c>
       <c r="N86" s="34" t="n">
-        <v>5051</v>
+        <v>6293</v>
       </c>
       <c r="O86" s="34" t="n">
-        <v>23641</v>
+        <v>17985</v>
       </c>
       <c r="P86" s="35" t="n">
-        <v>41625</v>
+        <v>42690</v>
       </c>
       <c r="Q86" s="34" t="n">
-        <v>836</v>
+        <v>10002</v>
       </c>
       <c r="R86" s="34" t="n">
-        <v>998</v>
+        <v>11048</v>
       </c>
       <c r="S86" s="34" t="n">
-        <v>154816</v>
+        <v>38628</v>
       </c>
       <c r="T86" s="34" t="n">
-        <v>-19934</v>
+        <v>4848</v>
       </c>
       <c r="U86" s="35" t="n">
-        <v>136716</v>
+        <v>64526</v>
       </c>
       <c r="V86" s="34" t="n">
-        <v>6844</v>
+        <v>6229</v>
       </c>
       <c r="W86" s="34" t="n">
-        <v>279207</v>
+        <v>64400</v>
       </c>
       <c r="X86" s="36" t="n">
-        <v>13620</v>
+        <v>0</v>
       </c>
       <c r="Y86" s="10" t="n"/>
       <c r="Z86" s="11" t="n"/>
@@ -17763,63 +17733,63 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>파생상품손실</t>
+          <t>파생상품이익</t>
         </is>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="34" t="n">
-        <v>35670</v>
+        <v>3259</v>
       </c>
       <c r="H87" s="34" t="n">
-        <v>162073</v>
+        <v>232</v>
       </c>
       <c r="I87" s="34" t="n">
-        <v>276020</v>
+        <v>-151</v>
       </c>
       <c r="J87" s="34" t="n">
-        <v>-268575</v>
+        <v>55453</v>
       </c>
       <c r="K87" s="35" t="n">
-        <v>205188</v>
+        <v>58793</v>
       </c>
       <c r="L87" s="34" t="n">
-        <v>83382</v>
+        <v>5008</v>
       </c>
       <c r="M87" s="34" t="n">
-        <v>29030</v>
+        <v>7925</v>
       </c>
       <c r="N87" s="34" t="n">
-        <v>97121</v>
+        <v>5051</v>
       </c>
       <c r="O87" s="34" t="n">
-        <v>-74201</v>
+        <v>23641</v>
       </c>
       <c r="P87" s="35" t="n">
-        <v>135332</v>
+        <v>41625</v>
       </c>
       <c r="Q87" s="34" t="n">
-        <v>136360</v>
+        <v>836</v>
       </c>
       <c r="R87" s="34" t="n">
-        <v>114421</v>
+        <v>998</v>
       </c>
       <c r="S87" s="34" t="n">
-        <v>22967</v>
+        <v>154816</v>
       </c>
       <c r="T87" s="34" t="n">
-        <v>359609</v>
+        <v>-19934</v>
       </c>
       <c r="U87" s="35" t="n">
-        <v>633357</v>
+        <v>136716</v>
       </c>
       <c r="V87" s="34" t="n">
-        <v>31244</v>
+        <v>6844</v>
       </c>
       <c r="W87" s="34" t="n">
-        <v>1374</v>
+        <v>279207</v>
       </c>
       <c r="X87" s="36" t="n">
-        <v>165333</v>
+        <v>13620</v>
       </c>
       <c r="Y87" s="10" t="n"/>
       <c r="Z87" s="11" t="n"/>
@@ -17845,63 +17815,63 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>이자손익</t>
+          <t>파생상품손실</t>
         </is>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="34" t="n">
-        <v>900</v>
+        <v>35670</v>
       </c>
       <c r="H88" s="34" t="n">
-        <v>1504</v>
+        <v>162073</v>
       </c>
       <c r="I88" s="34" t="n">
-        <v>2519</v>
+        <v>276020</v>
       </c>
       <c r="J88" s="34" t="n">
-        <v>3555</v>
+        <v>-268575</v>
       </c>
       <c r="K88" s="35" t="n">
-        <v>8478</v>
+        <v>205188</v>
       </c>
       <c r="L88" s="34" t="n">
-        <v>2522</v>
+        <v>83382</v>
       </c>
       <c r="M88" s="34" t="n">
-        <v>664</v>
+        <v>29030</v>
       </c>
       <c r="N88" s="34" t="n">
-        <v>16</v>
+        <v>97121</v>
       </c>
       <c r="O88" s="34" t="n">
-        <v>-1115</v>
+        <v>-74201</v>
       </c>
       <c r="P88" s="35" t="n">
-        <v>2087</v>
+        <v>135332</v>
       </c>
       <c r="Q88" s="34" t="n">
-        <v>-2556</v>
+        <v>136360</v>
       </c>
       <c r="R88" s="34" t="n">
-        <v>-1260</v>
+        <v>114421</v>
       </c>
       <c r="S88" s="34" t="n">
-        <v>-175</v>
+        <v>22967</v>
       </c>
       <c r="T88" s="34" t="n">
-        <v>786</v>
+        <v>359609</v>
       </c>
       <c r="U88" s="35" t="n">
-        <v>-3205</v>
+        <v>633357</v>
       </c>
       <c r="V88" s="34" t="n">
-        <v>-556</v>
+        <v>31244</v>
       </c>
       <c r="W88" s="34" t="n">
-        <v>2411</v>
+        <v>1374</v>
       </c>
       <c r="X88" s="36" t="n">
-        <v>3159</v>
+        <v>165333</v>
       </c>
       <c r="Y88" s="10" t="n"/>
       <c r="Z88" s="11" t="n"/>
@@ -17927,66 +17897,63 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E89" s="34" t="n">
-        <v>-277126.05</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="34" t="n">
-        <v>170813.3</v>
+        <v>900</v>
       </c>
       <c r="H89" s="34" t="n">
-        <v>104465.44</v>
+        <v>1504</v>
       </c>
       <c r="I89" s="34" t="n">
-        <v>-125000.98</v>
+        <v>2519</v>
       </c>
       <c r="J89" s="34" t="n">
-        <v>58129.01</v>
+        <v>3555</v>
       </c>
       <c r="K89" s="35" t="n">
-        <v>208406.77</v>
+        <v>8478</v>
       </c>
       <c r="L89" s="34" t="n">
-        <v>-188211.1</v>
+        <v>2522</v>
       </c>
       <c r="M89" s="34" t="n">
-        <v>-53555.39</v>
+        <v>664</v>
       </c>
       <c r="N89" s="34" t="n">
-        <v>11244.77</v>
+        <v>16</v>
       </c>
       <c r="O89" s="34" t="n">
-        <v>-302762.84</v>
+        <v>-1115</v>
       </c>
       <c r="P89" s="35" t="n">
-        <v>-533284.5600000001</v>
+        <v>2087</v>
       </c>
       <c r="Q89" s="34" t="n">
-        <v>273016.62</v>
+        <v>-2556</v>
       </c>
       <c r="R89" s="34" t="n">
-        <v>173229.52</v>
+        <v>-1260</v>
       </c>
       <c r="S89" s="34" t="n">
-        <v>177754.72</v>
+        <v>-175</v>
       </c>
       <c r="T89" s="34" t="n">
-        <v>-263100.88</v>
+        <v>786</v>
       </c>
       <c r="U89" s="35" t="n">
-        <v>360899.98</v>
+        <v>-3205</v>
       </c>
       <c r="V89" s="34" t="n">
-        <v>373397.19</v>
+        <v>-556</v>
       </c>
       <c r="W89" s="34" t="n">
-        <v>185990.07</v>
+        <v>2411</v>
       </c>
       <c r="X89" s="36" t="n">
-        <v>33364.41</v>
+        <v>3159</v>
       </c>
       <c r="Y89" s="10" t="n"/>
       <c r="Z89" s="11" t="n"/>
@@ -18012,66 +17979,66 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E90" s="34" t="n">
-        <v>4282.45</v>
+        <v>-277126.05</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="34" t="n">
-        <v>1706.76</v>
+        <v>170813.3</v>
       </c>
       <c r="H90" s="34" t="n">
-        <v>2481.35</v>
+        <v>104465.44</v>
       </c>
       <c r="I90" s="34" t="n">
-        <v>3695.38</v>
+        <v>-125000.98</v>
       </c>
       <c r="J90" s="34" t="n">
-        <v>5564.86</v>
+        <v>58129.01</v>
       </c>
       <c r="K90" s="35" t="n">
-        <v>13448.35</v>
+        <v>208406.77</v>
       </c>
       <c r="L90" s="34" t="n">
-        <v>4357.71</v>
+        <v>-188211.1</v>
       </c>
       <c r="M90" s="34" t="n">
-        <v>3827.73</v>
+        <v>-53555.39</v>
       </c>
       <c r="N90" s="34" t="n">
-        <v>3783.54</v>
+        <v>11244.77</v>
       </c>
       <c r="O90" s="34" t="n">
-        <v>4127.83</v>
+        <v>-302762.84</v>
       </c>
       <c r="P90" s="35" t="n">
-        <v>16096.81</v>
+        <v>-533284.5600000001</v>
       </c>
       <c r="Q90" s="34" t="n">
-        <v>4101.74</v>
+        <v>273016.62</v>
       </c>
       <c r="R90" s="34" t="n">
-        <v>4261.59</v>
+        <v>173229.52</v>
       </c>
       <c r="S90" s="34" t="n">
-        <v>4566.95</v>
+        <v>177754.72</v>
       </c>
       <c r="T90" s="34" t="n">
-        <v>3566.37</v>
+        <v>-263100.88</v>
       </c>
       <c r="U90" s="35" t="n">
-        <v>16496.65</v>
+        <v>360899.98</v>
       </c>
       <c r="V90" s="34" t="n">
-        <v>2607.4</v>
+        <v>373397.19</v>
       </c>
       <c r="W90" s="34" t="n">
-        <v>3185.5</v>
+        <v>185990.07</v>
       </c>
       <c r="X90" s="36" t="n">
-        <v>4529.74</v>
+        <v>33364.41</v>
       </c>
       <c r="Y90" s="10" t="n"/>
       <c r="Z90" s="11" t="n"/>
@@ -18097,66 +18064,66 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E91" s="34" t="n">
-        <v>-794.54</v>
+        <v>4282.45</v>
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="34" t="n">
-        <v>-893.52</v>
+        <v>1706.76</v>
       </c>
       <c r="H91" s="34" t="n">
-        <v>-1319.03</v>
+        <v>2481.35</v>
       </c>
       <c r="I91" s="34" t="n">
-        <v>-1626.76</v>
+        <v>3695.38</v>
       </c>
       <c r="J91" s="34" t="n">
-        <v>-1579.31</v>
+        <v>5564.86</v>
       </c>
       <c r="K91" s="35" t="n">
-        <v>-5418.62</v>
+        <v>13448.35</v>
       </c>
       <c r="L91" s="34" t="n">
-        <v>-1516.71</v>
+        <v>4357.71</v>
       </c>
       <c r="M91" s="34" t="n">
-        <v>-2761.78</v>
+        <v>3827.73</v>
       </c>
       <c r="N91" s="34" t="n">
-        <v>-3720.91</v>
+        <v>3783.54</v>
       </c>
       <c r="O91" s="34" t="n">
-        <v>-4621.86</v>
+        <v>4127.83</v>
       </c>
       <c r="P91" s="35" t="n">
-        <v>-12621.26</v>
+        <v>16096.81</v>
       </c>
       <c r="Q91" s="34" t="n">
-        <v>-7512.68</v>
+        <v>4101.74</v>
       </c>
       <c r="R91" s="34" t="n">
-        <v>-4709.32</v>
+        <v>4261.59</v>
       </c>
       <c r="S91" s="34" t="n">
-        <v>-5689.37</v>
+        <v>4566.95</v>
       </c>
       <c r="T91" s="34" t="n">
-        <v>-2725.01</v>
+        <v>3566.37</v>
       </c>
       <c r="U91" s="35" t="n">
-        <v>-20636.38</v>
+        <v>16496.65</v>
       </c>
       <c r="V91" s="34" t="n">
-        <v>-3253.48</v>
+        <v>2607.4</v>
       </c>
       <c r="W91" s="34" t="n">
-        <v>-980.22</v>
+        <v>3185.5</v>
       </c>
       <c r="X91" s="36" t="n">
-        <v>-1138.26</v>
+        <v>4529.74</v>
       </c>
       <c r="Y91" s="10" t="n"/>
       <c r="Z91" s="11" t="n"/>
@@ -18182,36 +18149,66 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E92" s="34" t="n">
-        <v>0</v>
+        <v>-794.54</v>
       </c>
       <c r="F92" s="9" t="n"/>
+      <c r="G92" s="34" t="n">
+        <v>-893.52</v>
+      </c>
+      <c r="H92" s="34" t="n">
+        <v>-1319.03</v>
+      </c>
       <c r="I92" s="34" t="n">
-        <v>0</v>
+        <v>-1626.76</v>
       </c>
       <c r="J92" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="9" t="n"/>
+        <v>-1579.31</v>
+      </c>
+      <c r="K92" s="35" t="n">
+        <v>-5418.62</v>
+      </c>
+      <c r="L92" s="34" t="n">
+        <v>-1516.71</v>
+      </c>
+      <c r="M92" s="34" t="n">
+        <v>-2761.78</v>
+      </c>
       <c r="N92" s="34" t="n">
-        <v>0</v>
+        <v>-3720.91</v>
       </c>
       <c r="O92" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" s="9" t="n"/>
+        <v>-4621.86</v>
+      </c>
+      <c r="P92" s="35" t="n">
+        <v>-12621.26</v>
+      </c>
+      <c r="Q92" s="34" t="n">
+        <v>-7512.68</v>
+      </c>
+      <c r="R92" s="34" t="n">
+        <v>-4709.32</v>
+      </c>
       <c r="S92" s="34" t="n">
-        <v>0</v>
+        <v>-5689.37</v>
       </c>
       <c r="T92" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" s="9" t="n"/>
+        <v>-2725.01</v>
+      </c>
+      <c r="U92" s="35" t="n">
+        <v>-20636.38</v>
+      </c>
+      <c r="V92" s="34" t="n">
+        <v>-3253.48</v>
+      </c>
+      <c r="W92" s="34" t="n">
+        <v>-980.22</v>
+      </c>
       <c r="X92" s="36" t="n">
-        <v>0</v>
+        <v>-1138.26</v>
       </c>
       <c r="Y92" s="10" t="n"/>
       <c r="Z92" s="11" t="n"/>
@@ -18237,66 +18234,36 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E93" s="34" t="n">
-        <v>998.0599999999999</v>
+        <v>0</v>
       </c>
       <c r="F93" s="9" t="n"/>
-      <c r="G93" s="34" t="n">
-        <v>-708.73</v>
-      </c>
-      <c r="H93" s="34" t="n">
-        <v>134.1</v>
-      </c>
       <c r="I93" s="34" t="n">
-        <v>-855.9</v>
+        <v>0</v>
       </c>
       <c r="J93" s="34" t="n">
-        <v>-754.63</v>
-      </c>
-      <c r="K93" s="35" t="n">
-        <v>-2185.16</v>
-      </c>
-      <c r="L93" s="34" t="n">
-        <v>-1603.51</v>
-      </c>
-      <c r="M93" s="34" t="n">
-        <v>436.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K93" s="9" t="n"/>
       <c r="N93" s="34" t="n">
-        <v>-908.67</v>
+        <v>0</v>
       </c>
       <c r="O93" s="34" t="n">
-        <v>-891.87</v>
-      </c>
-      <c r="P93" s="35" t="n">
-        <v>-2967.87</v>
-      </c>
-      <c r="Q93" s="34" t="n">
-        <v>-769.0599999999999</v>
-      </c>
-      <c r="R93" s="34" t="n">
-        <v>2243.11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P93" s="9" t="n"/>
       <c r="S93" s="34" t="n">
-        <v>-1015.08</v>
+        <v>0</v>
       </c>
       <c r="T93" s="34" t="n">
-        <v>-1671.63</v>
-      </c>
-      <c r="U93" s="35" t="n">
-        <v>-1212.66</v>
-      </c>
-      <c r="V93" s="34" t="n">
-        <v>-2780.83</v>
-      </c>
-      <c r="W93" s="34" t="n">
-        <v>93.31999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U93" s="9" t="n"/>
       <c r="X93" s="36" t="n">
-        <v>-4789.56</v>
+        <v>0</v>
       </c>
       <c r="Y93" s="10" t="n"/>
       <c r="Z93" s="11" t="n"/>
@@ -18322,66 +18289,66 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E94" s="34" t="n">
-        <v>59163.3</v>
+        <v>998.0599999999999</v>
       </c>
       <c r="F94" s="9" t="n"/>
       <c r="G94" s="34" t="n">
-        <v>14323.61</v>
+        <v>-708.73</v>
       </c>
       <c r="H94" s="34" t="n">
-        <v>-122026.47</v>
+        <v>134.1</v>
       </c>
       <c r="I94" s="34" t="n">
-        <v>11195.65</v>
+        <v>-855.9</v>
       </c>
       <c r="J94" s="34" t="n">
-        <v>49239.81</v>
+        <v>-754.63</v>
       </c>
       <c r="K94" s="35" t="n">
-        <v>-47267.4</v>
+        <v>-2185.16</v>
       </c>
       <c r="L94" s="34" t="n">
-        <v>-164.79</v>
+        <v>-1603.51</v>
       </c>
       <c r="M94" s="34" t="n">
-        <v>-41967.79</v>
+        <v>436.18</v>
       </c>
       <c r="N94" s="34" t="n">
-        <v>-41352.56</v>
+        <v>-908.67</v>
       </c>
       <c r="O94" s="34" t="n">
-        <v>-28139.68</v>
+        <v>-891.87</v>
       </c>
       <c r="P94" s="35" t="n">
-        <v>-111624.82</v>
+        <v>-2967.87</v>
       </c>
       <c r="Q94" s="34" t="n">
-        <v>-20168.17</v>
+        <v>-769.0599999999999</v>
       </c>
       <c r="R94" s="34" t="n">
-        <v>-46989.31</v>
+        <v>2243.11</v>
       </c>
       <c r="S94" s="34" t="n">
-        <v>-57535.23</v>
+        <v>-1015.08</v>
       </c>
       <c r="T94" s="34" t="n">
-        <v>-24467.08</v>
+        <v>-1671.63</v>
       </c>
       <c r="U94" s="35" t="n">
-        <v>-149159.79</v>
+        <v>-1212.66</v>
       </c>
       <c r="V94" s="34" t="n">
-        <v>-24053.75</v>
+        <v>-2780.83</v>
       </c>
       <c r="W94" s="34" t="n">
-        <v>-43203.86</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="X94" s="36" t="n">
-        <v>-47602.35</v>
+        <v>-4789.56</v>
       </c>
       <c r="Y94" s="10" t="n"/>
       <c r="Z94" s="11" t="n"/>
@@ -18407,66 +18374,66 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E95" s="34" t="n">
-        <v>81.06999999999999</v>
+        <v>59163.3</v>
       </c>
       <c r="F95" s="9" t="n"/>
       <c r="G95" s="34" t="n">
-        <v>152.44</v>
+        <v>14323.61</v>
       </c>
       <c r="H95" s="34" t="n">
-        <v>144.29</v>
+        <v>-122026.47</v>
       </c>
       <c r="I95" s="34" t="n">
-        <v>379.52</v>
+        <v>11195.65</v>
       </c>
       <c r="J95" s="34" t="n">
-        <v>143.01</v>
+        <v>49239.81</v>
       </c>
       <c r="K95" s="35" t="n">
-        <v>819.26</v>
+        <v>-47267.4</v>
       </c>
       <c r="L95" s="34" t="n">
-        <v>96.27</v>
+        <v>-164.79</v>
       </c>
       <c r="M95" s="34" t="n">
-        <v>156.54</v>
+        <v>-41967.79</v>
       </c>
       <c r="N95" s="34" t="n">
-        <v>1122.85</v>
+        <v>-41352.56</v>
       </c>
       <c r="O95" s="34" t="n">
-        <v>59.91</v>
+        <v>-28139.68</v>
       </c>
       <c r="P95" s="35" t="n">
-        <v>1435.57</v>
+        <v>-111624.82</v>
       </c>
       <c r="Q95" s="34" t="n">
-        <v>21.15</v>
+        <v>-20168.17</v>
       </c>
       <c r="R95" s="34" t="n">
-        <v>56.87</v>
+        <v>-46989.31</v>
       </c>
       <c r="S95" s="34" t="n">
-        <v>57.98</v>
+        <v>-57535.23</v>
       </c>
       <c r="T95" s="34" t="n">
-        <v>100.04</v>
+        <v>-24467.08</v>
       </c>
       <c r="U95" s="35" t="n">
-        <v>236.04</v>
+        <v>-149159.79</v>
       </c>
       <c r="V95" s="34" t="n">
-        <v>75.95</v>
+        <v>-24053.75</v>
       </c>
       <c r="W95" s="34" t="n">
-        <v>32.1</v>
+        <v>-43203.86</v>
       </c>
       <c r="X95" s="36" t="n">
-        <v>155.04</v>
+        <v>-47602.35</v>
       </c>
       <c r="Y95" s="10" t="n"/>
       <c r="Z95" s="11" t="n"/>
@@ -18492,17 +18459,67 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E96" s="34" t="n">
-        <v>300</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="F96" s="9" t="n"/>
-      <c r="K96" s="9" t="n"/>
-      <c r="P96" s="9" t="n"/>
-      <c r="U96" s="9" t="n"/>
-      <c r="X96" s="5" t="n"/>
+      <c r="G96" s="34" t="n">
+        <v>152.44</v>
+      </c>
+      <c r="H96" s="34" t="n">
+        <v>144.29</v>
+      </c>
+      <c r="I96" s="34" t="n">
+        <v>379.52</v>
+      </c>
+      <c r="J96" s="34" t="n">
+        <v>143.01</v>
+      </c>
+      <c r="K96" s="35" t="n">
+        <v>819.26</v>
+      </c>
+      <c r="L96" s="34" t="n">
+        <v>96.27</v>
+      </c>
+      <c r="M96" s="34" t="n">
+        <v>156.54</v>
+      </c>
+      <c r="N96" s="34" t="n">
+        <v>1122.85</v>
+      </c>
+      <c r="O96" s="34" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="P96" s="35" t="n">
+        <v>1435.57</v>
+      </c>
+      <c r="Q96" s="34" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="R96" s="34" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="S96" s="34" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="T96" s="34" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="U96" s="35" t="n">
+        <v>236.04</v>
+      </c>
+      <c r="V96" s="34" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="W96" s="34" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="X96" s="36" t="n">
+        <v>155.04</v>
+      </c>
       <c r="Y96" s="10" t="n"/>
       <c r="Z96" s="11" t="n"/>
       <c r="AA96" s="10" t="n"/>
@@ -18527,67 +18544,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="E97" s="34" t="n">
-        <v>24549.79</v>
+        <v>300</v>
       </c>
       <c r="F97" s="9" t="n"/>
-      <c r="G97" s="34" t="n">
-        <v>25778.59</v>
-      </c>
-      <c r="H97" s="34" t="n">
-        <v>27979.13</v>
-      </c>
-      <c r="I97" s="34" t="n">
-        <v>35363.12</v>
-      </c>
-      <c r="J97" s="34" t="n">
-        <v>24697.17</v>
-      </c>
-      <c r="K97" s="35" t="n">
-        <v>113818.01</v>
-      </c>
-      <c r="L97" s="34" t="n">
-        <v>12709.68</v>
-      </c>
-      <c r="M97" s="34" t="n">
-        <v>36541.6</v>
-      </c>
-      <c r="N97" s="34" t="n">
-        <v>37058.97</v>
-      </c>
-      <c r="O97" s="34" t="n">
-        <v>31051.26</v>
-      </c>
-      <c r="P97" s="35" t="n">
-        <v>117361.51</v>
-      </c>
-      <c r="Q97" s="34" t="n">
-        <v>25245.76</v>
-      </c>
-      <c r="R97" s="34" t="n">
-        <v>40674.65</v>
-      </c>
-      <c r="S97" s="34" t="n">
-        <v>52329.86</v>
-      </c>
-      <c r="T97" s="34" t="n">
-        <v>26366.14</v>
-      </c>
-      <c r="U97" s="35" t="n">
-        <v>144616.41</v>
-      </c>
-      <c r="V97" s="34" t="n">
-        <v>27973.91</v>
-      </c>
-      <c r="W97" s="34" t="n">
-        <v>34297.34</v>
-      </c>
-      <c r="X97" s="36" t="n">
-        <v>42028.58</v>
-      </c>
+      <c r="K97" s="9" t="n"/>
+      <c r="P97" s="9" t="n"/>
+      <c r="U97" s="9" t="n"/>
+      <c r="X97" s="5" t="n"/>
       <c r="Y97" s="10" t="n"/>
       <c r="Z97" s="11" t="n"/>
       <c r="AA97" s="10" t="n"/>
@@ -18612,66 +18579,66 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E98" s="34" t="n">
-        <v>24756.66</v>
+        <v>24549.79</v>
       </c>
       <c r="F98" s="9" t="n"/>
       <c r="G98" s="34" t="n">
-        <v>26483.58</v>
+        <v>25778.59</v>
       </c>
       <c r="H98" s="34" t="n">
-        <v>29160.3</v>
+        <v>27979.13</v>
       </c>
       <c r="I98" s="34" t="n">
-        <v>37179.8</v>
+        <v>35363.12</v>
       </c>
       <c r="J98" s="34" t="n">
-        <v>25944.91</v>
+        <v>24697.17</v>
       </c>
       <c r="K98" s="35" t="n">
-        <v>118768.59</v>
+        <v>113818.01</v>
       </c>
       <c r="L98" s="34" t="n">
-        <v>14294.11</v>
+        <v>12709.68</v>
       </c>
       <c r="M98" s="34" t="n">
-        <v>38862.7</v>
+        <v>36541.6</v>
       </c>
       <c r="N98" s="34" t="n">
-        <v>39913.4</v>
+        <v>37058.97</v>
       </c>
       <c r="O98" s="34" t="n">
-        <v>34557.88</v>
+        <v>31051.26</v>
       </c>
       <c r="P98" s="35" t="n">
-        <v>127628.09</v>
+        <v>117361.51</v>
       </c>
       <c r="Q98" s="34" t="n">
-        <v>25987.84</v>
+        <v>25245.76</v>
       </c>
       <c r="R98" s="34" t="n">
-        <v>42005.73</v>
+        <v>40674.65</v>
       </c>
       <c r="S98" s="34" t="n">
-        <v>53479.73</v>
+        <v>52329.86</v>
       </c>
       <c r="T98" s="34" t="n">
-        <v>29797.7</v>
+        <v>26366.14</v>
       </c>
       <c r="U98" s="35" t="n">
-        <v>151271</v>
+        <v>144616.41</v>
       </c>
       <c r="V98" s="34" t="n">
-        <v>28478.81</v>
+        <v>27973.91</v>
       </c>
       <c r="W98" s="34" t="n">
-        <v>35116.14</v>
+        <v>34297.34</v>
       </c>
       <c r="X98" s="36" t="n">
-        <v>42880.66</v>
+        <v>42028.58</v>
       </c>
       <c r="Y98" s="10" t="n"/>
       <c r="Z98" s="11" t="n"/>
@@ -18697,66 +18664,66 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E99" s="34" t="n">
-        <v>206.87</v>
+        <v>24756.66</v>
       </c>
       <c r="F99" s="9" t="n"/>
       <c r="G99" s="34" t="n">
-        <v>704.99</v>
+        <v>26483.58</v>
       </c>
       <c r="H99" s="34" t="n">
-        <v>1181.17</v>
+        <v>29160.3</v>
       </c>
       <c r="I99" s="34" t="n">
-        <v>1816.68</v>
+        <v>37179.8</v>
       </c>
       <c r="J99" s="34" t="n">
-        <v>1247.74</v>
+        <v>25944.91</v>
       </c>
       <c r="K99" s="35" t="n">
-        <v>4950.58</v>
+        <v>118768.59</v>
       </c>
       <c r="L99" s="34" t="n">
-        <v>1584.43</v>
+        <v>14294.11</v>
       </c>
       <c r="M99" s="34" t="n">
-        <v>2321.1</v>
+        <v>38862.7</v>
       </c>
       <c r="N99" s="34" t="n">
-        <v>2854.43</v>
+        <v>39913.4</v>
       </c>
       <c r="O99" s="34" t="n">
-        <v>3506.62</v>
+        <v>34557.88</v>
       </c>
       <c r="P99" s="35" t="n">
-        <v>10266.58</v>
+        <v>127628.09</v>
       </c>
       <c r="Q99" s="34" t="n">
-        <v>742.08</v>
+        <v>25987.84</v>
       </c>
       <c r="R99" s="34" t="n">
-        <v>1331.08</v>
+        <v>42005.73</v>
       </c>
       <c r="S99" s="34" t="n">
-        <v>1149.87</v>
+        <v>53479.73</v>
       </c>
       <c r="T99" s="34" t="n">
-        <v>3431.56</v>
+        <v>29797.7</v>
       </c>
       <c r="U99" s="35" t="n">
-        <v>6654.59</v>
+        <v>151271</v>
       </c>
       <c r="V99" s="34" t="n">
-        <v>504.9</v>
+        <v>28478.81</v>
       </c>
       <c r="W99" s="34" t="n">
-        <v>818.8</v>
+        <v>35116.14</v>
       </c>
       <c r="X99" s="36" t="n">
-        <v>852.08</v>
+        <v>42880.66</v>
       </c>
       <c r="Y99" s="10" t="n"/>
       <c r="Z99" s="11" t="n"/>
@@ -18782,66 +18749,66 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E100" s="34" t="n">
-        <v>-19803.01</v>
+        <v>206.87</v>
       </c>
       <c r="F100" s="9" t="n"/>
       <c r="G100" s="34" t="n">
-        <v>29459.88</v>
+        <v>704.99</v>
       </c>
       <c r="H100" s="34" t="n">
-        <v>-22849.06</v>
+        <v>1181.17</v>
       </c>
       <c r="I100" s="34" t="n">
-        <v>-41952.08</v>
+        <v>1816.68</v>
       </c>
       <c r="J100" s="34" t="n">
-        <v>-36271.62</v>
+        <v>1247.74</v>
       </c>
       <c r="K100" s="35" t="n">
-        <v>-71612.88</v>
+        <v>4950.58</v>
       </c>
       <c r="L100" s="34" t="n">
-        <v>61195.62</v>
+        <v>1584.43</v>
       </c>
       <c r="M100" s="34" t="n">
-        <v>112168.78</v>
+        <v>2321.1</v>
       </c>
       <c r="N100" s="34" t="n">
-        <v>72702.5</v>
+        <v>2854.43</v>
       </c>
       <c r="O100" s="34" t="n">
-        <v>217579.95</v>
+        <v>3506.62</v>
       </c>
       <c r="P100" s="35" t="n">
-        <v>463646.85</v>
+        <v>10266.58</v>
       </c>
       <c r="Q100" s="34" t="n">
-        <v>-145772.01</v>
+        <v>742.08</v>
       </c>
       <c r="R100" s="34" t="n">
-        <v>-124965.07</v>
+        <v>1331.08</v>
       </c>
       <c r="S100" s="34" t="n">
-        <v>-140452.34</v>
+        <v>1149.87</v>
       </c>
       <c r="T100" s="34" t="n">
-        <v>48048.03</v>
+        <v>3431.56</v>
       </c>
       <c r="U100" s="35" t="n">
-        <v>-363141.39</v>
+        <v>6654.59</v>
       </c>
       <c r="V100" s="34" t="n">
-        <v>-80956.35000000001</v>
+        <v>504.9</v>
       </c>
       <c r="W100" s="34" t="n">
-        <v>-58905.22</v>
+        <v>818.8</v>
       </c>
       <c r="X100" s="36" t="n">
-        <v>-26092.23</v>
+        <v>852.08</v>
       </c>
       <c r="Y100" s="10" t="n"/>
       <c r="Z100" s="11" t="n"/>
@@ -18867,66 +18834,66 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E101" s="34" t="n">
-        <v>488.69</v>
+        <v>-19803.01</v>
       </c>
       <c r="F101" s="9" t="n"/>
       <c r="G101" s="34" t="n">
-        <v>277.53</v>
+        <v>29459.88</v>
       </c>
       <c r="H101" s="34" t="n">
-        <v>292.48</v>
+        <v>-22849.06</v>
       </c>
       <c r="I101" s="34" t="n">
-        <v>478.95</v>
+        <v>-41952.08</v>
       </c>
       <c r="J101" s="34" t="n">
-        <v>460.06</v>
+        <v>-36271.62</v>
       </c>
       <c r="K101" s="35" t="n">
-        <v>1509.02</v>
+        <v>-71612.88</v>
       </c>
       <c r="L101" s="34" t="n">
-        <v>298.33</v>
+        <v>61195.62</v>
       </c>
       <c r="M101" s="34" t="n">
-        <v>369.84</v>
+        <v>112168.78</v>
       </c>
       <c r="N101" s="34" t="n">
-        <v>591.8200000000001</v>
+        <v>72702.5</v>
       </c>
       <c r="O101" s="34" t="n">
-        <v>404.48</v>
+        <v>217579.95</v>
       </c>
       <c r="P101" s="35" t="n">
-        <v>1664.47</v>
+        <v>463646.85</v>
       </c>
       <c r="Q101" s="34" t="n">
-        <v>1671.26</v>
+        <v>-145772.01</v>
       </c>
       <c r="R101" s="34" t="n">
-        <v>1472.54</v>
+        <v>-124965.07</v>
       </c>
       <c r="S101" s="34" t="n">
-        <v>1346.52</v>
+        <v>-140452.34</v>
       </c>
       <c r="T101" s="34" t="n">
-        <v>1299.29</v>
+        <v>48048.03</v>
       </c>
       <c r="U101" s="35" t="n">
-        <v>5789.61</v>
+        <v>-363141.39</v>
       </c>
       <c r="V101" s="34" t="n">
-        <v>956.35</v>
+        <v>-80956.35000000001</v>
       </c>
       <c r="W101" s="34" t="n">
-        <v>1012.32</v>
+        <v>-58905.22</v>
       </c>
       <c r="X101" s="36" t="n">
-        <v>1412.31</v>
+        <v>-26092.23</v>
       </c>
       <c r="Y101" s="10" t="n"/>
       <c r="Z101" s="11" t="n"/>
@@ -18952,66 +18919,66 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>리스부채의상환</t>
         </is>
       </c>
       <c r="E102" s="34" t="n">
-        <v>-237877.95</v>
+        <v>488.69</v>
       </c>
       <c r="F102" s="9" t="n"/>
       <c r="G102" s="34" t="n">
-        <v>215217.07</v>
+        <v>277.53</v>
       </c>
       <c r="H102" s="34" t="n">
-        <v>-37791.11</v>
+        <v>292.48</v>
       </c>
       <c r="I102" s="34" t="n">
-        <v>-151538.89</v>
+        <v>478.95</v>
       </c>
       <c r="J102" s="34" t="n">
-        <v>63885.83</v>
+        <v>460.06</v>
       </c>
       <c r="K102" s="35" t="n">
-        <v>89772.89999999999</v>
+        <v>1509.02</v>
       </c>
       <c r="L102" s="34" t="n">
-        <v>-125351.78</v>
+        <v>298.33</v>
       </c>
       <c r="M102" s="34" t="n">
-        <v>16293.35</v>
+        <v>369.84</v>
       </c>
       <c r="N102" s="34" t="n">
-        <v>43112.89</v>
+        <v>591.8200000000001</v>
       </c>
       <c r="O102" s="34" t="n">
-        <v>-114157.42</v>
+        <v>404.48</v>
       </c>
       <c r="P102" s="35" t="n">
-        <v>-180102.96</v>
+        <v>1664.47</v>
       </c>
       <c r="Q102" s="34" t="n">
-        <v>108171.53</v>
+        <v>1671.26</v>
       </c>
       <c r="R102" s="34" t="n">
-        <v>2781.94</v>
+        <v>1472.54</v>
       </c>
       <c r="S102" s="34" t="n">
-        <v>-24390.76</v>
+        <v>1346.52</v>
       </c>
       <c r="T102" s="34" t="n">
-        <v>-231507.39</v>
+        <v>1299.29</v>
       </c>
       <c r="U102" s="35" t="n">
-        <v>-144944.68</v>
+        <v>5789.61</v>
       </c>
       <c r="V102" s="34" t="n">
-        <v>268913.28</v>
+        <v>956.35</v>
       </c>
       <c r="W102" s="34" t="n">
-        <v>78806.78999999999</v>
+        <v>1012.32</v>
       </c>
       <c r="X102" s="36" t="n">
-        <v>-39252.17</v>
+        <v>1412.31</v>
       </c>
       <c r="Y102" s="10" t="n"/>
       <c r="Z102" s="11" t="n"/>
@@ -19037,7 +19004,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>현금및현금성자산의증감</t>
         </is>
       </c>
       <c r="E103" s="34" t="n">
@@ -19045,7 +19012,7 @@
       </c>
       <c r="F103" s="9" t="n"/>
       <c r="G103" s="34" t="n">
-        <v>615588.03</v>
+        <v>215217.07</v>
       </c>
       <c r="H103" s="34" t="n">
         <v>-37791.11</v>
@@ -19054,13 +19021,13 @@
         <v>-151538.89</v>
       </c>
       <c r="J103" s="34" t="n">
-        <v>63885.82</v>
+        <v>63885.83</v>
       </c>
       <c r="K103" s="35" t="n">
-        <v>490143.85</v>
+        <v>89772.89999999999</v>
       </c>
       <c r="L103" s="34" t="n">
-        <v>364792.08</v>
+        <v>-125351.78</v>
       </c>
       <c r="M103" s="34" t="n">
         <v>16293.35</v>
@@ -19069,16 +19036,16 @@
         <v>43112.89</v>
       </c>
       <c r="O103" s="34" t="n">
-        <v>-114157.43</v>
+        <v>-114157.42</v>
       </c>
       <c r="P103" s="35" t="n">
-        <v>310040.89</v>
+        <v>-180102.96</v>
       </c>
       <c r="Q103" s="34" t="n">
-        <v>418212.43</v>
+        <v>108171.53</v>
       </c>
       <c r="R103" s="34" t="n">
-        <v>2781.93</v>
+        <v>2781.94</v>
       </c>
       <c r="S103" s="34" t="n">
         <v>-24390.76</v>
@@ -19087,10 +19054,10 @@
         <v>-231507.39</v>
       </c>
       <c r="U103" s="35" t="n">
-        <v>165096.21</v>
+        <v>-144944.68</v>
       </c>
       <c r="V103" s="34" t="n">
-        <v>434009.49</v>
+        <v>268913.28</v>
       </c>
       <c r="W103" s="34" t="n">
         <v>78806.78999999999</v>
@@ -19122,15 +19089,66 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>배당금지급</t>
-        </is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E104" s="34" t="n">
+        <v>-237877.95</v>
       </c>
       <c r="F104" s="9" t="n"/>
-      <c r="K104" s="9" t="n"/>
-      <c r="P104" s="9" t="n"/>
-      <c r="U104" s="9" t="n"/>
+      <c r="G104" s="34" t="n">
+        <v>615588.03</v>
+      </c>
+      <c r="H104" s="34" t="n">
+        <v>-37791.11</v>
+      </c>
+      <c r="I104" s="34" t="n">
+        <v>-151538.89</v>
+      </c>
+      <c r="J104" s="34" t="n">
+        <v>63885.82</v>
+      </c>
+      <c r="K104" s="35" t="n">
+        <v>490143.85</v>
+      </c>
+      <c r="L104" s="34" t="n">
+        <v>364792.08</v>
+      </c>
+      <c r="M104" s="34" t="n">
+        <v>16293.35</v>
+      </c>
+      <c r="N104" s="34" t="n">
+        <v>43112.89</v>
+      </c>
+      <c r="O104" s="34" t="n">
+        <v>-114157.43</v>
+      </c>
+      <c r="P104" s="35" t="n">
+        <v>310040.89</v>
+      </c>
+      <c r="Q104" s="34" t="n">
+        <v>418212.43</v>
+      </c>
+      <c r="R104" s="34" t="n">
+        <v>2781.93</v>
+      </c>
+      <c r="S104" s="34" t="n">
+        <v>-24390.76</v>
+      </c>
+      <c r="T104" s="34" t="n">
+        <v>-231507.39</v>
+      </c>
+      <c r="U104" s="35" t="n">
+        <v>165096.21</v>
+      </c>
+      <c r="V104" s="34" t="n">
+        <v>434009.49</v>
+      </c>
+      <c r="W104" s="34" t="n">
+        <v>78806.78999999999</v>
+      </c>
       <c r="X104" s="36" t="n">
-        <v>19144.46</v>
+        <v>-39252.17</v>
       </c>
       <c r="Y104" s="10" t="n"/>
       <c r="Z104" s="11" t="n"/>
@@ -19149,6 +19167,40 @@
       <c r="AM104" s="10" t="n"/>
       <c r="AN104" s="10" t="n"/>
       <c r="AO104" s="11" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="n"/>
+      <c r="K105" s="9" t="n"/>
+      <c r="P105" s="9" t="n"/>
+      <c r="U105" s="9" t="n"/>
+      <c r="X105" s="36" t="n">
+        <v>19144.46</v>
+      </c>
+      <c r="Y105" s="10" t="n"/>
+      <c r="Z105" s="11" t="n"/>
+      <c r="AA105" s="10" t="n"/>
+      <c r="AB105" s="10" t="n"/>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="11" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="11" t="n"/>
+      <c r="AK105" s="10" t="n"/>
+      <c r="AL105" s="10" t="n"/>
+      <c r="AM105" s="10" t="n"/>
+      <c r="AN105" s="10" t="n"/>
+      <c r="AO105" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19409,7 +19461,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -22306,25 +22358,25 @@
         <v>9968.530000000001</v>
       </c>
       <c r="G35" s="34" t="n">
-        <v>1477.57</v>
+        <v>10012.97</v>
       </c>
       <c r="H35" s="34" t="n">
-        <v>1194.33</v>
+        <v>9699.1</v>
       </c>
       <c r="I35" s="34" t="n">
-        <v>1116.17</v>
+        <v>9277.299999999999</v>
       </c>
       <c r="J35" s="34" t="n">
-        <v>1676.15</v>
+        <v>11465.14</v>
       </c>
       <c r="K35" s="35" t="n">
-        <v>1676.15</v>
+        <v>11465.14</v>
       </c>
       <c r="L35" s="34" t="n">
-        <v>1895.6</v>
+        <v>11821.43</v>
       </c>
       <c r="M35" s="34" t="n">
-        <v>1972.52</v>
+        <v>12061.34</v>
       </c>
       <c r="N35" s="34" t="n">
         <v>18112.81</v>
@@ -22984,7 +23036,27 @@
       <c r="F43" s="35" t="n">
         <v>8533.9</v>
       </c>
-      <c r="K43" s="9" t="n"/>
+      <c r="G43" s="34" t="n">
+        <v>8535.4</v>
+      </c>
+      <c r="H43" s="34" t="n">
+        <v>8504.77</v>
+      </c>
+      <c r="I43" s="34" t="n">
+        <v>8161.13</v>
+      </c>
+      <c r="J43" s="34" t="n">
+        <v>9788.99</v>
+      </c>
+      <c r="K43" s="35" t="n">
+        <v>9788.99</v>
+      </c>
+      <c r="L43" s="34" t="n">
+        <v>9925.83</v>
+      </c>
+      <c r="M43" s="34" t="n">
+        <v>10088.82</v>
+      </c>
       <c r="N43" s="34" t="n">
         <v>14324.89</v>
       </c>
@@ -23052,25 +23124,25 @@
         <v>41473.53</v>
       </c>
       <c r="G44" s="34" t="n">
-        <v>30456.02</v>
+        <v>38991.42</v>
       </c>
       <c r="H44" s="34" t="n">
-        <v>81004.24000000001</v>
+        <v>89509.00999999999</v>
       </c>
       <c r="I44" s="34" t="n">
-        <v>174527.51</v>
+        <v>182688.64</v>
       </c>
       <c r="J44" s="34" t="n">
-        <v>44078.8</v>
+        <v>53867.79</v>
       </c>
       <c r="K44" s="35" t="n">
-        <v>44078.8</v>
+        <v>53867.79</v>
       </c>
       <c r="L44" s="34" t="n">
-        <v>46542.5</v>
+        <v>56468.33</v>
       </c>
       <c r="M44" s="34" t="n">
-        <v>44884.86</v>
+        <v>54973.68</v>
       </c>
       <c r="N44" s="34" t="n">
         <v>74530.73</v>

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$105</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$104</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$92</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -5906,35 +5906,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -6025,35 +6025,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6144,35 +6144,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6263,35 +6263,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6382,35 +6382,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6501,35 +6501,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6620,35 +6620,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6739,35 +6739,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="D47" s="33" t="n">
-        <v>0.9354648903175657</v>
+        <v>0.9354648903175656</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO105"/>
+  <dimension ref="A1:AO104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12847,7 +12847,7 @@
         <v>276982.09</v>
       </c>
       <c r="R28" s="34" t="n">
-        <v>160481</v>
+        <v>180481.47</v>
       </c>
       <c r="S28" s="34" t="n">
         <v>94568.63</v>
@@ -12933,6 +12933,9 @@
       <c r="Q29" s="34" t="n">
         <v>276982.09</v>
       </c>
+      <c r="R29" s="34" t="n">
+        <v>180481.47</v>
+      </c>
       <c r="S29" s="34" t="n">
         <v>94568.63</v>
       </c>
@@ -15193,7 +15196,7 @@
         <v>436982.09</v>
       </c>
       <c r="R55" s="34" t="n">
-        <v>320481</v>
+        <v>320481.47</v>
       </c>
       <c r="S55" s="34" t="n">
         <v>174568.63</v>
@@ -15280,7 +15283,7 @@
         <v>-74037.61</v>
       </c>
       <c r="R56" s="34" t="n">
-        <v>-225830.81</v>
+        <v>-225830.34</v>
       </c>
       <c r="S56" s="34" t="n">
         <v>-304288.68</v>
@@ -15594,17 +15597,67 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>유동성장기부채</t>
-        </is>
+          <t>매출액(수익)</t>
+        </is>
+      </c>
+      <c r="E61" s="34" t="n">
+        <v>860545.88</v>
       </c>
       <c r="F61" s="9" t="n"/>
-      <c r="K61" s="9" t="n"/>
-      <c r="P61" s="9" t="n"/>
+      <c r="G61" s="34" t="n">
+        <v>875958.75</v>
+      </c>
+      <c r="H61" s="34" t="n">
+        <v>935436.14</v>
+      </c>
+      <c r="I61" s="34" t="n">
+        <v>882268.5699999999</v>
+      </c>
+      <c r="J61" s="34" t="n">
+        <v>1023197.48</v>
+      </c>
+      <c r="K61" s="35" t="n">
+        <v>3716860.94</v>
+      </c>
+      <c r="L61" s="34" t="n">
+        <v>909161.3</v>
+      </c>
+      <c r="M61" s="34" t="n">
+        <v>1033370.76</v>
+      </c>
+      <c r="N61" s="34" t="n">
+        <v>993800.53</v>
+      </c>
+      <c r="O61" s="34" t="n">
+        <v>1102733.12</v>
+      </c>
+      <c r="P61" s="35" t="n">
+        <v>4039065.71</v>
+      </c>
+      <c r="Q61" s="34" t="n">
+        <v>1000493.63</v>
+      </c>
       <c r="R61" s="34" t="n">
-        <v>20000</v>
-      </c>
-      <c r="U61" s="9" t="n"/>
-      <c r="X61" s="5" t="n"/>
+        <v>1129062.86</v>
+      </c>
+      <c r="S61" s="34" t="n">
+        <v>1077667.04</v>
+      </c>
+      <c r="T61" s="34" t="n">
+        <v>1422825.22</v>
+      </c>
+      <c r="U61" s="35" t="n">
+        <v>4630048.75</v>
+      </c>
+      <c r="V61" s="34" t="n">
+        <v>1183823.02</v>
+      </c>
+      <c r="W61" s="34" t="n">
+        <v>1234448.39</v>
+      </c>
+      <c r="X61" s="36" t="n">
+        <v>1300349.18</v>
+      </c>
       <c r="Y61" s="10" t="n"/>
       <c r="Z61" s="11" t="n"/>
       <c r="AA61" s="10" t="n"/>
@@ -15629,66 +15682,66 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="E62" s="34" t="n">
-        <v>860545.88</v>
+        <v>904118.38</v>
       </c>
       <c r="F62" s="9" t="n"/>
       <c r="G62" s="34" t="n">
-        <v>875958.75</v>
+        <v>910119.27</v>
       </c>
       <c r="H62" s="34" t="n">
-        <v>935436.14</v>
+        <v>912937.13</v>
       </c>
       <c r="I62" s="34" t="n">
-        <v>882268.5699999999</v>
+        <v>837566.97</v>
       </c>
       <c r="J62" s="34" t="n">
-        <v>1023197.48</v>
+        <v>1043382.9</v>
       </c>
       <c r="K62" s="35" t="n">
-        <v>3716860.94</v>
+        <v>3704006.27</v>
       </c>
       <c r="L62" s="34" t="n">
-        <v>909161.3</v>
+        <v>916503.53</v>
       </c>
       <c r="M62" s="34" t="n">
-        <v>1033370.76</v>
+        <v>1055211.06</v>
       </c>
       <c r="N62" s="34" t="n">
-        <v>993800.53</v>
+        <v>968931.1800000001</v>
       </c>
       <c r="O62" s="34" t="n">
-        <v>1102733.12</v>
+        <v>1129092.3</v>
       </c>
       <c r="P62" s="35" t="n">
-        <v>4039065.71</v>
+        <v>4069738.07</v>
       </c>
       <c r="Q62" s="34" t="n">
-        <v>1000493.63</v>
+        <v>973253.53</v>
       </c>
       <c r="R62" s="34" t="n">
-        <v>1129062.86</v>
+        <v>1073429.94</v>
       </c>
       <c r="S62" s="34" t="n">
-        <v>1077667.04</v>
+        <v>1003389.35</v>
       </c>
       <c r="T62" s="34" t="n">
-        <v>1422825.22</v>
+        <v>1332063.89</v>
       </c>
       <c r="U62" s="35" t="n">
-        <v>4630048.75</v>
+        <v>4382136.71</v>
       </c>
       <c r="V62" s="34" t="n">
-        <v>1183823.02</v>
+        <v>1076844.94</v>
       </c>
       <c r="W62" s="34" t="n">
-        <v>1234448.39</v>
+        <v>1101947.64</v>
       </c>
       <c r="X62" s="36" t="n">
-        <v>1300349.18</v>
+        <v>1050007.01</v>
       </c>
       <c r="Y62" s="10" t="n"/>
       <c r="Z62" s="11" t="n"/>
@@ -15714,66 +15767,66 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="E63" s="34" t="n">
-        <v>904118.38</v>
+        <v>-43572.51</v>
       </c>
       <c r="F63" s="9" t="n"/>
       <c r="G63" s="34" t="n">
-        <v>910119.27</v>
+        <v>-34160.52</v>
       </c>
       <c r="H63" s="34" t="n">
-        <v>912937.13</v>
+        <v>22499.01</v>
       </c>
       <c r="I63" s="34" t="n">
-        <v>837566.97</v>
+        <v>44701.59</v>
       </c>
       <c r="J63" s="34" t="n">
-        <v>1043382.9</v>
+        <v>-20185.4</v>
       </c>
       <c r="K63" s="35" t="n">
-        <v>3704006.27</v>
+        <v>12854.68</v>
       </c>
       <c r="L63" s="34" t="n">
-        <v>916503.53</v>
+        <v>-7342.24</v>
       </c>
       <c r="M63" s="34" t="n">
-        <v>1055211.06</v>
+        <v>-21840.3</v>
       </c>
       <c r="N63" s="34" t="n">
-        <v>968931.1800000001</v>
+        <v>24869.35</v>
       </c>
       <c r="O63" s="34" t="n">
-        <v>1129092.3</v>
+        <v>-26359.17</v>
       </c>
       <c r="P63" s="35" t="n">
-        <v>4069738.07</v>
+        <v>-30672.36</v>
       </c>
       <c r="Q63" s="34" t="n">
-        <v>973253.53</v>
+        <v>27240.1</v>
       </c>
       <c r="R63" s="34" t="n">
-        <v>1073429.94</v>
+        <v>55632.92</v>
       </c>
       <c r="S63" s="34" t="n">
-        <v>1003389.35</v>
+        <v>74277.7</v>
       </c>
       <c r="T63" s="34" t="n">
-        <v>1332063.89</v>
+        <v>90761.35000000001</v>
       </c>
       <c r="U63" s="35" t="n">
-        <v>4382136.71</v>
+        <v>247912.07</v>
       </c>
       <c r="V63" s="34" t="n">
-        <v>1076844.94</v>
+        <v>106978.08</v>
       </c>
       <c r="W63" s="34" t="n">
-        <v>1101947.64</v>
+        <v>132500.75</v>
       </c>
       <c r="X63" s="36" t="n">
-        <v>1050007.01</v>
+        <v>250342.17</v>
       </c>
       <c r="Y63" s="10" t="n"/>
       <c r="Z63" s="11" t="n"/>
@@ -15799,66 +15852,66 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="E64" s="34" t="n">
-        <v>-43572.51</v>
+        <v>33434.36</v>
       </c>
       <c r="F64" s="9" t="n"/>
       <c r="G64" s="34" t="n">
-        <v>-34160.52</v>
+        <v>27674.49</v>
       </c>
       <c r="H64" s="34" t="n">
-        <v>22499.01</v>
+        <v>29099.78</v>
       </c>
       <c r="I64" s="34" t="n">
-        <v>44701.59</v>
+        <v>30633.25</v>
       </c>
       <c r="J64" s="34" t="n">
-        <v>-20185.4</v>
+        <v>34513.27</v>
       </c>
       <c r="K64" s="35" t="n">
-        <v>12854.68</v>
+        <v>121920.79</v>
       </c>
       <c r="L64" s="34" t="n">
-        <v>-7342.24</v>
+        <v>20070.5</v>
       </c>
       <c r="M64" s="34" t="n">
-        <v>-21840.3</v>
+        <v>30627.65</v>
       </c>
       <c r="N64" s="34" t="n">
-        <v>24869.35</v>
+        <v>32725.63</v>
       </c>
       <c r="O64" s="34" t="n">
-        <v>-26359.17</v>
+        <v>38820.2</v>
       </c>
       <c r="P64" s="35" t="n">
-        <v>-30672.36</v>
+        <v>122243.98</v>
       </c>
       <c r="Q64" s="34" t="n">
-        <v>27240.1</v>
+        <v>38284.07</v>
       </c>
       <c r="R64" s="34" t="n">
-        <v>55632.92</v>
+        <v>38208.52</v>
       </c>
       <c r="S64" s="34" t="n">
-        <v>74277.7</v>
+        <v>39027.39</v>
       </c>
       <c r="T64" s="34" t="n">
-        <v>90761.35000000001</v>
+        <v>43864.18</v>
       </c>
       <c r="U64" s="35" t="n">
-        <v>247912.07</v>
+        <v>159384.16</v>
       </c>
       <c r="V64" s="34" t="n">
-        <v>106978.08</v>
+        <v>38493.99</v>
       </c>
       <c r="W64" s="34" t="n">
-        <v>132500.75</v>
+        <v>43081.52</v>
       </c>
       <c r="X64" s="36" t="n">
-        <v>250342.17</v>
+        <v>49534.75</v>
       </c>
       <c r="Y64" s="10" t="n"/>
       <c r="Z64" s="11" t="n"/>
@@ -15884,66 +15937,66 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="E65" s="34" t="n">
-        <v>33434.36</v>
+        <v>-77006.86</v>
       </c>
       <c r="F65" s="9" t="n"/>
       <c r="G65" s="34" t="n">
-        <v>27674.49</v>
+        <v>-61835.01</v>
       </c>
       <c r="H65" s="34" t="n">
-        <v>29099.78</v>
+        <v>-6600.78</v>
       </c>
       <c r="I65" s="34" t="n">
-        <v>30633.25</v>
+        <v>14068.34</v>
       </c>
       <c r="J65" s="34" t="n">
-        <v>34513.27</v>
+        <v>-54698.67</v>
       </c>
       <c r="K65" s="35" t="n">
-        <v>121920.79</v>
+        <v>-109066.12</v>
       </c>
       <c r="L65" s="34" t="n">
-        <v>20070.5</v>
+        <v>-27412.73</v>
       </c>
       <c r="M65" s="34" t="n">
-        <v>30627.65</v>
+        <v>-52467.95</v>
       </c>
       <c r="N65" s="34" t="n">
-        <v>32725.63</v>
+        <v>-7856.29</v>
       </c>
       <c r="O65" s="34" t="n">
-        <v>38820.2</v>
+        <v>-65179.38</v>
       </c>
       <c r="P65" s="35" t="n">
-        <v>122243.98</v>
+        <v>-152916.35</v>
       </c>
       <c r="Q65" s="34" t="n">
-        <v>38284.07</v>
+        <v>-11043.97</v>
       </c>
       <c r="R65" s="34" t="n">
-        <v>38208.52</v>
+        <v>17424.4</v>
       </c>
       <c r="S65" s="34" t="n">
-        <v>39027.39</v>
+        <v>35250.31</v>
       </c>
       <c r="T65" s="34" t="n">
-        <v>43864.18</v>
+        <v>46897.16</v>
       </c>
       <c r="U65" s="35" t="n">
-        <v>159384.16</v>
+        <v>88527.89999999999</v>
       </c>
       <c r="V65" s="34" t="n">
-        <v>38493.99</v>
+        <v>68484.09</v>
       </c>
       <c r="W65" s="34" t="n">
-        <v>43081.52</v>
+        <v>89419.23</v>
       </c>
       <c r="X65" s="36" t="n">
-        <v>49534.75</v>
+        <v>200807.42</v>
       </c>
       <c r="Y65" s="10" t="n"/>
       <c r="Z65" s="11" t="n"/>
@@ -15969,66 +16022,66 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="E66" s="34" t="n">
-        <v>-77006.86</v>
+        <v>1195.07</v>
       </c>
       <c r="F66" s="9" t="n"/>
       <c r="G66" s="34" t="n">
-        <v>-61835.01</v>
+        <v>53668.16</v>
       </c>
       <c r="H66" s="34" t="n">
-        <v>-6600.78</v>
+        <v>104555.76</v>
       </c>
       <c r="I66" s="34" t="n">
-        <v>14068.34</v>
+        <v>189143.77</v>
       </c>
       <c r="J66" s="34" t="n">
-        <v>-54698.67</v>
+        <v>15041.13</v>
       </c>
       <c r="K66" s="35" t="n">
-        <v>-109066.12</v>
+        <v>362408.82</v>
       </c>
       <c r="L66" s="34" t="n">
-        <v>-27412.73</v>
+        <v>96006.47</v>
       </c>
       <c r="M66" s="34" t="n">
-        <v>-52467.95</v>
+        <v>58463.62</v>
       </c>
       <c r="N66" s="34" t="n">
-        <v>-7856.29</v>
+        <v>66725.12</v>
       </c>
       <c r="O66" s="34" t="n">
-        <v>-65179.38</v>
+        <v>25449.53</v>
       </c>
       <c r="P66" s="35" t="n">
-        <v>-152916.35</v>
+        <v>246644.74</v>
       </c>
       <c r="Q66" s="34" t="n">
-        <v>-11043.97</v>
+        <v>96732.17999999999</v>
       </c>
       <c r="R66" s="34" t="n">
-        <v>17424.4</v>
+        <v>75761.3</v>
       </c>
       <c r="S66" s="34" t="n">
-        <v>35250.31</v>
+        <v>197846.34</v>
       </c>
       <c r="T66" s="34" t="n">
-        <v>46897.16</v>
+        <v>111172.08</v>
       </c>
       <c r="U66" s="35" t="n">
-        <v>88527.89999999999</v>
+        <v>481511.9</v>
       </c>
       <c r="V66" s="34" t="n">
-        <v>68484.09</v>
+        <v>45383.44</v>
       </c>
       <c r="W66" s="34" t="n">
-        <v>89419.23</v>
+        <v>336070.62</v>
       </c>
       <c r="X66" s="36" t="n">
-        <v>200807.42</v>
+        <v>126873.65</v>
       </c>
       <c r="Y66" s="10" t="n"/>
       <c r="Z66" s="11" t="n"/>
@@ -16054,66 +16107,66 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="E67" s="34" t="n">
-        <v>1195.07</v>
+        <v>4460.13</v>
       </c>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="34" t="n">
-        <v>53668.16</v>
+        <v>66730.03999999999</v>
       </c>
       <c r="H67" s="34" t="n">
-        <v>104555.76</v>
+        <v>195716.47</v>
       </c>
       <c r="I67" s="34" t="n">
-        <v>189143.77</v>
+        <v>317517.92</v>
       </c>
       <c r="J67" s="34" t="n">
-        <v>15041.13</v>
+        <v>-140005</v>
       </c>
       <c r="K67" s="35" t="n">
-        <v>362408.82</v>
+        <v>439959.43</v>
       </c>
       <c r="L67" s="34" t="n">
-        <v>96006.47</v>
+        <v>132242.95</v>
       </c>
       <c r="M67" s="34" t="n">
-        <v>58463.62</v>
+        <v>64766.54</v>
       </c>
       <c r="N67" s="34" t="n">
-        <v>66725.12</v>
+        <v>130225.19</v>
       </c>
       <c r="O67" s="34" t="n">
-        <v>25449.53</v>
+        <v>-16833.39</v>
       </c>
       <c r="P67" s="35" t="n">
-        <v>246644.74</v>
+        <v>310401.29</v>
       </c>
       <c r="Q67" s="34" t="n">
-        <v>96732.17999999999</v>
+        <v>176351.15</v>
       </c>
       <c r="R67" s="34" t="n">
-        <v>75761.3</v>
+        <v>155883.22</v>
       </c>
       <c r="S67" s="34" t="n">
-        <v>197846.34</v>
+        <v>114720.45</v>
       </c>
       <c r="T67" s="34" t="n">
-        <v>111172.08</v>
+        <v>388132.17</v>
       </c>
       <c r="U67" s="35" t="n">
-        <v>481511.9</v>
+        <v>835086.99</v>
       </c>
       <c r="V67" s="34" t="n">
-        <v>45383.44</v>
+        <v>72937.35000000001</v>
       </c>
       <c r="W67" s="34" t="n">
-        <v>336070.62</v>
+        <v>149070.35</v>
       </c>
       <c r="X67" s="36" t="n">
-        <v>126873.65</v>
+        <v>226429.97</v>
       </c>
       <c r="Y67" s="10" t="n"/>
       <c r="Z67" s="11" t="n"/>
@@ -16139,66 +16192,66 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="E68" s="34" t="n">
-        <v>4460.13</v>
+        <v>285.48</v>
       </c>
       <c r="F68" s="9" t="n"/>
       <c r="G68" s="34" t="n">
-        <v>66730.03999999999</v>
+        <v>30870.54</v>
       </c>
       <c r="H68" s="34" t="n">
-        <v>195716.47</v>
+        <v>151072.65</v>
       </c>
       <c r="I68" s="34" t="n">
-        <v>317517.92</v>
+        <v>284603.73</v>
       </c>
       <c r="J68" s="34" t="n">
-        <v>-140005</v>
+        <v>-249360.06</v>
       </c>
       <c r="K68" s="35" t="n">
-        <v>439959.43</v>
+        <v>217186.86</v>
       </c>
       <c r="L68" s="34" t="n">
-        <v>132242.95</v>
+        <v>67092.05</v>
       </c>
       <c r="M68" s="34" t="n">
-        <v>64766.54</v>
+        <v>22391.99</v>
       </c>
       <c r="N68" s="34" t="n">
-        <v>130225.19</v>
+        <v>90055.83</v>
       </c>
       <c r="O68" s="34" t="n">
-        <v>-16833.39</v>
+        <v>-66761.22</v>
       </c>
       <c r="P68" s="35" t="n">
-        <v>310401.29</v>
+        <v>112778.65</v>
       </c>
       <c r="Q68" s="34" t="n">
-        <v>176351.15</v>
+        <v>107249.15</v>
       </c>
       <c r="R68" s="34" t="n">
-        <v>155883.22</v>
+        <v>103563.63</v>
       </c>
       <c r="S68" s="34" t="n">
-        <v>114720.45</v>
+        <v>847.11</v>
       </c>
       <c r="T68" s="34" t="n">
-        <v>388132.17</v>
+        <v>333631.87</v>
       </c>
       <c r="U68" s="35" t="n">
-        <v>835086.99</v>
+        <v>545291.76</v>
       </c>
       <c r="V68" s="34" t="n">
-        <v>72937.35000000001</v>
+        <v>28986.59</v>
       </c>
       <c r="W68" s="34" t="n">
-        <v>149070.35</v>
+        <v>500.66</v>
       </c>
       <c r="X68" s="36" t="n">
-        <v>226429.97</v>
+        <v>136763.59</v>
       </c>
       <c r="Y68" s="10" t="n"/>
       <c r="Z68" s="11" t="n"/>
@@ -16224,66 +16277,66 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="E69" s="34" t="n">
-        <v>285.48</v>
+        <v>23192.57</v>
       </c>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="34" t="n">
-        <v>30870.54</v>
+        <v>5630.29</v>
       </c>
       <c r="H69" s="34" t="n">
-        <v>151072.65</v>
+        <v>2474.16</v>
       </c>
       <c r="I69" s="34" t="n">
-        <v>284603.73</v>
+        <v>28300.93</v>
       </c>
       <c r="J69" s="34" t="n">
-        <v>-249360.06</v>
+        <v>57412.41</v>
       </c>
       <c r="K69" s="35" t="n">
-        <v>217186.86</v>
+        <v>93817.78999999999</v>
       </c>
       <c r="L69" s="34" t="n">
-        <v>67092.05</v>
+        <v>8258.299999999999</v>
       </c>
       <c r="M69" s="34" t="n">
-        <v>22391.99</v>
+        <v>9968.09</v>
       </c>
       <c r="N69" s="34" t="n">
-        <v>90055.83</v>
+        <v>5080.01</v>
       </c>
       <c r="O69" s="34" t="n">
-        <v>-66761.22</v>
+        <v>29685.92</v>
       </c>
       <c r="P69" s="35" t="n">
-        <v>112778.65</v>
+        <v>52992.32</v>
       </c>
       <c r="Q69" s="34" t="n">
-        <v>107249.15</v>
+        <v>13284.14</v>
       </c>
       <c r="R69" s="34" t="n">
-        <v>103563.63</v>
+        <v>5274.82</v>
       </c>
       <c r="S69" s="34" t="n">
-        <v>847.11</v>
+        <v>116381.47</v>
       </c>
       <c r="T69" s="34" t="n">
-        <v>333631.87</v>
+        <v>-903.7</v>
       </c>
       <c r="U69" s="35" t="n">
-        <v>545291.76</v>
+        <v>134036.73</v>
       </c>
       <c r="V69" s="34" t="n">
-        <v>28986.59</v>
+        <v>10106.06</v>
       </c>
       <c r="W69" s="34" t="n">
-        <v>500.66</v>
+        <v>249025.31</v>
       </c>
       <c r="X69" s="36" t="n">
-        <v>136763.59</v>
+        <v>7236.62</v>
       </c>
       <c r="Y69" s="10" t="n"/>
       <c r="Z69" s="11" t="n"/>
@@ -16309,66 +16362,66 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="E70" s="34" t="n">
-        <v>23192.57</v>
+        <v>-103179.03</v>
       </c>
       <c r="F70" s="9" t="n"/>
       <c r="G70" s="34" t="n">
-        <v>5630.29</v>
+        <v>-49656.65</v>
       </c>
       <c r="H70" s="34" t="n">
-        <v>2474.16</v>
+        <v>50837.01</v>
       </c>
       <c r="I70" s="34" t="n">
-        <v>28300.93</v>
+        <v>141996.99</v>
       </c>
       <c r="J70" s="34" t="n">
-        <v>57412.41</v>
+        <v>-206425.01</v>
       </c>
       <c r="K70" s="35" t="n">
-        <v>93817.78999999999</v>
+        <v>-63247.66</v>
       </c>
       <c r="L70" s="34" t="n">
-        <v>8258.299999999999</v>
+        <v>-4815.46</v>
       </c>
       <c r="M70" s="34" t="n">
-        <v>9968.09</v>
+        <v>-46346.97</v>
       </c>
       <c r="N70" s="34" t="n">
-        <v>5080.01</v>
+        <v>13619.47</v>
       </c>
       <c r="O70" s="34" t="n">
-        <v>29685.92</v>
+        <v>-119343.61</v>
       </c>
       <c r="P70" s="35" t="n">
-        <v>52992.32</v>
+        <v>-156886.57</v>
       </c>
       <c r="Q70" s="34" t="n">
-        <v>13284.14</v>
+        <v>3302.06</v>
       </c>
       <c r="R70" s="34" t="n">
-        <v>5274.82</v>
+        <v>35591.29</v>
       </c>
       <c r="S70" s="34" t="n">
-        <v>116381.47</v>
+        <v>2841.83</v>
       </c>
       <c r="T70" s="34" t="n">
-        <v>-903.7</v>
+        <v>104472.65</v>
       </c>
       <c r="U70" s="35" t="n">
-        <v>134036.73</v>
+        <v>146207.83</v>
       </c>
       <c r="V70" s="34" t="n">
-        <v>10106.06</v>
+        <v>59810.7</v>
       </c>
       <c r="W70" s="34" t="n">
-        <v>249025.31</v>
+        <v>27894.84</v>
       </c>
       <c r="X70" s="36" t="n">
-        <v>7236.62</v>
+        <v>230778.08</v>
       </c>
       <c r="Y70" s="10" t="n"/>
       <c r="Z70" s="11" t="n"/>
@@ -16394,66 +16447,66 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E71" s="34" t="n">
-        <v>-103179.03</v>
+        <v>-24812.81</v>
       </c>
       <c r="F71" s="9" t="n"/>
       <c r="G71" s="34" t="n">
-        <v>-49656.65</v>
+        <v>-10198.24</v>
       </c>
       <c r="H71" s="34" t="n">
-        <v>50837.01</v>
+        <v>13368.58</v>
       </c>
       <c r="I71" s="34" t="n">
-        <v>141996.99</v>
+        <v>34717.31</v>
       </c>
       <c r="J71" s="34" t="n">
-        <v>-206425.01</v>
+        <v>-57368.52</v>
       </c>
       <c r="K71" s="35" t="n">
-        <v>-63247.66</v>
+        <v>-19480.87</v>
       </c>
       <c r="L71" s="34" t="n">
-        <v>-4815.46</v>
+        <v>-445.95</v>
       </c>
       <c r="M71" s="34" t="n">
-        <v>-46346.97</v>
+        <v>-11399.12</v>
       </c>
       <c r="N71" s="34" t="n">
-        <v>13619.47</v>
+        <v>3886.5</v>
       </c>
       <c r="O71" s="34" t="n">
-        <v>-119343.61</v>
+        <v>-9975.280000000001</v>
       </c>
       <c r="P71" s="35" t="n">
-        <v>-156886.57</v>
+        <v>-17933.85</v>
       </c>
       <c r="Q71" s="34" t="n">
-        <v>3302.06</v>
+        <v>1165.49</v>
       </c>
       <c r="R71" s="34" t="n">
-        <v>35591.29</v>
+        <v>6662.5</v>
       </c>
       <c r="S71" s="34" t="n">
-        <v>2841.83</v>
+        <v>237.49</v>
       </c>
       <c r="T71" s="34" t="n">
-        <v>104472.65</v>
+        <v>24894</v>
       </c>
       <c r="U71" s="35" t="n">
-        <v>146207.83</v>
+        <v>32959.48</v>
       </c>
       <c r="V71" s="34" t="n">
-        <v>59810.7</v>
+        <v>8113.35</v>
       </c>
       <c r="W71" s="34" t="n">
-        <v>27894.84</v>
+        <v>2685.97</v>
       </c>
       <c r="X71" s="36" t="n">
-        <v>230778.08</v>
+        <v>47936.06</v>
       </c>
       <c r="Y71" s="10" t="n"/>
       <c r="Z71" s="11" t="n"/>
@@ -16479,66 +16532,66 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E72" s="34" t="n">
-        <v>-24812.81</v>
+        <v>-78366.22</v>
       </c>
       <c r="F72" s="9" t="n"/>
       <c r="G72" s="34" t="n">
-        <v>-10198.24</v>
+        <v>-39458.41</v>
       </c>
       <c r="H72" s="34" t="n">
-        <v>13368.58</v>
+        <v>37468.43</v>
       </c>
       <c r="I72" s="34" t="n">
-        <v>34717.31</v>
+        <v>107279.69</v>
       </c>
       <c r="J72" s="34" t="n">
-        <v>-57368.52</v>
+        <v>-149056.49</v>
       </c>
       <c r="K72" s="35" t="n">
-        <v>-19480.87</v>
+        <v>-43766.78</v>
       </c>
       <c r="L72" s="34" t="n">
-        <v>-445.95</v>
+        <v>-4369.51</v>
       </c>
       <c r="M72" s="34" t="n">
-        <v>-11399.12</v>
+        <v>-34947.84</v>
       </c>
       <c r="N72" s="34" t="n">
-        <v>3886.5</v>
+        <v>9732.969999999999</v>
       </c>
       <c r="O72" s="34" t="n">
-        <v>-9975.280000000001</v>
+        <v>-109368.33</v>
       </c>
       <c r="P72" s="35" t="n">
-        <v>-17933.85</v>
+        <v>-138952.71</v>
       </c>
       <c r="Q72" s="34" t="n">
-        <v>1165.49</v>
+        <v>2136.57</v>
       </c>
       <c r="R72" s="34" t="n">
-        <v>6662.5</v>
+        <v>28928.79</v>
       </c>
       <c r="S72" s="34" t="n">
-        <v>237.49</v>
+        <v>2604.35</v>
       </c>
       <c r="T72" s="34" t="n">
-        <v>24894</v>
+        <v>79578.64</v>
       </c>
       <c r="U72" s="35" t="n">
-        <v>32959.48</v>
+        <v>113248.35</v>
       </c>
       <c r="V72" s="34" t="n">
-        <v>8113.35</v>
+        <v>51697.35</v>
       </c>
       <c r="W72" s="34" t="n">
-        <v>2685.97</v>
+        <v>25208.87</v>
       </c>
       <c r="X72" s="36" t="n">
-        <v>47936.06</v>
+        <v>182842.03</v>
       </c>
       <c r="Y72" s="10" t="n"/>
       <c r="Z72" s="11" t="n"/>
@@ -16564,66 +16617,66 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="E73" s="34" t="n">
-        <v>-78366.22</v>
+        <v>-85841.95</v>
       </c>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="34" t="n">
-        <v>-39458.41</v>
+        <v>-33607.76</v>
       </c>
       <c r="H73" s="34" t="n">
-        <v>37468.43</v>
+        <v>43063.65</v>
       </c>
       <c r="I73" s="34" t="n">
-        <v>107279.69</v>
+        <v>116987.24</v>
       </c>
       <c r="J73" s="34" t="n">
-        <v>-149056.49</v>
+        <v>-151845.84</v>
       </c>
       <c r="K73" s="35" t="n">
-        <v>-43766.78</v>
+        <v>-25402.71</v>
       </c>
       <c r="L73" s="34" t="n">
-        <v>-4369.51</v>
+        <v>-1773.34</v>
       </c>
       <c r="M73" s="34" t="n">
-        <v>-34947.84</v>
+        <v>-34249.21</v>
       </c>
       <c r="N73" s="34" t="n">
-        <v>9732.969999999999</v>
+        <v>12135.61</v>
       </c>
       <c r="O73" s="34" t="n">
-        <v>-109368.33</v>
+        <v>-136163.58</v>
       </c>
       <c r="P73" s="35" t="n">
-        <v>-138952.71</v>
+        <v>-160050.52</v>
       </c>
       <c r="Q73" s="34" t="n">
-        <v>2136.57</v>
+        <v>6592.48</v>
       </c>
       <c r="R73" s="34" t="n">
-        <v>28928.79</v>
+        <v>31914.81</v>
       </c>
       <c r="S73" s="34" t="n">
-        <v>2604.35</v>
+        <v>-2695.38</v>
       </c>
       <c r="T73" s="34" t="n">
-        <v>79578.64</v>
+        <v>56741.83</v>
       </c>
       <c r="U73" s="35" t="n">
-        <v>113248.35</v>
+        <v>92553.74000000001</v>
       </c>
       <c r="V73" s="34" t="n">
-        <v>51697.35</v>
+        <v>51457.82</v>
       </c>
       <c r="W73" s="34" t="n">
-        <v>25208.87</v>
+        <v>69514.88</v>
       </c>
       <c r="X73" s="36" t="n">
-        <v>182842.03</v>
+        <v>187199.9</v>
       </c>
       <c r="Y73" s="10" t="n"/>
       <c r="Z73" s="11" t="n"/>
@@ -16649,66 +16702,66 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E74" s="34" t="n">
-        <v>-85841.95</v>
+        <v>-79240.08</v>
       </c>
       <c r="F74" s="9" t="n"/>
       <c r="G74" s="34" t="n">
-        <v>-33607.76</v>
+        <v>-41229.95</v>
       </c>
       <c r="H74" s="34" t="n">
-        <v>43063.65</v>
+        <v>40110.16</v>
       </c>
       <c r="I74" s="34" t="n">
-        <v>116987.24</v>
+        <v>107279.35</v>
       </c>
       <c r="J74" s="34" t="n">
-        <v>-151845.84</v>
+        <v>-150740.68</v>
       </c>
       <c r="K74" s="35" t="n">
-        <v>-25402.71</v>
+        <v>-44581.12</v>
       </c>
       <c r="L74" s="34" t="n">
-        <v>-1773.34</v>
+        <v>-4516.24</v>
       </c>
       <c r="M74" s="34" t="n">
-        <v>-34249.21</v>
+        <v>-37006.41</v>
       </c>
       <c r="N74" s="34" t="n">
-        <v>12135.61</v>
+        <v>9302.52</v>
       </c>
       <c r="O74" s="34" t="n">
-        <v>-136163.58</v>
+        <v>-110719</v>
       </c>
       <c r="P74" s="35" t="n">
-        <v>-160050.52</v>
+        <v>-142939.13</v>
       </c>
       <c r="Q74" s="34" t="n">
-        <v>6592.48</v>
+        <v>1859.49</v>
       </c>
       <c r="R74" s="34" t="n">
-        <v>31914.81</v>
+        <v>27372.69</v>
       </c>
       <c r="S74" s="34" t="n">
-        <v>-2695.38</v>
+        <v>-168.22</v>
       </c>
       <c r="T74" s="34" t="n">
-        <v>56741.83</v>
+        <v>76465.67999999999</v>
       </c>
       <c r="U74" s="35" t="n">
-        <v>92553.74000000001</v>
+        <v>105529.64</v>
       </c>
       <c r="V74" s="34" t="n">
-        <v>51457.82</v>
+        <v>49003.03</v>
       </c>
       <c r="W74" s="34" t="n">
-        <v>69514.88</v>
+        <v>22253.22</v>
       </c>
       <c r="X74" s="36" t="n">
-        <v>187199.9</v>
+        <v>180549.41</v>
       </c>
       <c r="Y74" s="10" t="n"/>
       <c r="Z74" s="11" t="n"/>
@@ -16734,66 +16787,66 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>(비지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E75" s="34" t="n">
-        <v>-79240.08</v>
+        <v>873.87</v>
       </c>
       <c r="F75" s="9" t="n"/>
       <c r="G75" s="34" t="n">
-        <v>-41229.95</v>
+        <v>1771.54</v>
       </c>
       <c r="H75" s="34" t="n">
-        <v>40110.16</v>
+        <v>-2641.73</v>
       </c>
       <c r="I75" s="34" t="n">
-        <v>107279.35</v>
+        <v>0.34</v>
       </c>
       <c r="J75" s="34" t="n">
-        <v>-150740.68</v>
+        <v>1684.2</v>
       </c>
       <c r="K75" s="35" t="n">
-        <v>-44581.12</v>
+        <v>814.35</v>
       </c>
       <c r="L75" s="34" t="n">
-        <v>-4516.24</v>
+        <v>146.73</v>
       </c>
       <c r="M75" s="34" t="n">
-        <v>-37006.41</v>
+        <v>2058.57</v>
       </c>
       <c r="N75" s="34" t="n">
-        <v>9302.52</v>
+        <v>430.45</v>
       </c>
       <c r="O75" s="34" t="n">
-        <v>-110719</v>
+        <v>1350.67</v>
       </c>
       <c r="P75" s="35" t="n">
-        <v>-142939.13</v>
+        <v>3986.42</v>
       </c>
       <c r="Q75" s="34" t="n">
-        <v>1859.49</v>
+        <v>277.08</v>
       </c>
       <c r="R75" s="34" t="n">
-        <v>27372.69</v>
+        <v>1556.1</v>
       </c>
       <c r="S75" s="34" t="n">
-        <v>-168.22</v>
+        <v>2772.57</v>
       </c>
       <c r="T75" s="34" t="n">
-        <v>76465.67999999999</v>
+        <v>3112.97</v>
       </c>
       <c r="U75" s="35" t="n">
-        <v>105529.64</v>
+        <v>7718.72</v>
       </c>
       <c r="V75" s="34" t="n">
-        <v>49003.03</v>
+        <v>2694.33</v>
       </c>
       <c r="W75" s="34" t="n">
-        <v>22253.22</v>
+        <v>2955.64</v>
       </c>
       <c r="X75" s="36" t="n">
-        <v>180549.41</v>
+        <v>2292.62</v>
       </c>
       <c r="Y75" s="10" t="n"/>
       <c r="Z75" s="11" t="n"/>
@@ -16819,66 +16872,66 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(비지배주주지분)당기순이익</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="E76" s="34" t="n">
-        <v>873.87</v>
+        <v>-3265.06</v>
       </c>
       <c r="F76" s="9" t="n"/>
       <c r="G76" s="34" t="n">
-        <v>1771.54</v>
+        <v>-13061.88</v>
       </c>
       <c r="H76" s="34" t="n">
-        <v>-2641.73</v>
+        <v>-91160.71000000001</v>
       </c>
       <c r="I76" s="34" t="n">
-        <v>0.34</v>
+        <v>-128374.15</v>
       </c>
       <c r="J76" s="34" t="n">
-        <v>1684.2</v>
+        <v>155046.13</v>
       </c>
       <c r="K76" s="35" t="n">
-        <v>814.35</v>
+        <v>-77550.61</v>
       </c>
       <c r="L76" s="34" t="n">
-        <v>146.73</v>
+        <v>-36236.48</v>
       </c>
       <c r="M76" s="34" t="n">
-        <v>2058.57</v>
+        <v>-6302.92</v>
       </c>
       <c r="N76" s="34" t="n">
-        <v>430.45</v>
+        <v>-63500.07</v>
       </c>
       <c r="O76" s="34" t="n">
-        <v>1350.67</v>
+        <v>42282.92</v>
       </c>
       <c r="P76" s="35" t="n">
-        <v>3986.42</v>
+        <v>-63756.55</v>
       </c>
       <c r="Q76" s="34" t="n">
-        <v>277.08</v>
+        <v>-79618.97</v>
       </c>
       <c r="R76" s="34" t="n">
-        <v>1556.1</v>
+        <v>-80121.92</v>
       </c>
       <c r="S76" s="34" t="n">
-        <v>2772.57</v>
+        <v>83125.89</v>
       </c>
       <c r="T76" s="34" t="n">
-        <v>3112.97</v>
+        <v>-276960.09</v>
       </c>
       <c r="U76" s="35" t="n">
-        <v>7718.72</v>
+        <v>-353575.09</v>
       </c>
       <c r="V76" s="34" t="n">
-        <v>2694.33</v>
+        <v>-27553.91</v>
       </c>
       <c r="W76" s="34" t="n">
-        <v>2955.64</v>
+        <v>187000.27</v>
       </c>
       <c r="X76" s="36" t="n">
-        <v>2292.62</v>
+        <v>-99556.32000000001</v>
       </c>
       <c r="Y76" s="10" t="n"/>
       <c r="Z76" s="11" t="n"/>
@@ -16904,66 +16957,66 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E77" s="34" t="n">
-        <v>-3265.06</v>
+        <v>-22907.09</v>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="34" t="n">
-        <v>-13061.88</v>
+        <v>25240.25</v>
       </c>
       <c r="H77" s="34" t="n">
-        <v>-91160.71000000001</v>
+        <v>148598.49</v>
       </c>
       <c r="I77" s="34" t="n">
-        <v>-128374.15</v>
+        <v>256302.8</v>
       </c>
       <c r="J77" s="34" t="n">
-        <v>155046.13</v>
+        <v>-306772.47</v>
       </c>
       <c r="K77" s="35" t="n">
-        <v>-77550.61</v>
+        <v>123369.07</v>
       </c>
       <c r="L77" s="34" t="n">
-        <v>-36236.48</v>
+        <v>58833.75</v>
       </c>
       <c r="M77" s="34" t="n">
-        <v>-6302.92</v>
+        <v>12423.9</v>
       </c>
       <c r="N77" s="34" t="n">
-        <v>-63500.07</v>
+        <v>84975.82000000001</v>
       </c>
       <c r="O77" s="34" t="n">
-        <v>42282.92</v>
+        <v>-96447.14</v>
       </c>
       <c r="P77" s="35" t="n">
-        <v>-63756.55</v>
+        <v>59786.33</v>
       </c>
       <c r="Q77" s="34" t="n">
-        <v>-79618.97</v>
+        <v>93965.00999999999</v>
       </c>
       <c r="R77" s="34" t="n">
-        <v>-80121.92</v>
+        <v>98288.81</v>
       </c>
       <c r="S77" s="34" t="n">
-        <v>83125.89</v>
+        <v>-115534.36</v>
       </c>
       <c r="T77" s="34" t="n">
-        <v>-276960.09</v>
+        <v>334535.57</v>
       </c>
       <c r="U77" s="35" t="n">
-        <v>-353575.09</v>
+        <v>411255.03</v>
       </c>
       <c r="V77" s="34" t="n">
-        <v>-27553.91</v>
+        <v>18880.53</v>
       </c>
       <c r="W77" s="34" t="n">
-        <v>187000.27</v>
+        <v>-248524.65</v>
       </c>
       <c r="X77" s="36" t="n">
-        <v>-99556.32000000001</v>
+        <v>129526.97</v>
       </c>
       <c r="Y77" s="10" t="n"/>
       <c r="Z77" s="11" t="n"/>
@@ -16989,66 +17042,66 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>계속사업이익</t>
         </is>
       </c>
       <c r="E78" s="34" t="n">
-        <v>-22907.09</v>
+        <v>-78366.22</v>
       </c>
       <c r="F78" s="9" t="n"/>
       <c r="G78" s="34" t="n">
-        <v>25240.25</v>
+        <v>-39458.41</v>
       </c>
       <c r="H78" s="34" t="n">
-        <v>148598.49</v>
+        <v>37468.43</v>
       </c>
       <c r="I78" s="34" t="n">
-        <v>256302.8</v>
+        <v>107279.69</v>
       </c>
       <c r="J78" s="34" t="n">
-        <v>-306772.47</v>
+        <v>-149056.49</v>
       </c>
       <c r="K78" s="35" t="n">
-        <v>123369.07</v>
+        <v>-43766.78</v>
       </c>
       <c r="L78" s="34" t="n">
-        <v>58833.75</v>
+        <v>-4369.51</v>
       </c>
       <c r="M78" s="34" t="n">
-        <v>12423.9</v>
+        <v>-34947.84</v>
       </c>
       <c r="N78" s="34" t="n">
-        <v>84975.82000000001</v>
+        <v>9732.969999999999</v>
       </c>
       <c r="O78" s="34" t="n">
-        <v>-96447.14</v>
+        <v>-109368.33</v>
       </c>
       <c r="P78" s="35" t="n">
-        <v>59786.33</v>
+        <v>-138952.71</v>
       </c>
       <c r="Q78" s="34" t="n">
-        <v>93965.00999999999</v>
+        <v>2136.57</v>
       </c>
       <c r="R78" s="34" t="n">
-        <v>98288.81</v>
+        <v>28928.79</v>
       </c>
       <c r="S78" s="34" t="n">
-        <v>-115534.36</v>
+        <v>2604.35</v>
       </c>
       <c r="T78" s="34" t="n">
-        <v>334535.57</v>
+        <v>79578.64</v>
       </c>
       <c r="U78" s="35" t="n">
-        <v>411255.03</v>
+        <v>113248.35</v>
       </c>
       <c r="V78" s="34" t="n">
-        <v>18880.53</v>
+        <v>51697.35</v>
       </c>
       <c r="W78" s="34" t="n">
-        <v>-248524.65</v>
+        <v>25208.87</v>
       </c>
       <c r="X78" s="36" t="n">
-        <v>129526.97</v>
+        <v>182842.03</v>
       </c>
       <c r="Y78" s="10" t="n"/>
       <c r="Z78" s="11" t="n"/>
@@ -17074,66 +17127,63 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
-        </is>
-      </c>
-      <c r="E79" s="34" t="n">
-        <v>-78366.22</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
       <c r="G79" s="34" t="n">
-        <v>-39458.41</v>
+        <v>1721</v>
       </c>
       <c r="H79" s="34" t="n">
-        <v>37468.43</v>
+        <v>2717</v>
       </c>
       <c r="I79" s="34" t="n">
-        <v>107279.69</v>
+        <v>4028</v>
       </c>
       <c r="J79" s="34" t="n">
-        <v>-149056.49</v>
+        <v>5073</v>
       </c>
       <c r="K79" s="35" t="n">
-        <v>-43766.78</v>
+        <v>13539</v>
       </c>
       <c r="L79" s="34" t="n">
-        <v>-4369.51</v>
+        <v>4039</v>
       </c>
       <c r="M79" s="34" t="n">
-        <v>-34947.84</v>
+        <v>3835</v>
       </c>
       <c r="N79" s="34" t="n">
-        <v>9732.969999999999</v>
+        <v>3965</v>
       </c>
       <c r="O79" s="34" t="n">
-        <v>-109368.33</v>
+        <v>4081</v>
       </c>
       <c r="P79" s="35" t="n">
-        <v>-138952.71</v>
+        <v>15920</v>
       </c>
       <c r="Q79" s="34" t="n">
-        <v>2136.57</v>
+        <v>4357</v>
       </c>
       <c r="R79" s="34" t="n">
-        <v>28928.79</v>
+        <v>3987</v>
       </c>
       <c r="S79" s="34" t="n">
-        <v>2604.35</v>
+        <v>4372</v>
       </c>
       <c r="T79" s="34" t="n">
-        <v>79578.64</v>
+        <v>3542</v>
       </c>
       <c r="U79" s="35" t="n">
-        <v>113248.35</v>
+        <v>16258</v>
       </c>
       <c r="V79" s="34" t="n">
-        <v>51697.35</v>
+        <v>2662</v>
       </c>
       <c r="W79" s="34" t="n">
-        <v>25208.87</v>
+        <v>3356</v>
       </c>
       <c r="X79" s="36" t="n">
-        <v>182842.03</v>
+        <v>4295</v>
       </c>
       <c r="Y79" s="10" t="n"/>
       <c r="Z79" s="11" t="n"/>
@@ -17159,63 +17209,63 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="F80" s="9" t="n"/>
       <c r="G80" s="34" t="n">
-        <v>1721</v>
+        <v>37</v>
       </c>
       <c r="H80" s="34" t="n">
-        <v>2717</v>
+        <v>0</v>
       </c>
       <c r="I80" s="34" t="n">
-        <v>4028</v>
+        <v>0</v>
       </c>
       <c r="J80" s="34" t="n">
-        <v>5073</v>
+        <v>0</v>
       </c>
       <c r="K80" s="35" t="n">
-        <v>13539</v>
+        <v>37</v>
       </c>
       <c r="L80" s="34" t="n">
-        <v>4039</v>
+        <v>42</v>
       </c>
       <c r="M80" s="34" t="n">
-        <v>3835</v>
+        <v>0</v>
       </c>
       <c r="N80" s="34" t="n">
-        <v>3965</v>
+        <v>0</v>
       </c>
       <c r="O80" s="34" t="n">
-        <v>4081</v>
+        <v>0</v>
       </c>
       <c r="P80" s="35" t="n">
-        <v>15920</v>
+        <v>42</v>
       </c>
       <c r="Q80" s="34" t="n">
-        <v>4357</v>
+        <v>62</v>
       </c>
       <c r="R80" s="34" t="n">
-        <v>3987</v>
+        <v>0</v>
       </c>
       <c r="S80" s="34" t="n">
-        <v>4372</v>
+        <v>0</v>
       </c>
       <c r="T80" s="34" t="n">
-        <v>3542</v>
+        <v>0</v>
       </c>
       <c r="U80" s="35" t="n">
-        <v>16258</v>
+        <v>62</v>
       </c>
       <c r="V80" s="34" t="n">
-        <v>2662</v>
+        <v>62</v>
       </c>
       <c r="W80" s="34" t="n">
-        <v>3356</v>
+        <v>0</v>
       </c>
       <c r="X80" s="36" t="n">
-        <v>4295</v>
+        <v>0</v>
       </c>
       <c r="Y80" s="10" t="n"/>
       <c r="Z80" s="11" t="n"/>
@@ -17241,63 +17291,63 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>배당금수익</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="F81" s="9" t="n"/>
       <c r="G81" s="34" t="n">
-        <v>37</v>
+        <v>821</v>
       </c>
       <c r="H81" s="34" t="n">
-        <v>0</v>
+        <v>1213</v>
       </c>
       <c r="I81" s="34" t="n">
-        <v>0</v>
+        <v>1509</v>
       </c>
       <c r="J81" s="34" t="n">
-        <v>0</v>
+        <v>1518</v>
       </c>
       <c r="K81" s="35" t="n">
-        <v>37</v>
+        <v>5061</v>
       </c>
       <c r="L81" s="34" t="n">
-        <v>42</v>
+        <v>1517</v>
       </c>
       <c r="M81" s="34" t="n">
-        <v>0</v>
+        <v>3171</v>
       </c>
       <c r="N81" s="34" t="n">
-        <v>0</v>
+        <v>3949</v>
       </c>
       <c r="O81" s="34" t="n">
-        <v>0</v>
+        <v>5196</v>
       </c>
       <c r="P81" s="35" t="n">
-        <v>42</v>
+        <v>13833</v>
       </c>
       <c r="Q81" s="34" t="n">
-        <v>62</v>
+        <v>6913</v>
       </c>
       <c r="R81" s="34" t="n">
-        <v>0</v>
+        <v>5247</v>
       </c>
       <c r="S81" s="34" t="n">
-        <v>0</v>
+        <v>4547</v>
       </c>
       <c r="T81" s="34" t="n">
-        <v>0</v>
+        <v>2756</v>
       </c>
       <c r="U81" s="35" t="n">
-        <v>62</v>
+        <v>19463</v>
       </c>
       <c r="V81" s="34" t="n">
-        <v>62</v>
+        <v>3218</v>
       </c>
       <c r="W81" s="34" t="n">
-        <v>0</v>
+        <v>945</v>
       </c>
       <c r="X81" s="36" t="n">
-        <v>0</v>
+        <v>1136</v>
       </c>
       <c r="Y81" s="10" t="n"/>
       <c r="Z81" s="11" t="n"/>
@@ -17323,63 +17373,63 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="F82" s="9" t="n"/>
       <c r="G82" s="34" t="n">
-        <v>821</v>
+        <v>38996</v>
       </c>
       <c r="H82" s="34" t="n">
-        <v>1213</v>
+        <v>58814</v>
       </c>
       <c r="I82" s="34" t="n">
-        <v>1509</v>
+        <v>86354</v>
       </c>
       <c r="J82" s="34" t="n">
-        <v>1518</v>
+        <v>87300</v>
       </c>
       <c r="K82" s="35" t="n">
-        <v>5061</v>
+        <v>271464</v>
       </c>
       <c r="L82" s="34" t="n">
-        <v>1517</v>
+        <v>52556</v>
       </c>
       <c r="M82" s="34" t="n">
-        <v>3171</v>
+        <v>46704</v>
       </c>
       <c r="N82" s="34" t="n">
-        <v>3949</v>
+        <v>41098</v>
       </c>
       <c r="O82" s="34" t="n">
-        <v>5196</v>
+        <v>28852</v>
       </c>
       <c r="P82" s="35" t="n">
-        <v>13833</v>
+        <v>169210</v>
       </c>
       <c r="Q82" s="34" t="n">
-        <v>6913</v>
+        <v>55680</v>
       </c>
       <c r="R82" s="34" t="n">
-        <v>5247</v>
+        <v>70776</v>
       </c>
       <c r="S82" s="34" t="n">
-        <v>4547</v>
+        <v>38658</v>
       </c>
       <c r="T82" s="34" t="n">
-        <v>2756</v>
+        <v>49739</v>
       </c>
       <c r="U82" s="35" t="n">
-        <v>19463</v>
+        <v>214853</v>
       </c>
       <c r="V82" s="34" t="n">
-        <v>3218</v>
+        <v>25945</v>
       </c>
       <c r="W82" s="34" t="n">
-        <v>945</v>
+        <v>42459</v>
       </c>
       <c r="X82" s="36" t="n">
-        <v>1136</v>
+        <v>52535</v>
       </c>
       <c r="Y82" s="10" t="n"/>
       <c r="Z82" s="11" t="n"/>
@@ -17405,63 +17455,63 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>외환차익</t>
+          <t>외환차손</t>
         </is>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="34" t="n">
-        <v>38996</v>
+        <v>23277</v>
       </c>
       <c r="H83" s="34" t="n">
-        <v>58814</v>
+        <v>20508</v>
       </c>
       <c r="I83" s="34" t="n">
-        <v>86354</v>
+        <v>18165</v>
       </c>
       <c r="J83" s="34" t="n">
-        <v>87300</v>
+        <v>70742</v>
       </c>
       <c r="K83" s="35" t="n">
-        <v>271464</v>
+        <v>132692</v>
       </c>
       <c r="L83" s="34" t="n">
-        <v>52556</v>
+        <v>38078</v>
       </c>
       <c r="M83" s="34" t="n">
-        <v>46704</v>
+        <v>23420</v>
       </c>
       <c r="N83" s="34" t="n">
-        <v>41098</v>
+        <v>22862</v>
       </c>
       <c r="O83" s="34" t="n">
-        <v>28852</v>
+        <v>34179</v>
       </c>
       <c r="P83" s="35" t="n">
-        <v>169210</v>
+        <v>118539</v>
       </c>
       <c r="Q83" s="34" t="n">
-        <v>55680</v>
+        <v>23076</v>
       </c>
       <c r="R83" s="34" t="n">
-        <v>70776</v>
+        <v>25167</v>
       </c>
       <c r="S83" s="34" t="n">
-        <v>38658</v>
+        <v>48578</v>
       </c>
       <c r="T83" s="34" t="n">
-        <v>49739</v>
+        <v>20919</v>
       </c>
       <c r="U83" s="35" t="n">
-        <v>214853</v>
+        <v>117740</v>
       </c>
       <c r="V83" s="34" t="n">
-        <v>25945</v>
+        <v>32246</v>
       </c>
       <c r="W83" s="34" t="n">
-        <v>42459</v>
+        <v>82351</v>
       </c>
       <c r="X83" s="36" t="n">
-        <v>52535</v>
+        <v>59961</v>
       </c>
       <c r="Y83" s="10" t="n"/>
       <c r="Z83" s="11" t="n"/>
@@ -17487,63 +17537,63 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>외화환산이익</t>
         </is>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="34" t="n">
-        <v>23277</v>
+        <v>9518</v>
       </c>
       <c r="H84" s="34" t="n">
-        <v>20508</v>
+        <v>42793</v>
       </c>
       <c r="I84" s="34" t="n">
-        <v>18165</v>
+        <v>98762</v>
       </c>
       <c r="J84" s="34" t="n">
-        <v>70742</v>
+        <v>-132785</v>
       </c>
       <c r="K84" s="35" t="n">
-        <v>132692</v>
+        <v>18288</v>
       </c>
       <c r="L84" s="34" t="n">
-        <v>38078</v>
+        <v>34361</v>
       </c>
       <c r="M84" s="34" t="n">
-        <v>23420</v>
+        <v>-12185</v>
       </c>
       <c r="N84" s="34" t="n">
-        <v>22862</v>
+        <v>16611</v>
       </c>
       <c r="O84" s="34" t="n">
-        <v>34179</v>
+        <v>-31125</v>
       </c>
       <c r="P84" s="35" t="n">
-        <v>118539</v>
+        <v>7662</v>
       </c>
       <c r="Q84" s="34" t="n">
-        <v>23076</v>
+        <v>35797</v>
       </c>
       <c r="R84" s="34" t="n">
-        <v>25167</v>
+        <v>0</v>
       </c>
       <c r="S84" s="34" t="n">
-        <v>48578</v>
+        <v>0</v>
       </c>
       <c r="T84" s="34" t="n">
-        <v>20919</v>
+        <v>77825</v>
       </c>
       <c r="U84" s="35" t="n">
-        <v>117740</v>
+        <v>113622</v>
       </c>
       <c r="V84" s="34" t="n">
-        <v>32246</v>
+        <v>9870</v>
       </c>
       <c r="W84" s="34" t="n">
-        <v>82351</v>
+        <v>11049</v>
       </c>
       <c r="X84" s="36" t="n">
-        <v>59961</v>
+        <v>56424</v>
       </c>
       <c r="Y84" s="10" t="n"/>
       <c r="Z84" s="11" t="n"/>
@@ -17569,63 +17619,63 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>외화환산이익</t>
+          <t>외화환산손실</t>
         </is>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="34" t="n">
-        <v>9518</v>
+        <v>6962</v>
       </c>
       <c r="H85" s="34" t="n">
-        <v>42793</v>
+        <v>11922</v>
       </c>
       <c r="I85" s="34" t="n">
-        <v>98762</v>
+        <v>21824</v>
       </c>
       <c r="J85" s="34" t="n">
-        <v>-132785</v>
+        <v>56309</v>
       </c>
       <c r="K85" s="35" t="n">
-        <v>18288</v>
+        <v>97017</v>
       </c>
       <c r="L85" s="34" t="n">
-        <v>34361</v>
+        <v>9266</v>
       </c>
       <c r="M85" s="34" t="n">
-        <v>-12185</v>
+        <v>9146</v>
       </c>
       <c r="N85" s="34" t="n">
-        <v>16611</v>
+        <v>6293</v>
       </c>
       <c r="O85" s="34" t="n">
-        <v>-31125</v>
+        <v>17985</v>
       </c>
       <c r="P85" s="35" t="n">
-        <v>7662</v>
+        <v>42690</v>
       </c>
       <c r="Q85" s="34" t="n">
-        <v>35797</v>
+        <v>10002</v>
       </c>
       <c r="R85" s="34" t="n">
+        <v>11048</v>
+      </c>
+      <c r="S85" s="34" t="n">
+        <v>38628</v>
+      </c>
+      <c r="T85" s="34" t="n">
+        <v>4848</v>
+      </c>
+      <c r="U85" s="35" t="n">
+        <v>64526</v>
+      </c>
+      <c r="V85" s="34" t="n">
+        <v>6229</v>
+      </c>
+      <c r="W85" s="34" t="n">
+        <v>64400</v>
+      </c>
+      <c r="X85" s="36" t="n">
         <v>0</v>
-      </c>
-      <c r="S85" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" s="34" t="n">
-        <v>77825</v>
-      </c>
-      <c r="U85" s="35" t="n">
-        <v>113622</v>
-      </c>
-      <c r="V85" s="34" t="n">
-        <v>9870</v>
-      </c>
-      <c r="W85" s="34" t="n">
-        <v>11049</v>
-      </c>
-      <c r="X85" s="36" t="n">
-        <v>56424</v>
       </c>
       <c r="Y85" s="10" t="n"/>
       <c r="Z85" s="11" t="n"/>
@@ -17651,63 +17701,63 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>외화환산손실</t>
+          <t>파생상품이익</t>
         </is>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="34" t="n">
-        <v>6962</v>
+        <v>3259</v>
       </c>
       <c r="H86" s="34" t="n">
-        <v>11922</v>
+        <v>232</v>
       </c>
       <c r="I86" s="34" t="n">
-        <v>21824</v>
+        <v>-151</v>
       </c>
       <c r="J86" s="34" t="n">
-        <v>56309</v>
+        <v>55453</v>
       </c>
       <c r="K86" s="35" t="n">
-        <v>97017</v>
+        <v>58793</v>
       </c>
       <c r="L86" s="34" t="n">
-        <v>9266</v>
+        <v>5008</v>
       </c>
       <c r="M86" s="34" t="n">
-        <v>9146</v>
+        <v>7925</v>
       </c>
       <c r="N86" s="34" t="n">
-        <v>6293</v>
+        <v>5051</v>
       </c>
       <c r="O86" s="34" t="n">
-        <v>17985</v>
+        <v>23641</v>
       </c>
       <c r="P86" s="35" t="n">
-        <v>42690</v>
+        <v>41625</v>
       </c>
       <c r="Q86" s="34" t="n">
-        <v>10002</v>
+        <v>836</v>
       </c>
       <c r="R86" s="34" t="n">
-        <v>11048</v>
+        <v>998</v>
       </c>
       <c r="S86" s="34" t="n">
-        <v>38628</v>
+        <v>154816</v>
       </c>
       <c r="T86" s="34" t="n">
-        <v>4848</v>
+        <v>-19934</v>
       </c>
       <c r="U86" s="35" t="n">
-        <v>64526</v>
+        <v>136716</v>
       </c>
       <c r="V86" s="34" t="n">
-        <v>6229</v>
+        <v>6844</v>
       </c>
       <c r="W86" s="34" t="n">
-        <v>64400</v>
+        <v>279207</v>
       </c>
       <c r="X86" s="36" t="n">
-        <v>0</v>
+        <v>13620</v>
       </c>
       <c r="Y86" s="10" t="n"/>
       <c r="Z86" s="11" t="n"/>
@@ -17733,63 +17783,63 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>파생상품이익</t>
+          <t>파생상품손실</t>
         </is>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="34" t="n">
-        <v>3259</v>
+        <v>35670</v>
       </c>
       <c r="H87" s="34" t="n">
-        <v>232</v>
+        <v>162073</v>
       </c>
       <c r="I87" s="34" t="n">
-        <v>-151</v>
+        <v>276020</v>
       </c>
       <c r="J87" s="34" t="n">
-        <v>55453</v>
+        <v>-268575</v>
       </c>
       <c r="K87" s="35" t="n">
-        <v>58793</v>
+        <v>205188</v>
       </c>
       <c r="L87" s="34" t="n">
-        <v>5008</v>
+        <v>83382</v>
       </c>
       <c r="M87" s="34" t="n">
-        <v>7925</v>
+        <v>29030</v>
       </c>
       <c r="N87" s="34" t="n">
-        <v>5051</v>
+        <v>97121</v>
       </c>
       <c r="O87" s="34" t="n">
-        <v>23641</v>
+        <v>-74201</v>
       </c>
       <c r="P87" s="35" t="n">
-        <v>41625</v>
+        <v>135332</v>
       </c>
       <c r="Q87" s="34" t="n">
-        <v>836</v>
+        <v>136360</v>
       </c>
       <c r="R87" s="34" t="n">
-        <v>998</v>
+        <v>114421</v>
       </c>
       <c r="S87" s="34" t="n">
-        <v>154816</v>
+        <v>22967</v>
       </c>
       <c r="T87" s="34" t="n">
-        <v>-19934</v>
+        <v>359609</v>
       </c>
       <c r="U87" s="35" t="n">
-        <v>136716</v>
+        <v>633357</v>
       </c>
       <c r="V87" s="34" t="n">
-        <v>6844</v>
+        <v>31244</v>
       </c>
       <c r="W87" s="34" t="n">
-        <v>279207</v>
+        <v>1374</v>
       </c>
       <c r="X87" s="36" t="n">
-        <v>13620</v>
+        <v>165333</v>
       </c>
       <c r="Y87" s="10" t="n"/>
       <c r="Z87" s="11" t="n"/>
@@ -17815,63 +17865,63 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>파생상품손실</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="34" t="n">
-        <v>35670</v>
+        <v>900</v>
       </c>
       <c r="H88" s="34" t="n">
-        <v>162073</v>
+        <v>1504</v>
       </c>
       <c r="I88" s="34" t="n">
-        <v>276020</v>
+        <v>2519</v>
       </c>
       <c r="J88" s="34" t="n">
-        <v>-268575</v>
+        <v>3555</v>
       </c>
       <c r="K88" s="35" t="n">
-        <v>205188</v>
+        <v>8478</v>
       </c>
       <c r="L88" s="34" t="n">
-        <v>83382</v>
+        <v>2522</v>
       </c>
       <c r="M88" s="34" t="n">
-        <v>29030</v>
+        <v>664</v>
       </c>
       <c r="N88" s="34" t="n">
-        <v>97121</v>
+        <v>16</v>
       </c>
       <c r="O88" s="34" t="n">
-        <v>-74201</v>
+        <v>-1115</v>
       </c>
       <c r="P88" s="35" t="n">
-        <v>135332</v>
+        <v>2087</v>
       </c>
       <c r="Q88" s="34" t="n">
-        <v>136360</v>
+        <v>-2556</v>
       </c>
       <c r="R88" s="34" t="n">
-        <v>114421</v>
+        <v>-1260</v>
       </c>
       <c r="S88" s="34" t="n">
-        <v>22967</v>
+        <v>-175</v>
       </c>
       <c r="T88" s="34" t="n">
-        <v>359609</v>
+        <v>786</v>
       </c>
       <c r="U88" s="35" t="n">
-        <v>633357</v>
+        <v>-3205</v>
       </c>
       <c r="V88" s="34" t="n">
-        <v>31244</v>
+        <v>-556</v>
       </c>
       <c r="W88" s="34" t="n">
-        <v>1374</v>
+        <v>2411</v>
       </c>
       <c r="X88" s="36" t="n">
-        <v>165333</v>
+        <v>3159</v>
       </c>
       <c r="Y88" s="10" t="n"/>
       <c r="Z88" s="11" t="n"/>
@@ -17897,63 +17947,66 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>이자손익</t>
-        </is>
+          <t>영업활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E89" s="34" t="n">
+        <v>-277126.05</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="34" t="n">
-        <v>900</v>
+        <v>170813.3</v>
       </c>
       <c r="H89" s="34" t="n">
-        <v>1504</v>
+        <v>104465.44</v>
       </c>
       <c r="I89" s="34" t="n">
-        <v>2519</v>
+        <v>-125000.98</v>
       </c>
       <c r="J89" s="34" t="n">
-        <v>3555</v>
+        <v>58129.01</v>
       </c>
       <c r="K89" s="35" t="n">
-        <v>8478</v>
+        <v>208406.77</v>
       </c>
       <c r="L89" s="34" t="n">
-        <v>2522</v>
+        <v>-188211.1</v>
       </c>
       <c r="M89" s="34" t="n">
-        <v>664</v>
+        <v>-53555.39</v>
       </c>
       <c r="N89" s="34" t="n">
-        <v>16</v>
+        <v>11244.77</v>
       </c>
       <c r="O89" s="34" t="n">
-        <v>-1115</v>
+        <v>-302762.84</v>
       </c>
       <c r="P89" s="35" t="n">
-        <v>2087</v>
+        <v>-533284.5600000001</v>
       </c>
       <c r="Q89" s="34" t="n">
-        <v>-2556</v>
+        <v>273016.62</v>
       </c>
       <c r="R89" s="34" t="n">
-        <v>-1260</v>
+        <v>173229.52</v>
       </c>
       <c r="S89" s="34" t="n">
-        <v>-175</v>
+        <v>177754.72</v>
       </c>
       <c r="T89" s="34" t="n">
-        <v>786</v>
+        <v>-263100.88</v>
       </c>
       <c r="U89" s="35" t="n">
-        <v>-3205</v>
+        <v>360899.98</v>
       </c>
       <c r="V89" s="34" t="n">
-        <v>-556</v>
+        <v>373397.19</v>
       </c>
       <c r="W89" s="34" t="n">
-        <v>2411</v>
+        <v>185990.07</v>
       </c>
       <c r="X89" s="36" t="n">
-        <v>3159</v>
+        <v>33364.41</v>
       </c>
       <c r="Y89" s="10" t="n"/>
       <c r="Z89" s="11" t="n"/>
@@ -17979,66 +18032,66 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E90" s="34" t="n">
-        <v>-277126.05</v>
+        <v>4282.45</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="34" t="n">
-        <v>170813.3</v>
+        <v>1706.76</v>
       </c>
       <c r="H90" s="34" t="n">
-        <v>104465.44</v>
+        <v>2481.35</v>
       </c>
       <c r="I90" s="34" t="n">
-        <v>-125000.98</v>
+        <v>3695.38</v>
       </c>
       <c r="J90" s="34" t="n">
-        <v>58129.01</v>
+        <v>5564.86</v>
       </c>
       <c r="K90" s="35" t="n">
-        <v>208406.77</v>
+        <v>13448.35</v>
       </c>
       <c r="L90" s="34" t="n">
-        <v>-188211.1</v>
+        <v>4357.71</v>
       </c>
       <c r="M90" s="34" t="n">
-        <v>-53555.39</v>
+        <v>3827.73</v>
       </c>
       <c r="N90" s="34" t="n">
-        <v>11244.77</v>
+        <v>3783.54</v>
       </c>
       <c r="O90" s="34" t="n">
-        <v>-302762.84</v>
+        <v>4127.83</v>
       </c>
       <c r="P90" s="35" t="n">
-        <v>-533284.5600000001</v>
+        <v>16096.81</v>
       </c>
       <c r="Q90" s="34" t="n">
-        <v>273016.62</v>
+        <v>4101.74</v>
       </c>
       <c r="R90" s="34" t="n">
-        <v>173229.52</v>
+        <v>4261.59</v>
       </c>
       <c r="S90" s="34" t="n">
-        <v>177754.72</v>
+        <v>4566.95</v>
       </c>
       <c r="T90" s="34" t="n">
-        <v>-263100.88</v>
+        <v>3566.37</v>
       </c>
       <c r="U90" s="35" t="n">
-        <v>360899.98</v>
+        <v>16496.65</v>
       </c>
       <c r="V90" s="34" t="n">
-        <v>373397.19</v>
+        <v>2607.4</v>
       </c>
       <c r="W90" s="34" t="n">
-        <v>185990.07</v>
+        <v>3185.5</v>
       </c>
       <c r="X90" s="36" t="n">
-        <v>33364.41</v>
+        <v>4529.74</v>
       </c>
       <c r="Y90" s="10" t="n"/>
       <c r="Z90" s="11" t="n"/>
@@ -18064,66 +18117,66 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E91" s="34" t="n">
-        <v>4282.45</v>
+        <v>-794.54</v>
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="34" t="n">
-        <v>1706.76</v>
+        <v>-893.52</v>
       </c>
       <c r="H91" s="34" t="n">
-        <v>2481.35</v>
+        <v>-1319.03</v>
       </c>
       <c r="I91" s="34" t="n">
-        <v>3695.38</v>
+        <v>-1626.76</v>
       </c>
       <c r="J91" s="34" t="n">
-        <v>5564.86</v>
+        <v>-1579.31</v>
       </c>
       <c r="K91" s="35" t="n">
-        <v>13448.35</v>
+        <v>-5418.62</v>
       </c>
       <c r="L91" s="34" t="n">
-        <v>4357.71</v>
+        <v>-1516.71</v>
       </c>
       <c r="M91" s="34" t="n">
-        <v>3827.73</v>
+        <v>-2761.78</v>
       </c>
       <c r="N91" s="34" t="n">
-        <v>3783.54</v>
+        <v>-3720.91</v>
       </c>
       <c r="O91" s="34" t="n">
-        <v>4127.83</v>
+        <v>-4621.86</v>
       </c>
       <c r="P91" s="35" t="n">
-        <v>16096.81</v>
+        <v>-12621.26</v>
       </c>
       <c r="Q91" s="34" t="n">
-        <v>4101.74</v>
+        <v>-7512.68</v>
       </c>
       <c r="R91" s="34" t="n">
-        <v>4261.59</v>
+        <v>-4709.32</v>
       </c>
       <c r="S91" s="34" t="n">
-        <v>4566.95</v>
+        <v>-5689.37</v>
       </c>
       <c r="T91" s="34" t="n">
-        <v>3566.37</v>
+        <v>-2725.01</v>
       </c>
       <c r="U91" s="35" t="n">
-        <v>16496.65</v>
+        <v>-20636.38</v>
       </c>
       <c r="V91" s="34" t="n">
-        <v>2607.4</v>
+        <v>-3253.48</v>
       </c>
       <c r="W91" s="34" t="n">
-        <v>3185.5</v>
+        <v>-980.22</v>
       </c>
       <c r="X91" s="36" t="n">
-        <v>4529.74</v>
+        <v>-1138.26</v>
       </c>
       <c r="Y91" s="10" t="n"/>
       <c r="Z91" s="11" t="n"/>
@@ -18149,66 +18202,36 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E92" s="34" t="n">
-        <v>-794.54</v>
+        <v>0</v>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="34" t="n">
-        <v>-893.52</v>
-      </c>
-      <c r="H92" s="34" t="n">
-        <v>-1319.03</v>
-      </c>
       <c r="I92" s="34" t="n">
-        <v>-1626.76</v>
+        <v>0</v>
       </c>
       <c r="J92" s="34" t="n">
-        <v>-1579.31</v>
-      </c>
-      <c r="K92" s="35" t="n">
-        <v>-5418.62</v>
-      </c>
-      <c r="L92" s="34" t="n">
-        <v>-1516.71</v>
-      </c>
-      <c r="M92" s="34" t="n">
-        <v>-2761.78</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K92" s="9" t="n"/>
       <c r="N92" s="34" t="n">
-        <v>-3720.91</v>
+        <v>0</v>
       </c>
       <c r="O92" s="34" t="n">
-        <v>-4621.86</v>
-      </c>
-      <c r="P92" s="35" t="n">
-        <v>-12621.26</v>
-      </c>
-      <c r="Q92" s="34" t="n">
-        <v>-7512.68</v>
-      </c>
-      <c r="R92" s="34" t="n">
-        <v>-4709.32</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P92" s="9" t="n"/>
       <c r="S92" s="34" t="n">
-        <v>-5689.37</v>
+        <v>0</v>
       </c>
       <c r="T92" s="34" t="n">
-        <v>-2725.01</v>
-      </c>
-      <c r="U92" s="35" t="n">
-        <v>-20636.38</v>
-      </c>
-      <c r="V92" s="34" t="n">
-        <v>-3253.48</v>
-      </c>
-      <c r="W92" s="34" t="n">
-        <v>-980.22</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U92" s="9" t="n"/>
       <c r="X92" s="36" t="n">
-        <v>-1138.26</v>
+        <v>0</v>
       </c>
       <c r="Y92" s="10" t="n"/>
       <c r="Z92" s="11" t="n"/>
@@ -18234,36 +18257,66 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E93" s="34" t="n">
-        <v>0</v>
+        <v>998.0599999999999</v>
       </c>
       <c r="F93" s="9" t="n"/>
+      <c r="G93" s="34" t="n">
+        <v>-708.73</v>
+      </c>
+      <c r="H93" s="34" t="n">
+        <v>134.1</v>
+      </c>
       <c r="I93" s="34" t="n">
-        <v>0</v>
+        <v>-855.9</v>
       </c>
       <c r="J93" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="9" t="n"/>
+        <v>-754.63</v>
+      </c>
+      <c r="K93" s="35" t="n">
+        <v>-2185.16</v>
+      </c>
+      <c r="L93" s="34" t="n">
+        <v>-1603.51</v>
+      </c>
+      <c r="M93" s="34" t="n">
+        <v>436.18</v>
+      </c>
       <c r="N93" s="34" t="n">
-        <v>0</v>
+        <v>-908.67</v>
       </c>
       <c r="O93" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" s="9" t="n"/>
+        <v>-891.87</v>
+      </c>
+      <c r="P93" s="35" t="n">
+        <v>-2967.87</v>
+      </c>
+      <c r="Q93" s="34" t="n">
+        <v>-769.0599999999999</v>
+      </c>
+      <c r="R93" s="34" t="n">
+        <v>2243.11</v>
+      </c>
       <c r="S93" s="34" t="n">
-        <v>0</v>
+        <v>-1015.08</v>
       </c>
       <c r="T93" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" s="9" t="n"/>
+        <v>-1671.63</v>
+      </c>
+      <c r="U93" s="35" t="n">
+        <v>-1212.66</v>
+      </c>
+      <c r="V93" s="34" t="n">
+        <v>-2780.83</v>
+      </c>
+      <c r="W93" s="34" t="n">
+        <v>93.31999999999999</v>
+      </c>
       <c r="X93" s="36" t="n">
-        <v>0</v>
+        <v>-4789.56</v>
       </c>
       <c r="Y93" s="10" t="n"/>
       <c r="Z93" s="11" t="n"/>
@@ -18289,66 +18342,66 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E94" s="34" t="n">
-        <v>998.0599999999999</v>
+        <v>59163.3</v>
       </c>
       <c r="F94" s="9" t="n"/>
       <c r="G94" s="34" t="n">
-        <v>-708.73</v>
+        <v>14323.61</v>
       </c>
       <c r="H94" s="34" t="n">
-        <v>134.1</v>
+        <v>-122026.47</v>
       </c>
       <c r="I94" s="34" t="n">
-        <v>-855.9</v>
+        <v>11195.65</v>
       </c>
       <c r="J94" s="34" t="n">
-        <v>-754.63</v>
+        <v>49239.81</v>
       </c>
       <c r="K94" s="35" t="n">
-        <v>-2185.16</v>
+        <v>-47267.4</v>
       </c>
       <c r="L94" s="34" t="n">
-        <v>-1603.51</v>
+        <v>-164.79</v>
       </c>
       <c r="M94" s="34" t="n">
-        <v>436.18</v>
+        <v>-41967.79</v>
       </c>
       <c r="N94" s="34" t="n">
-        <v>-908.67</v>
+        <v>-41352.56</v>
       </c>
       <c r="O94" s="34" t="n">
-        <v>-891.87</v>
+        <v>-28139.68</v>
       </c>
       <c r="P94" s="35" t="n">
-        <v>-2967.87</v>
+        <v>-111624.82</v>
       </c>
       <c r="Q94" s="34" t="n">
-        <v>-769.0599999999999</v>
+        <v>-20168.17</v>
       </c>
       <c r="R94" s="34" t="n">
-        <v>2243.11</v>
+        <v>-46989.31</v>
       </c>
       <c r="S94" s="34" t="n">
-        <v>-1015.08</v>
+        <v>-57535.23</v>
       </c>
       <c r="T94" s="34" t="n">
-        <v>-1671.63</v>
+        <v>-24467.08</v>
       </c>
       <c r="U94" s="35" t="n">
-        <v>-1212.66</v>
+        <v>-149159.79</v>
       </c>
       <c r="V94" s="34" t="n">
-        <v>-2780.83</v>
+        <v>-24053.75</v>
       </c>
       <c r="W94" s="34" t="n">
-        <v>93.31999999999999</v>
+        <v>-43203.86</v>
       </c>
       <c r="X94" s="36" t="n">
-        <v>-4789.56</v>
+        <v>-47602.35</v>
       </c>
       <c r="Y94" s="10" t="n"/>
       <c r="Z94" s="11" t="n"/>
@@ -18374,66 +18427,66 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E95" s="34" t="n">
-        <v>59163.3</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="F95" s="9" t="n"/>
       <c r="G95" s="34" t="n">
-        <v>14323.61</v>
+        <v>152.44</v>
       </c>
       <c r="H95" s="34" t="n">
-        <v>-122026.47</v>
+        <v>144.29</v>
       </c>
       <c r="I95" s="34" t="n">
-        <v>11195.65</v>
+        <v>379.52</v>
       </c>
       <c r="J95" s="34" t="n">
-        <v>49239.81</v>
+        <v>143.01</v>
       </c>
       <c r="K95" s="35" t="n">
-        <v>-47267.4</v>
+        <v>819.26</v>
       </c>
       <c r="L95" s="34" t="n">
-        <v>-164.79</v>
+        <v>96.27</v>
       </c>
       <c r="M95" s="34" t="n">
-        <v>-41967.79</v>
+        <v>156.54</v>
       </c>
       <c r="N95" s="34" t="n">
-        <v>-41352.56</v>
+        <v>1122.85</v>
       </c>
       <c r="O95" s="34" t="n">
-        <v>-28139.68</v>
+        <v>59.91</v>
       </c>
       <c r="P95" s="35" t="n">
-        <v>-111624.82</v>
+        <v>1435.57</v>
       </c>
       <c r="Q95" s="34" t="n">
-        <v>-20168.17</v>
+        <v>21.15</v>
       </c>
       <c r="R95" s="34" t="n">
-        <v>-46989.31</v>
+        <v>56.87</v>
       </c>
       <c r="S95" s="34" t="n">
-        <v>-57535.23</v>
+        <v>57.98</v>
       </c>
       <c r="T95" s="34" t="n">
-        <v>-24467.08</v>
+        <v>100.04</v>
       </c>
       <c r="U95" s="35" t="n">
-        <v>-149159.79</v>
+        <v>236.04</v>
       </c>
       <c r="V95" s="34" t="n">
-        <v>-24053.75</v>
+        <v>75.95</v>
       </c>
       <c r="W95" s="34" t="n">
-        <v>-43203.86</v>
+        <v>32.1</v>
       </c>
       <c r="X95" s="36" t="n">
-        <v>-47602.35</v>
+        <v>155.04</v>
       </c>
       <c r="Y95" s="10" t="n"/>
       <c r="Z95" s="11" t="n"/>
@@ -18459,67 +18512,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="E96" s="34" t="n">
-        <v>81.06999999999999</v>
+        <v>300</v>
       </c>
       <c r="F96" s="9" t="n"/>
-      <c r="G96" s="34" t="n">
-        <v>152.44</v>
-      </c>
-      <c r="H96" s="34" t="n">
-        <v>144.29</v>
-      </c>
-      <c r="I96" s="34" t="n">
-        <v>379.52</v>
-      </c>
-      <c r="J96" s="34" t="n">
-        <v>143.01</v>
-      </c>
-      <c r="K96" s="35" t="n">
-        <v>819.26</v>
-      </c>
-      <c r="L96" s="34" t="n">
-        <v>96.27</v>
-      </c>
-      <c r="M96" s="34" t="n">
-        <v>156.54</v>
-      </c>
-      <c r="N96" s="34" t="n">
-        <v>1122.85</v>
-      </c>
-      <c r="O96" s="34" t="n">
-        <v>59.91</v>
-      </c>
-      <c r="P96" s="35" t="n">
-        <v>1435.57</v>
-      </c>
-      <c r="Q96" s="34" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="R96" s="34" t="n">
-        <v>56.87</v>
-      </c>
-      <c r="S96" s="34" t="n">
-        <v>57.98</v>
-      </c>
-      <c r="T96" s="34" t="n">
-        <v>100.04</v>
-      </c>
-      <c r="U96" s="35" t="n">
-        <v>236.04</v>
-      </c>
-      <c r="V96" s="34" t="n">
-        <v>75.95</v>
-      </c>
-      <c r="W96" s="34" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="X96" s="36" t="n">
-        <v>155.04</v>
-      </c>
+      <c r="K96" s="9" t="n"/>
+      <c r="P96" s="9" t="n"/>
+      <c r="U96" s="9" t="n"/>
+      <c r="X96" s="5" t="n"/>
       <c r="Y96" s="10" t="n"/>
       <c r="Z96" s="11" t="n"/>
       <c r="AA96" s="10" t="n"/>
@@ -18544,17 +18547,67 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E97" s="34" t="n">
-        <v>300</v>
+        <v>24549.79</v>
       </c>
       <c r="F97" s="9" t="n"/>
-      <c r="K97" s="9" t="n"/>
-      <c r="P97" s="9" t="n"/>
-      <c r="U97" s="9" t="n"/>
-      <c r="X97" s="5" t="n"/>
+      <c r="G97" s="34" t="n">
+        <v>25778.59</v>
+      </c>
+      <c r="H97" s="34" t="n">
+        <v>27979.13</v>
+      </c>
+      <c r="I97" s="34" t="n">
+        <v>35363.12</v>
+      </c>
+      <c r="J97" s="34" t="n">
+        <v>24697.17</v>
+      </c>
+      <c r="K97" s="35" t="n">
+        <v>113818.01</v>
+      </c>
+      <c r="L97" s="34" t="n">
+        <v>12709.68</v>
+      </c>
+      <c r="M97" s="34" t="n">
+        <v>36541.6</v>
+      </c>
+      <c r="N97" s="34" t="n">
+        <v>37058.97</v>
+      </c>
+      <c r="O97" s="34" t="n">
+        <v>31051.26</v>
+      </c>
+      <c r="P97" s="35" t="n">
+        <v>117361.51</v>
+      </c>
+      <c r="Q97" s="34" t="n">
+        <v>25245.76</v>
+      </c>
+      <c r="R97" s="34" t="n">
+        <v>40674.65</v>
+      </c>
+      <c r="S97" s="34" t="n">
+        <v>52329.86</v>
+      </c>
+      <c r="T97" s="34" t="n">
+        <v>26366.14</v>
+      </c>
+      <c r="U97" s="35" t="n">
+        <v>144616.41</v>
+      </c>
+      <c r="V97" s="34" t="n">
+        <v>27973.91</v>
+      </c>
+      <c r="W97" s="34" t="n">
+        <v>34297.34</v>
+      </c>
+      <c r="X97" s="36" t="n">
+        <v>42028.58</v>
+      </c>
       <c r="Y97" s="10" t="n"/>
       <c r="Z97" s="11" t="n"/>
       <c r="AA97" s="10" t="n"/>
@@ -18579,66 +18632,66 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E98" s="34" t="n">
-        <v>24549.79</v>
+        <v>24756.66</v>
       </c>
       <c r="F98" s="9" t="n"/>
       <c r="G98" s="34" t="n">
-        <v>25778.59</v>
+        <v>26483.58</v>
       </c>
       <c r="H98" s="34" t="n">
-        <v>27979.13</v>
+        <v>29160.3</v>
       </c>
       <c r="I98" s="34" t="n">
-        <v>35363.12</v>
+        <v>37179.8</v>
       </c>
       <c r="J98" s="34" t="n">
-        <v>24697.17</v>
+        <v>25944.91</v>
       </c>
       <c r="K98" s="35" t="n">
-        <v>113818.01</v>
+        <v>118768.59</v>
       </c>
       <c r="L98" s="34" t="n">
-        <v>12709.68</v>
+        <v>14294.11</v>
       </c>
       <c r="M98" s="34" t="n">
-        <v>36541.6</v>
+        <v>38862.7</v>
       </c>
       <c r="N98" s="34" t="n">
-        <v>37058.97</v>
+        <v>39913.4</v>
       </c>
       <c r="O98" s="34" t="n">
-        <v>31051.26</v>
+        <v>34557.88</v>
       </c>
       <c r="P98" s="35" t="n">
-        <v>117361.51</v>
+        <v>127628.09</v>
       </c>
       <c r="Q98" s="34" t="n">
-        <v>25245.76</v>
+        <v>25987.84</v>
       </c>
       <c r="R98" s="34" t="n">
-        <v>40674.65</v>
+        <v>42005.73</v>
       </c>
       <c r="S98" s="34" t="n">
-        <v>52329.86</v>
+        <v>53479.73</v>
       </c>
       <c r="T98" s="34" t="n">
-        <v>26366.14</v>
+        <v>29797.7</v>
       </c>
       <c r="U98" s="35" t="n">
-        <v>144616.41</v>
+        <v>151271</v>
       </c>
       <c r="V98" s="34" t="n">
-        <v>27973.91</v>
+        <v>28478.81</v>
       </c>
       <c r="W98" s="34" t="n">
-        <v>34297.34</v>
+        <v>35116.14</v>
       </c>
       <c r="X98" s="36" t="n">
-        <v>42028.58</v>
+        <v>42880.66</v>
       </c>
       <c r="Y98" s="10" t="n"/>
       <c r="Z98" s="11" t="n"/>
@@ -18664,66 +18717,66 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E99" s="34" t="n">
-        <v>24756.66</v>
+        <v>206.87</v>
       </c>
       <c r="F99" s="9" t="n"/>
       <c r="G99" s="34" t="n">
-        <v>26483.58</v>
+        <v>704.99</v>
       </c>
       <c r="H99" s="34" t="n">
-        <v>29160.3</v>
+        <v>1181.17</v>
       </c>
       <c r="I99" s="34" t="n">
-        <v>37179.8</v>
+        <v>1816.68</v>
       </c>
       <c r="J99" s="34" t="n">
-        <v>25944.91</v>
+        <v>1247.74</v>
       </c>
       <c r="K99" s="35" t="n">
-        <v>118768.59</v>
+        <v>4950.58</v>
       </c>
       <c r="L99" s="34" t="n">
-        <v>14294.11</v>
+        <v>1584.43</v>
       </c>
       <c r="M99" s="34" t="n">
-        <v>38862.7</v>
+        <v>2321.1</v>
       </c>
       <c r="N99" s="34" t="n">
-        <v>39913.4</v>
+        <v>2854.43</v>
       </c>
       <c r="O99" s="34" t="n">
-        <v>34557.88</v>
+        <v>3506.62</v>
       </c>
       <c r="P99" s="35" t="n">
-        <v>127628.09</v>
+        <v>10266.58</v>
       </c>
       <c r="Q99" s="34" t="n">
-        <v>25987.84</v>
+        <v>742.08</v>
       </c>
       <c r="R99" s="34" t="n">
-        <v>42005.73</v>
+        <v>1331.08</v>
       </c>
       <c r="S99" s="34" t="n">
-        <v>53479.73</v>
+        <v>1149.87</v>
       </c>
       <c r="T99" s="34" t="n">
-        <v>29797.7</v>
+        <v>3431.56</v>
       </c>
       <c r="U99" s="35" t="n">
-        <v>151271</v>
+        <v>6654.59</v>
       </c>
       <c r="V99" s="34" t="n">
-        <v>28478.81</v>
+        <v>504.9</v>
       </c>
       <c r="W99" s="34" t="n">
-        <v>35116.14</v>
+        <v>818.8</v>
       </c>
       <c r="X99" s="36" t="n">
-        <v>42880.66</v>
+        <v>852.08</v>
       </c>
       <c r="Y99" s="10" t="n"/>
       <c r="Z99" s="11" t="n"/>
@@ -18749,66 +18802,66 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E100" s="34" t="n">
-        <v>206.87</v>
+        <v>-19803.01</v>
       </c>
       <c r="F100" s="9" t="n"/>
       <c r="G100" s="34" t="n">
-        <v>704.99</v>
+        <v>29459.88</v>
       </c>
       <c r="H100" s="34" t="n">
-        <v>1181.17</v>
+        <v>-22849.06</v>
       </c>
       <c r="I100" s="34" t="n">
-        <v>1816.68</v>
+        <v>-41952.08</v>
       </c>
       <c r="J100" s="34" t="n">
-        <v>1247.74</v>
+        <v>-36271.62</v>
       </c>
       <c r="K100" s="35" t="n">
-        <v>4950.58</v>
+        <v>-71612.88</v>
       </c>
       <c r="L100" s="34" t="n">
-        <v>1584.43</v>
+        <v>61195.62</v>
       </c>
       <c r="M100" s="34" t="n">
-        <v>2321.1</v>
+        <v>112168.78</v>
       </c>
       <c r="N100" s="34" t="n">
-        <v>2854.43</v>
+        <v>72702.5</v>
       </c>
       <c r="O100" s="34" t="n">
-        <v>3506.62</v>
+        <v>217579.95</v>
       </c>
       <c r="P100" s="35" t="n">
-        <v>10266.58</v>
+        <v>463646.85</v>
       </c>
       <c r="Q100" s="34" t="n">
-        <v>742.08</v>
+        <v>-145772.01</v>
       </c>
       <c r="R100" s="34" t="n">
-        <v>1331.08</v>
+        <v>-124965.07</v>
       </c>
       <c r="S100" s="34" t="n">
-        <v>1149.87</v>
+        <v>-140452.34</v>
       </c>
       <c r="T100" s="34" t="n">
-        <v>3431.56</v>
+        <v>48048.03</v>
       </c>
       <c r="U100" s="35" t="n">
-        <v>6654.59</v>
+        <v>-363141.39</v>
       </c>
       <c r="V100" s="34" t="n">
-        <v>504.9</v>
+        <v>-80956.35000000001</v>
       </c>
       <c r="W100" s="34" t="n">
-        <v>818.8</v>
+        <v>-58905.22</v>
       </c>
       <c r="X100" s="36" t="n">
-        <v>852.08</v>
+        <v>-26092.23</v>
       </c>
       <c r="Y100" s="10" t="n"/>
       <c r="Z100" s="11" t="n"/>
@@ -18834,66 +18887,66 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>리스부채의상환</t>
         </is>
       </c>
       <c r="E101" s="34" t="n">
-        <v>-19803.01</v>
+        <v>488.69</v>
       </c>
       <c r="F101" s="9" t="n"/>
       <c r="G101" s="34" t="n">
-        <v>29459.88</v>
+        <v>277.53</v>
       </c>
       <c r="H101" s="34" t="n">
-        <v>-22849.06</v>
+        <v>292.48</v>
       </c>
       <c r="I101" s="34" t="n">
-        <v>-41952.08</v>
+        <v>478.95</v>
       </c>
       <c r="J101" s="34" t="n">
-        <v>-36271.62</v>
+        <v>460.06</v>
       </c>
       <c r="K101" s="35" t="n">
-        <v>-71612.88</v>
+        <v>1509.02</v>
       </c>
       <c r="L101" s="34" t="n">
-        <v>61195.62</v>
+        <v>298.33</v>
       </c>
       <c r="M101" s="34" t="n">
-        <v>112168.78</v>
+        <v>369.84</v>
       </c>
       <c r="N101" s="34" t="n">
-        <v>72702.5</v>
+        <v>591.8200000000001</v>
       </c>
       <c r="O101" s="34" t="n">
-        <v>217579.95</v>
+        <v>404.48</v>
       </c>
       <c r="P101" s="35" t="n">
-        <v>463646.85</v>
+        <v>1664.47</v>
       </c>
       <c r="Q101" s="34" t="n">
-        <v>-145772.01</v>
+        <v>1671.26</v>
       </c>
       <c r="R101" s="34" t="n">
-        <v>-124965.07</v>
+        <v>1472.54</v>
       </c>
       <c r="S101" s="34" t="n">
-        <v>-140452.34</v>
+        <v>1346.52</v>
       </c>
       <c r="T101" s="34" t="n">
-        <v>48048.03</v>
+        <v>1299.29</v>
       </c>
       <c r="U101" s="35" t="n">
-        <v>-363141.39</v>
+        <v>5789.61</v>
       </c>
       <c r="V101" s="34" t="n">
-        <v>-80956.35000000001</v>
+        <v>956.35</v>
       </c>
       <c r="W101" s="34" t="n">
-        <v>-58905.22</v>
+        <v>1012.32</v>
       </c>
       <c r="X101" s="36" t="n">
-        <v>-26092.23</v>
+        <v>1412.31</v>
       </c>
       <c r="Y101" s="10" t="n"/>
       <c r="Z101" s="11" t="n"/>
@@ -18919,66 +18972,66 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>현금및현금성자산의증감</t>
         </is>
       </c>
       <c r="E102" s="34" t="n">
-        <v>488.69</v>
+        <v>-237877.95</v>
       </c>
       <c r="F102" s="9" t="n"/>
       <c r="G102" s="34" t="n">
-        <v>277.53</v>
+        <v>215217.07</v>
       </c>
       <c r="H102" s="34" t="n">
-        <v>292.48</v>
+        <v>-37791.11</v>
       </c>
       <c r="I102" s="34" t="n">
-        <v>478.95</v>
+        <v>-151538.89</v>
       </c>
       <c r="J102" s="34" t="n">
-        <v>460.06</v>
+        <v>63885.83</v>
       </c>
       <c r="K102" s="35" t="n">
-        <v>1509.02</v>
+        <v>89772.89999999999</v>
       </c>
       <c r="L102" s="34" t="n">
-        <v>298.33</v>
+        <v>-125351.78</v>
       </c>
       <c r="M102" s="34" t="n">
-        <v>369.84</v>
+        <v>16293.35</v>
       </c>
       <c r="N102" s="34" t="n">
-        <v>591.8200000000001</v>
+        <v>43112.89</v>
       </c>
       <c r="O102" s="34" t="n">
-        <v>404.48</v>
+        <v>-114157.42</v>
       </c>
       <c r="P102" s="35" t="n">
-        <v>1664.47</v>
+        <v>-180102.96</v>
       </c>
       <c r="Q102" s="34" t="n">
-        <v>1671.26</v>
+        <v>108171.53</v>
       </c>
       <c r="R102" s="34" t="n">
-        <v>1472.54</v>
+        <v>2781.94</v>
       </c>
       <c r="S102" s="34" t="n">
-        <v>1346.52</v>
+        <v>-24390.76</v>
       </c>
       <c r="T102" s="34" t="n">
-        <v>1299.29</v>
+        <v>-231507.39</v>
       </c>
       <c r="U102" s="35" t="n">
-        <v>5789.61</v>
+        <v>-144944.68</v>
       </c>
       <c r="V102" s="34" t="n">
-        <v>956.35</v>
+        <v>268913.28</v>
       </c>
       <c r="W102" s="34" t="n">
-        <v>1012.32</v>
+        <v>78806.78999999999</v>
       </c>
       <c r="X102" s="36" t="n">
-        <v>1412.31</v>
+        <v>-39252.17</v>
       </c>
       <c r="Y102" s="10" t="n"/>
       <c r="Z102" s="11" t="n"/>
@@ -19004,7 +19057,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>기말현금및현금성자산</t>
         </is>
       </c>
       <c r="E103" s="34" t="n">
@@ -19012,7 +19065,7 @@
       </c>
       <c r="F103" s="9" t="n"/>
       <c r="G103" s="34" t="n">
-        <v>215217.07</v>
+        <v>615588.03</v>
       </c>
       <c r="H103" s="34" t="n">
         <v>-37791.11</v>
@@ -19021,13 +19074,13 @@
         <v>-151538.89</v>
       </c>
       <c r="J103" s="34" t="n">
-        <v>63885.83</v>
+        <v>63885.82</v>
       </c>
       <c r="K103" s="35" t="n">
-        <v>89772.89999999999</v>
+        <v>490143.85</v>
       </c>
       <c r="L103" s="34" t="n">
-        <v>-125351.78</v>
+        <v>364792.08</v>
       </c>
       <c r="M103" s="34" t="n">
         <v>16293.35</v>
@@ -19036,16 +19089,16 @@
         <v>43112.89</v>
       </c>
       <c r="O103" s="34" t="n">
-        <v>-114157.42</v>
+        <v>-114157.43</v>
       </c>
       <c r="P103" s="35" t="n">
-        <v>-180102.96</v>
+        <v>310040.89</v>
       </c>
       <c r="Q103" s="34" t="n">
-        <v>108171.53</v>
+        <v>418212.43</v>
       </c>
       <c r="R103" s="34" t="n">
-        <v>2781.94</v>
+        <v>2781.93</v>
       </c>
       <c r="S103" s="34" t="n">
         <v>-24390.76</v>
@@ -19054,10 +19107,10 @@
         <v>-231507.39</v>
       </c>
       <c r="U103" s="35" t="n">
-        <v>-144944.68</v>
+        <v>165096.21</v>
       </c>
       <c r="V103" s="34" t="n">
-        <v>268913.28</v>
+        <v>434009.49</v>
       </c>
       <c r="W103" s="34" t="n">
         <v>78806.78999999999</v>
@@ -19089,66 +19142,15 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
-        </is>
-      </c>
-      <c r="E104" s="34" t="n">
-        <v>-237877.95</v>
+          <t>배당금지급</t>
+        </is>
       </c>
       <c r="F104" s="9" t="n"/>
-      <c r="G104" s="34" t="n">
-        <v>615588.03</v>
-      </c>
-      <c r="H104" s="34" t="n">
-        <v>-37791.11</v>
-      </c>
-      <c r="I104" s="34" t="n">
-        <v>-151538.89</v>
-      </c>
-      <c r="J104" s="34" t="n">
-        <v>63885.82</v>
-      </c>
-      <c r="K104" s="35" t="n">
-        <v>490143.85</v>
-      </c>
-      <c r="L104" s="34" t="n">
-        <v>364792.08</v>
-      </c>
-      <c r="M104" s="34" t="n">
-        <v>16293.35</v>
-      </c>
-      <c r="N104" s="34" t="n">
-        <v>43112.89</v>
-      </c>
-      <c r="O104" s="34" t="n">
-        <v>-114157.43</v>
-      </c>
-      <c r="P104" s="35" t="n">
-        <v>310040.89</v>
-      </c>
-      <c r="Q104" s="34" t="n">
-        <v>418212.43</v>
-      </c>
-      <c r="R104" s="34" t="n">
-        <v>2781.93</v>
-      </c>
-      <c r="S104" s="34" t="n">
-        <v>-24390.76</v>
-      </c>
-      <c r="T104" s="34" t="n">
-        <v>-231507.39</v>
-      </c>
-      <c r="U104" s="35" t="n">
-        <v>165096.21</v>
-      </c>
-      <c r="V104" s="34" t="n">
-        <v>434009.49</v>
-      </c>
-      <c r="W104" s="34" t="n">
-        <v>78806.78999999999</v>
-      </c>
+      <c r="K104" s="9" t="n"/>
+      <c r="P104" s="9" t="n"/>
+      <c r="U104" s="9" t="n"/>
       <c r="X104" s="36" t="n">
-        <v>-39252.17</v>
+        <v>19144.46</v>
       </c>
       <c r="Y104" s="10" t="n"/>
       <c r="Z104" s="11" t="n"/>
@@ -19167,40 +19169,6 @@
       <c r="AM104" s="10" t="n"/>
       <c r="AN104" s="10" t="n"/>
       <c r="AO104" s="11" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>배당금지급</t>
-        </is>
-      </c>
-      <c r="F105" s="9" t="n"/>
-      <c r="K105" s="9" t="n"/>
-      <c r="P105" s="9" t="n"/>
-      <c r="U105" s="9" t="n"/>
-      <c r="X105" s="36" t="n">
-        <v>19144.46</v>
-      </c>
-      <c r="Y105" s="10" t="n"/>
-      <c r="Z105" s="11" t="n"/>
-      <c r="AA105" s="10" t="n"/>
-      <c r="AB105" s="10" t="n"/>
-      <c r="AC105" s="10" t="n"/>
-      <c r="AD105" s="10" t="n"/>
-      <c r="AE105" s="11" t="n"/>
-      <c r="AF105" s="10" t="n"/>
-      <c r="AG105" s="10" t="n"/>
-      <c r="AH105" s="10" t="n"/>
-      <c r="AI105" s="10" t="n"/>
-      <c r="AJ105" s="11" t="n"/>
-      <c r="AK105" s="10" t="n"/>
-      <c r="AL105" s="10" t="n"/>
-      <c r="AM105" s="10" t="n"/>
-      <c r="AN105" s="10" t="n"/>
-      <c r="AO105" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -5032,7 +5032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-09</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5906,35 +5906,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -6025,35 +6025,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6144,35 +6144,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6263,35 +6263,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6382,35 +6382,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6501,35 +6501,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6620,35 +6620,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6739,35 +6739,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -5032,7 +5032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-10</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -5032,7 +5032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-11</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -5032,7 +5032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-12</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5906,35 +5906,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -6025,35 +6025,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6144,35 +6144,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6263,35 +6263,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6382,35 +6382,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6501,35 +6501,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6620,35 +6620,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6739,35 +6739,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -5032,7 +5032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-13</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5906,35 +5906,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -6025,35 +6025,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6144,35 +6144,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6263,35 +6263,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6382,35 +6382,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6501,35 +6501,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6620,35 +6620,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6739,35 +6739,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -5032,7 +5032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-14</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5906,35 +5906,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -6025,35 +6025,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6144,35 +6144,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6263,35 +6263,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6382,35 +6382,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6501,35 +6501,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6620,35 +6620,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6739,35 +6739,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010620_model.xlsx
+++ b/argus/kship/models/010620_model.xlsx
@@ -5032,7 +5032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-19</t>
+          <t>기준 분기 2025Q3 · 마지막 실적 2025Q3 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5906,35 +5906,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -6025,35 +6025,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6144,35 +6144,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6263,35 +6263,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6382,35 +6382,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6501,35 +6501,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6620,35 +6620,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6739,35 +6739,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
